--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1572,6 +1572,118 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122497899</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57395</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>729278</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6367652</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson, Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490429</v>
+        <v>122490442</v>
       </c>
       <c r="B2" t="n">
-        <v>98180</v>
+        <v>106115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot</t>
-        </is>
+        <v>221903</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -729,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729301</v>
+        <v>729269</v>
       </c>
       <c r="R2" t="n">
-        <v>6367596</v>
+        <v>6367497</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490442</v>
+        <v>122490425</v>
       </c>
       <c r="B3" t="n">
-        <v>106106</v>
+        <v>106115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,11 +800,6 @@
       <c r="E3" t="n">
         <v>221903</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Axveronika</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Veronica spicata</t>
@@ -836,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729269</v>
+        <v>729247</v>
       </c>
       <c r="R3" t="n">
-        <v>6367497</v>
+        <v>6367747</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,11 +860,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,6 +868,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -903,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490425</v>
+        <v>122490424</v>
       </c>
       <c r="B4" t="n">
-        <v>106106</v>
+        <v>103737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Axveronika</t>
-        </is>
+        <v>220164</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1018,7 +999,7 @@
         <v>122490411</v>
       </c>
       <c r="B5" t="n">
-        <v>106106</v>
+        <v>106115</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,11 +1013,6 @@
       </c>
       <c r="E5" t="n">
         <v>221903</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Axveronika</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1122,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490424</v>
+        <v>122490446</v>
       </c>
       <c r="B6" t="n">
-        <v>103728</v>
+        <v>100477</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,43 +1110,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220164</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Solvända</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729247</v>
+        <v>729149</v>
       </c>
       <c r="R6" t="n">
-        <v>6367747</v>
+        <v>6367526</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,6 +1171,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vid gamla stenbrott.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1213,11 +1184,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1234,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490446</v>
+        <v>122490448</v>
       </c>
       <c r="B7" t="n">
-        <v>100468</v>
+        <v>106115</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,38 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>221903</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729149</v>
+        <v>729134</v>
       </c>
       <c r="R7" t="n">
-        <v>6367526</v>
+        <v>6367511</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,11 +1278,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1325,6 +1286,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1344,7 +1310,7 @@
         <v>122490430</v>
       </c>
       <c r="B8" t="n">
-        <v>98180</v>
+        <v>98189</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,11 +1324,6 @@
       </c>
       <c r="E8" t="n">
         <v>219798</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skogsknipprot</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1462,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490448</v>
+        <v>122490429</v>
       </c>
       <c r="B9" t="n">
-        <v>106106</v>
+        <v>98189</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,28 +1435,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221903</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Axveronika</t>
-        </is>
+        <v>219798</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1507,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729134</v>
+        <v>729301</v>
       </c>
       <c r="R9" t="n">
-        <v>6367511</v>
+        <v>6367596</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1553,11 +1518,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1591,11 +1551,6 @@
       </c>
       <c r="E10" t="n">
         <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490442</v>
+        <v>122490424</v>
       </c>
       <c r="B2" t="n">
-        <v>106115</v>
+        <v>103750</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221903</v>
+        <v>220164</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729269</v>
+        <v>729247</v>
       </c>
       <c r="R2" t="n">
-        <v>6367497</v>
+        <v>6367747</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,11 +758,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490425</v>
+        <v>122490429</v>
       </c>
       <c r="B3" t="n">
-        <v>106115</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,23 +799,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>219798</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -822,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729247</v>
+        <v>729301</v>
       </c>
       <c r="R3" t="n">
-        <v>6367747</v>
+        <v>6367596</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,11 +887,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490424</v>
+        <v>122490446</v>
       </c>
       <c r="B4" t="n">
-        <v>103737</v>
+        <v>100490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220164</v>
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729247</v>
+        <v>729149</v>
       </c>
       <c r="R4" t="n">
-        <v>6367747</v>
+        <v>6367526</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,6 +981,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid gamla stenbrott.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,11 +994,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490411</v>
+        <v>122490442</v>
       </c>
       <c r="B5" t="n">
-        <v>106115</v>
+        <v>106128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,6 +1028,11 @@
       <c r="E5" t="n">
         <v>221903</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Veronica spicata</t>
@@ -1036,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729160</v>
+        <v>729269</v>
       </c>
       <c r="R5" t="n">
-        <v>6367602</v>
+        <v>6367497</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,6 +1091,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490446</v>
+        <v>122490411</v>
       </c>
       <c r="B6" t="n">
-        <v>100477</v>
+        <v>106128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,33 +1134,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221903</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729149</v>
+        <v>729160</v>
       </c>
       <c r="R6" t="n">
-        <v>6367526</v>
+        <v>6367602</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,11 +1203,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1232,7 @@
         <v>122490448</v>
       </c>
       <c r="B7" t="n">
-        <v>106115</v>
+        <v>106128</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,6 +1246,11 @@
       </c>
       <c r="E7" t="n">
         <v>221903</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1307,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490430</v>
+        <v>122490425</v>
       </c>
       <c r="B8" t="n">
-        <v>98189</v>
+        <v>106128</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,32 +1353,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>221903</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1356,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729303</v>
+        <v>729247</v>
       </c>
       <c r="R8" t="n">
-        <v>6367559</v>
+        <v>6367747</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,11 +1424,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1407,6 +1432,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1423,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490429</v>
+        <v>122490430</v>
       </c>
       <c r="B9" t="n">
-        <v>98189</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,6 +1471,11 @@
       <c r="E9" t="n">
         <v>219798</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Epipactis helleborine</t>
@@ -1453,7 +1488,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1472,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729301</v>
+        <v>729303</v>
       </c>
       <c r="R9" t="n">
-        <v>6367596</v>
+        <v>6367559</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1508,6 +1543,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,7 +1577,7 @@
         <v>122497899</v>
       </c>
       <c r="B10" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,6 +1591,11 @@
       </c>
       <c r="E10" t="n">
         <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490424</v>
+        <v>122490448</v>
       </c>
       <c r="B2" t="n">
-        <v>103750</v>
+        <v>106141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729247</v>
+        <v>729134</v>
       </c>
       <c r="R2" t="n">
-        <v>6367747</v>
+        <v>6367511</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkglänta</t>
+          <t>Glänta</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490429</v>
+        <v>122490425</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>106141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,37 +799,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729301</v>
+        <v>729247</v>
       </c>
       <c r="R3" t="n">
-        <v>6367596</v>
+        <v>6367747</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,6 +878,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490446</v>
+        <v>122490424</v>
       </c>
       <c r="B4" t="n">
-        <v>100490</v>
+        <v>103763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220164</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729149</v>
+        <v>729247</v>
       </c>
       <c r="R4" t="n">
-        <v>6367526</v>
+        <v>6367747</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,11 +982,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -994,6 +990,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1010,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490442</v>
+        <v>122490429</v>
       </c>
       <c r="B5" t="n">
-        <v>106128</v>
+        <v>98215</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,28 +1023,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1055,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729269</v>
+        <v>729301</v>
       </c>
       <c r="R5" t="n">
-        <v>6367497</v>
+        <v>6367596</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,11 +1101,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490411</v>
+        <v>122490430</v>
       </c>
       <c r="B6" t="n">
-        <v>106128</v>
+        <v>98215</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,28 +1139,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1167,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729160</v>
+        <v>729303</v>
       </c>
       <c r="R6" t="n">
-        <v>6367602</v>
+        <v>6367559</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,6 +1217,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490448</v>
+        <v>122490442</v>
       </c>
       <c r="B7" t="n">
-        <v>106128</v>
+        <v>106141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729134</v>
+        <v>729269</v>
       </c>
       <c r="R7" t="n">
-        <v>6367511</v>
+        <v>6367497</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,6 +1331,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1320,11 +1344,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1341,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490425</v>
+        <v>122490411</v>
       </c>
       <c r="B8" t="n">
-        <v>106128</v>
+        <v>106141</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729247</v>
+        <v>729160</v>
       </c>
       <c r="R8" t="n">
-        <v>6367747</v>
+        <v>6367602</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,11 +1451,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1453,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490430</v>
+        <v>122490446</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>100503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,48 +1483,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729303</v>
+        <v>729149</v>
       </c>
       <c r="R9" t="n">
-        <v>6367559</v>
+        <v>6367526</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
+          <t>Vid gamla stenbrott.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490448</v>
+        <v>122490411</v>
       </c>
       <c r="B2" t="n">
         <v>106141</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729134</v>
+        <v>729160</v>
       </c>
       <c r="R2" t="n">
-        <v>6367511</v>
+        <v>6367602</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -766,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490425</v>
+        <v>122490424</v>
       </c>
       <c r="B3" t="n">
-        <v>106141</v>
+        <v>103763</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490424</v>
+        <v>122490448</v>
       </c>
       <c r="B4" t="n">
-        <v>103763</v>
+        <v>106141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729247</v>
+        <v>729134</v>
       </c>
       <c r="R4" t="n">
-        <v>6367747</v>
+        <v>6367511</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkglänta</t>
+          <t>Glänta</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490429</v>
+        <v>122490425</v>
       </c>
       <c r="B5" t="n">
-        <v>98215</v>
+        <v>106141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,37 +1018,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1065,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729301</v>
+        <v>729247</v>
       </c>
       <c r="R5" t="n">
-        <v>6367596</v>
+        <v>6367747</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,6 +1097,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1248,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490442</v>
+        <v>122490429</v>
       </c>
       <c r="B7" t="n">
-        <v>106141</v>
+        <v>98215</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,28 +1251,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729269</v>
+        <v>729301</v>
       </c>
       <c r="R7" t="n">
-        <v>6367497</v>
+        <v>6367596</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,11 +1329,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1355,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490411</v>
+        <v>122490442</v>
       </c>
       <c r="B8" t="n">
         <v>106141</v>
@@ -1405,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729160</v>
+        <v>729269</v>
       </c>
       <c r="R8" t="n">
-        <v>6367602</v>
+        <v>6367497</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1441,6 +1436,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490411</v>
+        <v>122490424</v>
       </c>
       <c r="B2" t="n">
-        <v>106141</v>
+        <v>103766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729160</v>
+        <v>729247</v>
       </c>
       <c r="R2" t="n">
-        <v>6367602</v>
+        <v>6367747</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -766,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490424</v>
+        <v>122490429</v>
       </c>
       <c r="B3" t="n">
-        <v>103763</v>
+        <v>98218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,28 +799,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -827,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729247</v>
+        <v>729301</v>
       </c>
       <c r="R3" t="n">
-        <v>6367747</v>
+        <v>6367596</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,11 +887,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490448</v>
+        <v>122490446</v>
       </c>
       <c r="B4" t="n">
-        <v>106141</v>
+        <v>100506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,43 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729134</v>
+        <v>729149</v>
       </c>
       <c r="R4" t="n">
-        <v>6367511</v>
+        <v>6367526</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,6 +981,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid gamla stenbrott.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -985,11 +994,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490425</v>
+        <v>122490430</v>
       </c>
       <c r="B5" t="n">
-        <v>106141</v>
+        <v>98218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,28 +1022,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1051,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729247</v>
+        <v>729303</v>
       </c>
       <c r="R5" t="n">
-        <v>6367747</v>
+        <v>6367559</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,6 +1102,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1097,11 +1115,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490430</v>
+        <v>122490425</v>
       </c>
       <c r="B6" t="n">
-        <v>98215</v>
+        <v>106144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,37 +1143,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1172,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729303</v>
+        <v>729247</v>
       </c>
       <c r="R6" t="n">
-        <v>6367559</v>
+        <v>6367747</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,11 +1214,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1223,6 +1222,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1239,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490429</v>
+        <v>122490448</v>
       </c>
       <c r="B7" t="n">
-        <v>98215</v>
+        <v>106144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,37 +1255,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1293,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729301</v>
+        <v>729134</v>
       </c>
       <c r="R7" t="n">
-        <v>6367596</v>
+        <v>6367511</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,6 +1334,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1358,7 +1358,7 @@
         <v>122490442</v>
       </c>
       <c r="B8" t="n">
-        <v>106141</v>
+        <v>106144</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490446</v>
+        <v>122490411</v>
       </c>
       <c r="B9" t="n">
-        <v>100503</v>
+        <v>106144</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,38 +1479,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221903</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729149</v>
+        <v>729160</v>
       </c>
       <c r="R9" t="n">
-        <v>6367526</v>
+        <v>6367602</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1543,11 +1548,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490424</v>
+        <v>122490442</v>
       </c>
       <c r="B2" t="n">
-        <v>103766</v>
+        <v>106144</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729247</v>
+        <v>729269</v>
       </c>
       <c r="R2" t="n">
-        <v>6367747</v>
+        <v>6367497</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,6 +758,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,11 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490429</v>
+        <v>122490448</v>
       </c>
       <c r="B3" t="n">
-        <v>98218</v>
+        <v>106144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,37 +799,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729301</v>
+        <v>729134</v>
       </c>
       <c r="R3" t="n">
-        <v>6367596</v>
+        <v>6367511</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,6 +878,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490446</v>
+        <v>122490429</v>
       </c>
       <c r="B4" t="n">
-        <v>100506</v>
+        <v>98218</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +915,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729149</v>
+        <v>729301</v>
       </c>
       <c r="R4" t="n">
-        <v>6367526</v>
+        <v>6367596</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,11 +989,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490430</v>
+        <v>122490424</v>
       </c>
       <c r="B5" t="n">
-        <v>98218</v>
+        <v>103766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,37 +1027,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220164</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1064,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729303</v>
+        <v>729247</v>
       </c>
       <c r="R5" t="n">
-        <v>6367559</v>
+        <v>6367747</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,11 +1098,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1115,6 +1106,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1131,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490425</v>
+        <v>122490446</v>
       </c>
       <c r="B6" t="n">
-        <v>106144</v>
+        <v>100506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,43 +1139,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221903</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729247</v>
+        <v>729149</v>
       </c>
       <c r="R6" t="n">
-        <v>6367747</v>
+        <v>6367526</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,6 +1205,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vid gamla stenbrott.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1222,11 +1218,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1243,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490448</v>
+        <v>122490425</v>
       </c>
       <c r="B7" t="n">
         <v>106144</v>
@@ -1288,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729134</v>
+        <v>729247</v>
       </c>
       <c r="R7" t="n">
-        <v>6367511</v>
+        <v>6367747</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1328,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Glänta</t>
+          <t>Kalkglänta</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1355,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490442</v>
+        <v>122490430</v>
       </c>
       <c r="B8" t="n">
-        <v>106144</v>
+        <v>98218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,28 +1358,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729269</v>
+        <v>729303</v>
       </c>
       <c r="R8" t="n">
-        <v>6367497</v>
+        <v>6367559</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
+          <t>10 m norrut finns ett kalkbrott.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490442</v>
+        <v>122490429</v>
       </c>
       <c r="B2" t="n">
-        <v>106144</v>
+        <v>98219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -720,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729269</v>
+        <v>729301</v>
       </c>
       <c r="R2" t="n">
-        <v>6367497</v>
+        <v>6367596</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,11 +765,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490448</v>
+        <v>122490424</v>
       </c>
       <c r="B3" t="n">
-        <v>106144</v>
+        <v>103767</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729134</v>
+        <v>729247</v>
       </c>
       <c r="R3" t="n">
-        <v>6367511</v>
+        <v>6367747</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,7 +885,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Glänta</t>
+          <t>Kalkglänta</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490429</v>
+        <v>122490430</v>
       </c>
       <c r="B4" t="n">
-        <v>98218</v>
+        <v>98219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -953,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729301</v>
+        <v>729303</v>
       </c>
       <c r="R4" t="n">
-        <v>6367596</v>
+        <v>6367559</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,6 +993,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490424</v>
+        <v>122490442</v>
       </c>
       <c r="B5" t="n">
-        <v>103766</v>
+        <v>106145</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729247</v>
+        <v>729269</v>
       </c>
       <c r="R5" t="n">
-        <v>6367747</v>
+        <v>6367497</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,6 +1107,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1106,11 +1120,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1127,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490446</v>
+        <v>122490411</v>
       </c>
       <c r="B6" t="n">
-        <v>100506</v>
+        <v>106145</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1148,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221903</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729149</v>
+        <v>729160</v>
       </c>
       <c r="R6" t="n">
-        <v>6367526</v>
+        <v>6367602</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,11 +1217,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490425</v>
+        <v>122490448</v>
       </c>
       <c r="B7" t="n">
-        <v>106144</v>
+        <v>106145</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729247</v>
+        <v>729134</v>
       </c>
       <c r="R7" t="n">
-        <v>6367747</v>
+        <v>6367511</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1337,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkglänta</t>
+          <t>Glänta</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1346,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490430</v>
+        <v>122490425</v>
       </c>
       <c r="B8" t="n">
-        <v>98218</v>
+        <v>106145</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,37 +1367,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729303</v>
+        <v>729247</v>
       </c>
       <c r="R8" t="n">
-        <v>6367559</v>
+        <v>6367747</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,11 +1438,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1451,6 +1446,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490411</v>
+        <v>122490446</v>
       </c>
       <c r="B9" t="n">
-        <v>106144</v>
+        <v>100507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,43 +1479,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221903</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729160</v>
+        <v>729149</v>
       </c>
       <c r="R9" t="n">
-        <v>6367602</v>
+        <v>6367526</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,6 +1543,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vid gamla stenbrott.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,7 +1577,7 @@
         <v>122497899</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122490429</v>
       </c>
       <c r="B2" t="n">
-        <v>98219</v>
+        <v>98222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490424</v>
+        <v>122490430</v>
       </c>
       <c r="B3" t="n">
-        <v>103767</v>
+        <v>98222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,28 +803,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -836,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729247</v>
+        <v>729303</v>
       </c>
       <c r="R3" t="n">
-        <v>6367747</v>
+        <v>6367559</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,6 +883,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -882,11 +896,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -903,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490430</v>
+        <v>122490411</v>
       </c>
       <c r="B4" t="n">
-        <v>98219</v>
+        <v>106148</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +924,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729303</v>
+        <v>729160</v>
       </c>
       <c r="R4" t="n">
-        <v>6367559</v>
+        <v>6367602</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,11 +993,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490442</v>
+        <v>122490424</v>
       </c>
       <c r="B5" t="n">
-        <v>106145</v>
+        <v>103770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729269</v>
+        <v>729247</v>
       </c>
       <c r="R5" t="n">
-        <v>6367497</v>
+        <v>6367747</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,11 +1102,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1120,6 +1110,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1136,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490411</v>
+        <v>122490425</v>
       </c>
       <c r="B6" t="n">
-        <v>106145</v>
+        <v>106148</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729160</v>
+        <v>729247</v>
       </c>
       <c r="R6" t="n">
-        <v>6367602</v>
+        <v>6367747</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,6 +1222,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1243,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490448</v>
+        <v>122490442</v>
       </c>
       <c r="B7" t="n">
-        <v>106145</v>
+        <v>106148</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729134</v>
+        <v>729269</v>
       </c>
       <c r="R7" t="n">
-        <v>6367511</v>
+        <v>6367497</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,6 +1326,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1334,11 +1339,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490425</v>
+        <v>122490448</v>
       </c>
       <c r="B8" t="n">
-        <v>106145</v>
+        <v>106148</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729247</v>
+        <v>729134</v>
       </c>
       <c r="R8" t="n">
-        <v>6367747</v>
+        <v>6367511</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkglänta</t>
+          <t>Glänta</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
         <v>122490446</v>
       </c>
       <c r="B9" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490429</v>
+        <v>122490424</v>
       </c>
       <c r="B2" t="n">
-        <v>98222</v>
+        <v>103770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>220164</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -729,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729301</v>
+        <v>729247</v>
       </c>
       <c r="R2" t="n">
-        <v>6367596</v>
+        <v>6367747</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490430</v>
+        <v>122490446</v>
       </c>
       <c r="B3" t="n">
-        <v>98222</v>
+        <v>100510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,48 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729303</v>
+        <v>729149</v>
       </c>
       <c r="R3" t="n">
-        <v>6367559</v>
+        <v>6367526</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
+          <t>Vid gamla stenbrott.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1019,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490424</v>
+        <v>122490425</v>
       </c>
       <c r="B5" t="n">
-        <v>103770</v>
+        <v>106148</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1131,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490425</v>
+        <v>122490429</v>
       </c>
       <c r="B6" t="n">
-        <v>106148</v>
+        <v>98222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,28 +1125,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1176,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729247</v>
+        <v>729301</v>
       </c>
       <c r="R6" t="n">
-        <v>6367747</v>
+        <v>6367596</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,11 +1213,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1355,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490448</v>
+        <v>122490430</v>
       </c>
       <c r="B8" t="n">
-        <v>106148</v>
+        <v>98222</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,28 +1353,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1400,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729134</v>
+        <v>729303</v>
       </c>
       <c r="R8" t="n">
-        <v>6367511</v>
+        <v>6367559</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,6 +1433,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1446,11 +1446,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1467,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490446</v>
+        <v>122490448</v>
       </c>
       <c r="B9" t="n">
-        <v>100510</v>
+        <v>106148</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,38 +1474,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221903</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729149</v>
+        <v>729134</v>
       </c>
       <c r="R9" t="n">
-        <v>6367526</v>
+        <v>6367511</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1545,11 +1545,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1558,6 +1553,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490430</v>
+        <v>122490448</v>
       </c>
       <c r="B8" t="n">
-        <v>98222</v>
+        <v>106148</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,37 +1353,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1395,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729303</v>
+        <v>729134</v>
       </c>
       <c r="R8" t="n">
-        <v>6367559</v>
+        <v>6367511</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,11 +1424,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1446,6 +1432,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1462,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490448</v>
+        <v>122490430</v>
       </c>
       <c r="B9" t="n">
-        <v>106148</v>
+        <v>98222</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,28 +1465,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729134</v>
+        <v>729303</v>
       </c>
       <c r="R9" t="n">
-        <v>6367511</v>
+        <v>6367559</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1545,6 +1545,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1553,11 +1558,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490448</v>
+        <v>122490430</v>
       </c>
       <c r="B8" t="n">
-        <v>106148</v>
+        <v>98222</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,28 +1353,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1386,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729134</v>
+        <v>729303</v>
       </c>
       <c r="R8" t="n">
-        <v>6367511</v>
+        <v>6367559</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,6 +1433,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1432,11 +1446,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1453,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490430</v>
+        <v>122490448</v>
       </c>
       <c r="B9" t="n">
-        <v>98222</v>
+        <v>106148</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,37 +1474,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729303</v>
+        <v>729134</v>
       </c>
       <c r="R9" t="n">
-        <v>6367559</v>
+        <v>6367511</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1545,11 +1545,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1558,6 +1553,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490424</v>
+        <v>122490446</v>
       </c>
       <c r="B2" t="n">
-        <v>103770</v>
+        <v>100613</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220164</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729247</v>
+        <v>729149</v>
       </c>
       <c r="R2" t="n">
-        <v>6367747</v>
+        <v>6367526</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,6 +753,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vid gamla stenbrott.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490446</v>
+        <v>122490429</v>
       </c>
       <c r="B3" t="n">
-        <v>100510</v>
+        <v>98325</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +798,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729149</v>
+        <v>729301</v>
       </c>
       <c r="R3" t="n">
-        <v>6367526</v>
+        <v>6367596</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,11 +872,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490411</v>
+        <v>122490425</v>
       </c>
       <c r="B4" t="n">
-        <v>106148</v>
+        <v>106251</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729160</v>
+        <v>729247</v>
       </c>
       <c r="R4" t="n">
-        <v>6367602</v>
+        <v>6367747</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,6 +989,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490425</v>
+        <v>122490448</v>
       </c>
       <c r="B5" t="n">
-        <v>106148</v>
+        <v>106251</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729247</v>
+        <v>729134</v>
       </c>
       <c r="R5" t="n">
-        <v>6367747</v>
+        <v>6367511</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1104,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkglänta</t>
+          <t>Glänta</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1113,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490429</v>
+        <v>122490442</v>
       </c>
       <c r="B6" t="n">
-        <v>98222</v>
+        <v>106251</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,37 +1134,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729301</v>
+        <v>729269</v>
       </c>
       <c r="R6" t="n">
-        <v>6367596</v>
+        <v>6367497</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,6 +1203,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490442</v>
+        <v>122490411</v>
       </c>
       <c r="B7" t="n">
-        <v>106148</v>
+        <v>106251</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729269</v>
+        <v>729160</v>
       </c>
       <c r="R7" t="n">
-        <v>6367497</v>
+        <v>6367602</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,11 +1315,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490430</v>
+        <v>122490424</v>
       </c>
       <c r="B8" t="n">
-        <v>98222</v>
+        <v>103873</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,37 +1353,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220164</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1395,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729303</v>
+        <v>729247</v>
       </c>
       <c r="R8" t="n">
-        <v>6367559</v>
+        <v>6367747</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,11 +1424,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1446,6 +1432,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1462,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490448</v>
+        <v>122490430</v>
       </c>
       <c r="B9" t="n">
-        <v>106148</v>
+        <v>98325</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,28 +1465,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729134</v>
+        <v>729303</v>
       </c>
       <c r="R9" t="n">
-        <v>6367511</v>
+        <v>6367559</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1545,6 +1545,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1553,11 +1558,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1577,7 +1577,7 @@
         <v>122497899</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490446</v>
+        <v>122490425</v>
       </c>
       <c r="B2" t="n">
-        <v>100613</v>
+        <v>106259</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221903</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729149</v>
+        <v>729247</v>
       </c>
       <c r="R2" t="n">
-        <v>6367526</v>
+        <v>6367747</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,11 +758,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490429</v>
+        <v>122490442</v>
       </c>
       <c r="B3" t="n">
-        <v>98325</v>
+        <v>106259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,37 +799,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -836,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729301</v>
+        <v>729269</v>
       </c>
       <c r="R3" t="n">
-        <v>6367596</v>
+        <v>6367497</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490425</v>
+        <v>122490411</v>
       </c>
       <c r="B4" t="n">
-        <v>106251</v>
+        <v>106259</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729247</v>
+        <v>729160</v>
       </c>
       <c r="R4" t="n">
-        <v>6367747</v>
+        <v>6367602</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,11 +990,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1010,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490448</v>
+        <v>122490424</v>
       </c>
       <c r="B5" t="n">
-        <v>106251</v>
+        <v>103881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729134</v>
+        <v>729247</v>
       </c>
       <c r="R5" t="n">
-        <v>6367511</v>
+        <v>6367747</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1100,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Glänta</t>
+          <t>Kalkglänta</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1122,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490442</v>
+        <v>122490448</v>
       </c>
       <c r="B6" t="n">
-        <v>106251</v>
+        <v>106259</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729269</v>
+        <v>729134</v>
       </c>
       <c r="R6" t="n">
-        <v>6367497</v>
+        <v>6367511</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,11 +1201,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1218,6 +1209,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1234,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490411</v>
+        <v>122490430</v>
       </c>
       <c r="B7" t="n">
-        <v>106251</v>
+        <v>98333</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,28 +1242,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1279,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729160</v>
+        <v>729303</v>
       </c>
       <c r="R7" t="n">
-        <v>6367602</v>
+        <v>6367559</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,6 +1320,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490424</v>
+        <v>122490446</v>
       </c>
       <c r="B8" t="n">
-        <v>103873</v>
+        <v>100621</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,43 +1363,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220164</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729247</v>
+        <v>729149</v>
       </c>
       <c r="R8" t="n">
-        <v>6367747</v>
+        <v>6367526</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,6 +1429,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid gamla stenbrott.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1432,11 +1442,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1453,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490430</v>
+        <v>122490429</v>
       </c>
       <c r="B9" t="n">
-        <v>98325</v>
+        <v>98333</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,7 +1493,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1507,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729303</v>
+        <v>729301</v>
       </c>
       <c r="R9" t="n">
-        <v>6367559</v>
+        <v>6367596</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1543,11 +1548,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490425</v>
+        <v>122490429</v>
       </c>
       <c r="B2" t="n">
-        <v>106259</v>
+        <v>98333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -720,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729247</v>
+        <v>729301</v>
       </c>
       <c r="R2" t="n">
-        <v>6367747</v>
+        <v>6367596</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -766,11 +775,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122490411</v>
+        <v>122490424</v>
       </c>
       <c r="B4" t="n">
-        <v>106259</v>
+        <v>103881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729160</v>
+        <v>729247</v>
       </c>
       <c r="R4" t="n">
-        <v>6367602</v>
+        <v>6367747</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,6 +994,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490424</v>
+        <v>122490425</v>
       </c>
       <c r="B5" t="n">
-        <v>103881</v>
+        <v>106259</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1118,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490448</v>
+        <v>122490430</v>
       </c>
       <c r="B6" t="n">
-        <v>106259</v>
+        <v>98333</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,28 +1139,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1163,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729134</v>
+        <v>729303</v>
       </c>
       <c r="R6" t="n">
-        <v>6367511</v>
+        <v>6367559</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,6 +1219,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1209,11 +1232,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122490430</v>
+        <v>122490446</v>
       </c>
       <c r="B7" t="n">
-        <v>98333</v>
+        <v>100621</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,48 +1264,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729303</v>
+        <v>729149</v>
       </c>
       <c r="R7" t="n">
-        <v>6367559</v>
+        <v>6367526</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,7 +1328,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
+          <t>Vid gamla stenbrott.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490446</v>
+        <v>122490448</v>
       </c>
       <c r="B8" t="n">
-        <v>100621</v>
+        <v>106259</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,38 +1367,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>221903</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gammelgarn, Skogby 1:16 2, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729149</v>
+        <v>729134</v>
       </c>
       <c r="R8" t="n">
-        <v>6367526</v>
+        <v>6367511</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1429,11 +1438,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Vid gamla stenbrott.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1442,6 +1446,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1458,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490429</v>
+        <v>122490411</v>
       </c>
       <c r="B9" t="n">
-        <v>98333</v>
+        <v>106259</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,37 +1479,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729301</v>
+        <v>729160</v>
       </c>
       <c r="R9" t="n">
-        <v>6367596</v>
+        <v>6367602</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122490429</v>
+        <v>122490442</v>
       </c>
       <c r="B2" t="n">
-        <v>98333</v>
+        <v>106261</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -729,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729301</v>
+        <v>729269</v>
       </c>
       <c r="R2" t="n">
-        <v>6367596</v>
+        <v>6367497</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122490442</v>
+        <v>122490411</v>
       </c>
       <c r="B3" t="n">
-        <v>106259</v>
+        <v>106261</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729269</v>
+        <v>729160</v>
       </c>
       <c r="R3" t="n">
-        <v>6367497</v>
+        <v>6367602</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,11 +868,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kalkglänta med karst, ca 60 x 40 m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +897,7 @@
         <v>122490424</v>
       </c>
       <c r="B4" t="n">
-        <v>103881</v>
+        <v>103883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1015,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122490425</v>
+        <v>122490429</v>
       </c>
       <c r="B5" t="n">
-        <v>106259</v>
+        <v>98335</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,28 +1018,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729247</v>
+        <v>729301</v>
       </c>
       <c r="R5" t="n">
-        <v>6367747</v>
+        <v>6367596</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,11 +1106,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkglänta</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1127,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122490430</v>
+        <v>122490448</v>
       </c>
       <c r="B6" t="n">
-        <v>98333</v>
+        <v>106261</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1134,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1181,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729303</v>
+        <v>729134</v>
       </c>
       <c r="R6" t="n">
-        <v>6367559</v>
+        <v>6367511</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,11 +1205,6 @@
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>10 m norrut finns ett kalkbrott.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1232,6 +1213,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1251,7 +1237,7 @@
         <v>122490446</v>
       </c>
       <c r="B7" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1355,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122490448</v>
+        <v>122490430</v>
       </c>
       <c r="B8" t="n">
-        <v>106259</v>
+        <v>98335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,28 +1353,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1400,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729134</v>
+        <v>729303</v>
       </c>
       <c r="R8" t="n">
-        <v>6367511</v>
+        <v>6367559</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,6 +1433,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>10 m norrut finns ett kalkbrott.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1446,11 +1446,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1467,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122490411</v>
+        <v>122490425</v>
       </c>
       <c r="B9" t="n">
-        <v>106259</v>
+        <v>106261</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729160</v>
+        <v>729247</v>
       </c>
       <c r="R9" t="n">
-        <v>6367602</v>
+        <v>6367747</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,6 +1553,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkglänta</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1796,6 +1796,135 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125824452</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>729207</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6367867</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2-3 meter från stigen.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Thomas Sjölund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Thomas Sjölund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>125824452</v>
       </c>
       <c r="B12" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126742589</v>
+        <v>126741435</v>
       </c>
       <c r="B13" t="n">
-        <v>98339</v>
+        <v>98473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,51 +1938,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>219875</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729176</v>
+        <v>729127</v>
       </c>
       <c r="R13" t="n">
-        <v>6367837</v>
+        <v>6367535</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126741435</v>
+        <v>126742589</v>
       </c>
       <c r="B14" t="n">
-        <v>98398</v>
+        <v>98414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,37 +2045,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219875</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729127</v>
+        <v>729176</v>
       </c>
       <c r="R14" t="n">
-        <v>6367535</v>
+        <v>6367837</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2265,7 +2265,7 @@
         <v>126742664</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>126741494</v>
       </c>
       <c r="B17" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>126741666</v>
       </c>
       <c r="B19" t="n">
-        <v>106200</v>
+        <v>106275</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>126742636</v>
       </c>
       <c r="B20" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>126781871</v>
       </c>
       <c r="B21" t="n">
-        <v>106654</v>
+        <v>106729</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>126781687</v>
       </c>
       <c r="B22" t="n">
-        <v>106200</v>
+        <v>106275</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>126780936</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>126802494</v>
       </c>
       <c r="B24" t="n">
-        <v>98336</v>
+        <v>98411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>127130221</v>
       </c>
       <c r="B25" t="n">
-        <v>106654</v>
+        <v>106729</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127130367</v>
+        <v>127130451</v>
       </c>
       <c r="B26" t="n">
-        <v>106200</v>
+        <v>106275</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3508,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127130319</v>
+        <v>127130573</v>
       </c>
       <c r="B27" t="n">
-        <v>106654</v>
+        <v>106275</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729262</v>
+        <v>729249</v>
       </c>
       <c r="R27" t="n">
-        <v>6367815</v>
+        <v>6367774</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127130573</v>
+        <v>127130319</v>
       </c>
       <c r="B28" t="n">
-        <v>106200</v>
+        <v>106729</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729249</v>
+        <v>729262</v>
       </c>
       <c r="R28" t="n">
-        <v>6367774</v>
+        <v>6367815</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3839,6 +3839,883 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127270256</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>729161</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6367508</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Thomas Sjölund</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Thomas Sjölund</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127269410</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98439</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223614</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vanlig brudsporre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>729161</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6367508</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Thomas Sjölund</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Thomas Sjölund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127296658</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>729131</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6367570</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Tallåga med födoskshål efte spillkråka.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127295470</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107318</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2025, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>729131</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6367570</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127295468</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106275</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>729154</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6367594</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Alvar, igenväxande med buskar..</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127296627</v>
+      </c>
+      <c r="B35" t="n">
+        <v>43059</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>729154</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6367594</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127295456</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>729163</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6367820</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127295467</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>729154</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6367594</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Alvar, igenväxande med buskar..</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1930,7 +1930,7 @@
         <v>126741435</v>
       </c>
       <c r="B13" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>126742589</v>
       </c>
       <c r="B14" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>126742664</v>
       </c>
       <c r="B16" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>126741494</v>
       </c>
       <c r="B17" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>126741666</v>
       </c>
       <c r="B19" t="n">
-        <v>106275</v>
+        <v>106281</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>126742636</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>126781871</v>
       </c>
       <c r="B21" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>126781687</v>
       </c>
       <c r="B22" t="n">
-        <v>106275</v>
+        <v>106281</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>126780936</v>
       </c>
       <c r="B23" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>126802494</v>
       </c>
       <c r="B24" t="n">
-        <v>98411</v>
+        <v>98417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>127130221</v>
       </c>
       <c r="B25" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>127130451</v>
       </c>
       <c r="B26" t="n">
-        <v>106275</v>
+        <v>106281</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127130573</v>
+        <v>127130319</v>
       </c>
       <c r="B27" t="n">
-        <v>106275</v>
+        <v>106735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729249</v>
+        <v>729262</v>
       </c>
       <c r="R27" t="n">
-        <v>6367774</v>
+        <v>6367815</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127130319</v>
+        <v>127130573</v>
       </c>
       <c r="B28" t="n">
-        <v>106729</v>
+        <v>106281</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729262</v>
+        <v>729249</v>
       </c>
       <c r="R28" t="n">
-        <v>6367815</v>
+        <v>6367774</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3844,7 +3844,7 @@
         <v>127270256</v>
       </c>
       <c r="B30" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127269410</v>
       </c>
       <c r="B31" t="n">
-        <v>98439</v>
+        <v>98445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106275</v>
+        <v>106281</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>127295456</v>
       </c>
       <c r="B36" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,6 +4715,113 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127311062</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6367544</v>
+      </c>
+      <c r="S38" t="n">
+        <v>50</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Lisa Wallström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Lisa Wallström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4384,67 +4384,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127296627</v>
+        <v>127295456</v>
       </c>
       <c r="B35" t="n">
-        <v>43059</v>
+        <v>98420</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729154</v>
+        <v>729163</v>
       </c>
       <c r="R35" t="n">
-        <v>6367594</v>
+        <v>6367820</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4487,7 +4477,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4505,57 +4495,67 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295456</v>
+        <v>127296627</v>
       </c>
       <c r="B36" t="n">
-        <v>98420</v>
+        <v>43059</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729163</v>
+        <v>729154</v>
       </c>
       <c r="R36" t="n">
-        <v>6367820</v>
+        <v>6367594</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1930,7 +1930,7 @@
         <v>126741435</v>
       </c>
       <c r="B13" t="n">
-        <v>98479</v>
+        <v>98480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>126742589</v>
       </c>
       <c r="B14" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>126742664</v>
       </c>
       <c r="B16" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>126741494</v>
       </c>
       <c r="B17" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>126741666</v>
       </c>
       <c r="B19" t="n">
-        <v>106281</v>
+        <v>106282</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>126742636</v>
       </c>
       <c r="B20" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>126781871</v>
       </c>
       <c r="B21" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>126781687</v>
       </c>
       <c r="B22" t="n">
-        <v>106281</v>
+        <v>106282</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>126780936</v>
       </c>
       <c r="B23" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>126802494</v>
       </c>
       <c r="B24" t="n">
-        <v>98417</v>
+        <v>98418</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>127130221</v>
       </c>
       <c r="B25" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>127130451</v>
       </c>
       <c r="B26" t="n">
-        <v>106281</v>
+        <v>106282</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>127130319</v>
       </c>
       <c r="B27" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>127130573</v>
       </c>
       <c r="B28" t="n">
-        <v>106281</v>
+        <v>106282</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>127270256</v>
       </c>
       <c r="B30" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127269410</v>
       </c>
       <c r="B31" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106281</v>
+        <v>106282</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,57 +4384,67 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295456</v>
+        <v>127296627</v>
       </c>
       <c r="B35" t="n">
-        <v>98420</v>
+        <v>43059</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729163</v>
+        <v>729154</v>
       </c>
       <c r="R35" t="n">
-        <v>6367820</v>
+        <v>6367594</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4477,7 +4487,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4495,67 +4505,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296627</v>
+        <v>127295456</v>
       </c>
       <c r="B36" t="n">
-        <v>43059</v>
+        <v>98421</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729154</v>
+        <v>729163</v>
       </c>
       <c r="R36" t="n">
-        <v>6367594</v>
+        <v>6367820</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4384,67 +4384,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127296627</v>
+        <v>127295456</v>
       </c>
       <c r="B35" t="n">
-        <v>43059</v>
+        <v>98421</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729154</v>
+        <v>729163</v>
       </c>
       <c r="R35" t="n">
-        <v>6367594</v>
+        <v>6367820</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4487,7 +4477,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4505,57 +4495,67 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295456</v>
+        <v>127296627</v>
       </c>
       <c r="B36" t="n">
-        <v>98421</v>
+        <v>43059</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729163</v>
+        <v>729154</v>
       </c>
       <c r="R36" t="n">
-        <v>6367820</v>
+        <v>6367594</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126741435</v>
+        <v>126742589</v>
       </c>
       <c r="B13" t="n">
-        <v>98480</v>
+        <v>98425</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,37 +1938,51 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219875</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729127</v>
+        <v>729176</v>
       </c>
       <c r="R13" t="n">
-        <v>6367535</v>
+        <v>6367837</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126742589</v>
+        <v>126741435</v>
       </c>
       <c r="B14" t="n">
-        <v>98421</v>
+        <v>98484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,51 +2059,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>219875</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729176</v>
+        <v>729127</v>
       </c>
       <c r="R14" t="n">
-        <v>6367837</v>
+        <v>6367535</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,7 +2158,7 @@
         <v>126742905</v>
       </c>
       <c r="B15" t="n">
-        <v>43278</v>
+        <v>43282</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>126742664</v>
       </c>
       <c r="B16" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>126741494</v>
       </c>
       <c r="B17" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>126741575</v>
       </c>
       <c r="B18" t="n">
-        <v>43059</v>
+        <v>43063</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>126741666</v>
       </c>
       <c r="B19" t="n">
-        <v>106282</v>
+        <v>106288</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>126742636</v>
       </c>
       <c r="B20" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>126781871</v>
       </c>
       <c r="B21" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>126781687</v>
       </c>
       <c r="B22" t="n">
-        <v>106282</v>
+        <v>106288</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>126780936</v>
       </c>
       <c r="B23" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>126802494</v>
       </c>
       <c r="B24" t="n">
-        <v>98418</v>
+        <v>98422</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>127130221</v>
       </c>
       <c r="B25" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>127130451</v>
       </c>
       <c r="B26" t="n">
-        <v>106282</v>
+        <v>106288</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127130319</v>
+        <v>127130573</v>
       </c>
       <c r="B27" t="n">
-        <v>106736</v>
+        <v>106288</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729262</v>
+        <v>729249</v>
       </c>
       <c r="R27" t="n">
-        <v>6367815</v>
+        <v>6367774</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127130573</v>
+        <v>127130319</v>
       </c>
       <c r="B28" t="n">
-        <v>106282</v>
+        <v>106742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729249</v>
+        <v>729262</v>
       </c>
       <c r="R28" t="n">
-        <v>6367774</v>
+        <v>6367815</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,7 +3743,7 @@
         <v>127167228</v>
       </c>
       <c r="B29" t="n">
-        <v>57603</v>
+        <v>57607</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>127270256</v>
       </c>
       <c r="B30" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127269410</v>
       </c>
       <c r="B31" t="n">
-        <v>98446</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>127296658</v>
       </c>
       <c r="B32" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106282</v>
+        <v>106288</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,57 +4384,67 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295456</v>
+        <v>127296627</v>
       </c>
       <c r="B35" t="n">
-        <v>98421</v>
+        <v>43063</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729163</v>
+        <v>729154</v>
       </c>
       <c r="R35" t="n">
-        <v>6367820</v>
+        <v>6367594</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4477,7 +4487,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4495,67 +4505,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296627</v>
+        <v>127295456</v>
       </c>
       <c r="B36" t="n">
-        <v>43059</v>
+        <v>98425</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729154</v>
+        <v>729163</v>
       </c>
       <c r="R36" t="n">
-        <v>6367594</v>
+        <v>6367820</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>127311062</v>
       </c>
       <c r="B38" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -3508,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127130573</v>
+        <v>127130319</v>
       </c>
       <c r="B27" t="n">
-        <v>106288</v>
+        <v>106742</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729249</v>
+        <v>729262</v>
       </c>
       <c r="R27" t="n">
-        <v>6367774</v>
+        <v>6367815</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127130319</v>
+        <v>127130573</v>
       </c>
       <c r="B28" t="n">
-        <v>106742</v>
+        <v>106288</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729262</v>
+        <v>729249</v>
       </c>
       <c r="R28" t="n">
-        <v>6367815</v>
+        <v>6367774</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4384,67 +4384,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127296627</v>
+        <v>127295456</v>
       </c>
       <c r="B35" t="n">
-        <v>43063</v>
+        <v>98425</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729154</v>
+        <v>729163</v>
       </c>
       <c r="R35" t="n">
-        <v>6367594</v>
+        <v>6367820</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4487,7 +4477,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4505,57 +4495,67 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295456</v>
+        <v>127296627</v>
       </c>
       <c r="B36" t="n">
-        <v>98425</v>
+        <v>43063</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729163</v>
+        <v>729154</v>
       </c>
       <c r="R36" t="n">
-        <v>6367820</v>
+        <v>6367594</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -3279,7 +3279,7 @@
         <v>127130221</v>
       </c>
       <c r="B25" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>127130451</v>
       </c>
       <c r="B26" t="n">
-        <v>106288</v>
+        <v>106290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127130319</v>
+        <v>127130573</v>
       </c>
       <c r="B27" t="n">
-        <v>106742</v>
+        <v>106290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729262</v>
+        <v>729249</v>
       </c>
       <c r="R27" t="n">
-        <v>6367815</v>
+        <v>6367774</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127130573</v>
+        <v>127130319</v>
       </c>
       <c r="B28" t="n">
-        <v>106288</v>
+        <v>106744</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729249</v>
+        <v>729262</v>
       </c>
       <c r="R28" t="n">
-        <v>6367774</v>
+        <v>6367815</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3844,7 +3844,7 @@
         <v>127270256</v>
       </c>
       <c r="B30" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127269410</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106288</v>
+        <v>106290</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,57 +4384,67 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295456</v>
+        <v>127296627</v>
       </c>
       <c r="B35" t="n">
-        <v>98425</v>
+        <v>43063</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729163</v>
+        <v>729154</v>
       </c>
       <c r="R35" t="n">
-        <v>6367820</v>
+        <v>6367594</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4477,7 +4487,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4495,67 +4505,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296627</v>
+        <v>127295456</v>
       </c>
       <c r="B36" t="n">
-        <v>43063</v>
+        <v>98426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729154</v>
+        <v>729163</v>
       </c>
       <c r="R36" t="n">
-        <v>6367594</v>
+        <v>6367820</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -3508,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127130573</v>
+        <v>127130319</v>
       </c>
       <c r="B27" t="n">
-        <v>106290</v>
+        <v>106744</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729249</v>
+        <v>729262</v>
       </c>
       <c r="R27" t="n">
-        <v>6367774</v>
+        <v>6367815</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127130319</v>
+        <v>127130573</v>
       </c>
       <c r="B28" t="n">
-        <v>106744</v>
+        <v>106290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729262</v>
+        <v>729249</v>
       </c>
       <c r="R28" t="n">
-        <v>6367815</v>
+        <v>6367774</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -3279,7 +3279,7 @@
         <v>127130221</v>
       </c>
       <c r="B25" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>127130451</v>
       </c>
       <c r="B26" t="n">
-        <v>106290</v>
+        <v>106292</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127130319</v>
+        <v>127130573</v>
       </c>
       <c r="B27" t="n">
-        <v>106744</v>
+        <v>106292</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729262</v>
+        <v>729249</v>
       </c>
       <c r="R27" t="n">
-        <v>6367815</v>
+        <v>6367774</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127130573</v>
+        <v>127130319</v>
       </c>
       <c r="B28" t="n">
-        <v>106290</v>
+        <v>106746</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729249</v>
+        <v>729262</v>
       </c>
       <c r="R28" t="n">
-        <v>6367774</v>
+        <v>6367815</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,7 +3743,7 @@
         <v>127167228</v>
       </c>
       <c r="B29" t="n">
-        <v>57607</v>
+        <v>57609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>127270256</v>
       </c>
       <c r="B30" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127269410</v>
       </c>
       <c r="B31" t="n">
-        <v>98451</v>
+        <v>98453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>127296658</v>
       </c>
       <c r="B32" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106290</v>
+        <v>106292</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127296627</v>
       </c>
       <c r="B35" t="n">
-        <v>43063</v>
+        <v>43065</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>127295456</v>
       </c>
       <c r="B36" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>127311062</v>
       </c>
       <c r="B38" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -3508,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127130573</v>
+        <v>127130319</v>
       </c>
       <c r="B27" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729249</v>
+        <v>729262</v>
       </c>
       <c r="R27" t="n">
-        <v>6367774</v>
+        <v>6367815</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127130319</v>
+        <v>127130573</v>
       </c>
       <c r="B28" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729262</v>
+        <v>729249</v>
       </c>
       <c r="R28" t="n">
-        <v>6367815</v>
+        <v>6367774</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4823,6 +4823,8388 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127771932</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>729269</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6367727</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127771574</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>729271</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6367489</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127771431</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>729197</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6367641</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Alvarglänta med karstsprickor.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127771423</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>729206</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6367643</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Röjd skog mot O.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127771437</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>729159</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6367602</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Alvarglänta med karstsprickor.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127771363</v>
+      </c>
+      <c r="B44" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>729296</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6367803</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Vid gräns mot Klints 1:9.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127771857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5493</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6367746</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tall med angrepp.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127771381</v>
+      </c>
+      <c r="B46" t="n">
+        <v>107335</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>729236</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6367761</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127771573</v>
+      </c>
+      <c r="B47" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>729265</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6367490</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127771608</v>
+      </c>
+      <c r="B48" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>729267</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6367464</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127771367</v>
+      </c>
+      <c r="B49" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>729279</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6367813</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127771570</v>
+      </c>
+      <c r="B50" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>729262</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6367486</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127771405</v>
+      </c>
+      <c r="B51" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>729259</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6367748</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127771419</v>
+      </c>
+      <c r="B52" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>729198</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6367656</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Alvarglänta med karstsprickor.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127771460</v>
+      </c>
+      <c r="B53" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>729130</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6367518</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Alvarglänta, kalkhäll.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127771410</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98428</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>729272</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6367702</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127771552</v>
+      </c>
+      <c r="B55" t="n">
+        <v>107335</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>729282</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6367498</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127771421</v>
+      </c>
+      <c r="B56" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>729214</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6367664</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127771565</v>
+      </c>
+      <c r="B57" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>729264</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6367501</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127771933</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>729149</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6367526</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127771440</v>
+      </c>
+      <c r="B59" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>729123</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6367520</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Alvarglänta.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127771415</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>729205</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6367685</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Alvarglänta med karstsprickor.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127771386</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>729222</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6367752</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127771390</v>
+      </c>
+      <c r="B62" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>729230</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6367743</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127771935</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>729189</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6367526</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre bo i nu fallen död tall.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127771559</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>729273</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6367508</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127771397</v>
+      </c>
+      <c r="B65" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>729249</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6367746</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127771463</v>
+      </c>
+      <c r="B66" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>729143</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6367517</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Alvarglänta.</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127771371</v>
+      </c>
+      <c r="B67" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>729244</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6367780</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127771605</v>
+      </c>
+      <c r="B68" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>729264</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6367467</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127771401</v>
+      </c>
+      <c r="B69" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>729249</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6367753</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127771593</v>
+      </c>
+      <c r="B70" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>729273</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6367480</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127771387</v>
+      </c>
+      <c r="B71" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>729222</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6367752</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127771588</v>
+      </c>
+      <c r="B72" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>729260</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6367474</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127771590</v>
+      </c>
+      <c r="B73" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6367477</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127771564</v>
+      </c>
+      <c r="B74" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>729264</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6367501</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127771416</v>
+      </c>
+      <c r="B75" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>729198</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6367656</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Alvarglänta med karstsprickor.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127771562</v>
+      </c>
+      <c r="B76" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>729266</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6367511</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127771382</v>
+      </c>
+      <c r="B77" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>729236</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6367761</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127771568</v>
+      </c>
+      <c r="B78" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>729259</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6367495</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127771450</v>
+      </c>
+      <c r="B79" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>729150</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6367499</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Stenbrottskant?</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Alvarglänta, kalkhäll.</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127771366</v>
+      </c>
+      <c r="B80" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>729279</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6367813</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127771586</v>
+      </c>
+      <c r="B81" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>729260</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6367485</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127771392</v>
+      </c>
+      <c r="B82" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>729237</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6367741</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127771931</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6367746</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127771375</v>
+      </c>
+      <c r="B84" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>729236</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6367778</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127771584</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>729267</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6367487</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127771581</v>
+      </c>
+      <c r="B86" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>729272</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6367485</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127771393</v>
+      </c>
+      <c r="B87" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>729237</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6367741</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127771466</v>
+      </c>
+      <c r="B88" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>729154</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6367521</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog , vid stig.</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127771575</v>
+      </c>
+      <c r="B89" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>729271</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6367489</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127771930</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57676</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>729246</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6367767</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127771383</v>
+      </c>
+      <c r="B91" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>729236</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6367761</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127771556</v>
+      </c>
+      <c r="B92" t="n">
+        <v>103906</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>729273</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6367508</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127771578</v>
+      </c>
+      <c r="B93" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>729275</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6367487</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127771365</v>
+      </c>
+      <c r="B94" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>729296</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6367803</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Vid gräns mot Klints 1:9.</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127771379</v>
+      </c>
+      <c r="B95" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>729229</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6367768</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127771429</v>
+      </c>
+      <c r="B96" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>729197</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6367641</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Alvarglänta med karstsprickor.</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127771461</v>
+      </c>
+      <c r="B97" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>729130</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6367518</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Alvarglänta, kalkhäll.</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127771607</v>
+      </c>
+      <c r="B98" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>729264</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6367467</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127771929</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>729237</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6367741</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Födosöksspår i död tallåga med mycket rikligt med utgångshål för insekter.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127771604</v>
+      </c>
+      <c r="B100" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6367470</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127771412</v>
+      </c>
+      <c r="B101" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>729227</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6367700</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127771592</v>
+      </c>
+      <c r="B102" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>729273</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6367480</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>127771554</v>
+      </c>
+      <c r="B103" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>729277</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6367499</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>127771378</v>
+      </c>
+      <c r="B104" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>729229</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6367768</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>127771400</v>
+      </c>
+      <c r="B105" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>729243</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6367748</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>127771580</v>
+      </c>
+      <c r="B106" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>729272</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6367485</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>127771462</v>
+      </c>
+      <c r="B107" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>729143</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6367517</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Alvarglänta.</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>127771610</v>
+      </c>
+      <c r="B108" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>729267</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6367464</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>127771435</v>
+      </c>
+      <c r="B109" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>729159</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6367602</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Alvarglänta med karstsprickor.</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>127771389</v>
+      </c>
+      <c r="B110" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>729230</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6367743</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127771374</v>
+      </c>
+      <c r="B111" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>729236</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6367778</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>127771555</v>
+      </c>
+      <c r="B112" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>729277</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6367499</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127771577</v>
+      </c>
+      <c r="B113" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>729275</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6367487</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127771414</v>
+      </c>
+      <c r="B114" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>729205</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6367685</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Alvarglänta med karstsprickor.</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>127771458</v>
+      </c>
+      <c r="B115" t="n">
+        <v>103906</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>729130</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6367518</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>Alvarglänta, kalkhäll.</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>127771439</v>
+      </c>
+      <c r="B116" t="n">
+        <v>103906</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>729123</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6367520</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>Alvarglänta.</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>127771558</v>
+      </c>
+      <c r="B117" t="n">
+        <v>106292</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>729273</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6367508</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>127771396</v>
+      </c>
+      <c r="B118" t="n">
+        <v>106746</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>729249</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6367746</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>127771936</v>
+      </c>
+      <c r="B119" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>729289</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6367518</v>
+      </c>
+      <c r="S119" t="n">
+        <v>25</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4937,10 +4937,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127771574</v>
+        <v>127771423</v>
       </c>
       <c r="B40" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4948,16 +4948,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729271</v>
+        <v>729206</v>
       </c>
       <c r="R40" t="n">
-        <v>6367489</v>
+        <v>6367643</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,6 +5010,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Röjd skog mot O.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5021,7 +5026,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5039,10 +5044,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127771431</v>
+        <v>127771574</v>
       </c>
       <c r="B41" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5050,16 +5055,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5074,10 +5079,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729197</v>
+        <v>729271</v>
       </c>
       <c r="R41" t="n">
-        <v>6367641</v>
+        <v>6367489</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5123,7 +5128,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5141,7 +5146,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127771423</v>
+        <v>127771431</v>
       </c>
       <c r="B42" t="n">
         <v>106746</v>
@@ -5176,10 +5181,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729206</v>
+        <v>729197</v>
       </c>
       <c r="R42" t="n">
-        <v>6367643</v>
+        <v>6367641</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5214,11 +5219,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Röjd skog mot O.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5675,7 +5675,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127771573</v>
+        <v>127771570</v>
       </c>
       <c r="B47" t="n">
         <v>106292</v>
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729265</v>
+        <v>729262</v>
       </c>
       <c r="R47" t="n">
-        <v>6367490</v>
+        <v>6367486</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127771608</v>
+        <v>127771573</v>
       </c>
       <c r="B48" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5788,16 +5788,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729267</v>
+        <v>729265</v>
       </c>
       <c r="R48" t="n">
-        <v>6367464</v>
+        <v>6367490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5879,7 +5879,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127771367</v>
+        <v>127771405</v>
       </c>
       <c r="B49" t="n">
         <v>106292</v>
@@ -5914,13 +5914,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729279</v>
+        <v>729259</v>
       </c>
       <c r="R49" t="n">
-        <v>6367813</v>
+        <v>6367748</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127771570</v>
+        <v>127771608</v>
       </c>
       <c r="B50" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,16 +5992,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729262</v>
+        <v>729267</v>
       </c>
       <c r="R50" t="n">
-        <v>6367486</v>
+        <v>6367464</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127771405</v>
+        <v>127771419</v>
       </c>
       <c r="B51" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6094,16 +6094,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R51" t="n">
-        <v>6367748</v>
+        <v>6367656</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127771419</v>
+        <v>127771367</v>
       </c>
       <c r="B52" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6196,16 +6196,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6220,13 +6220,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729198</v>
+        <v>729279</v>
       </c>
       <c r="R52" t="n">
-        <v>6367656</v>
+        <v>6367813</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6389,54 +6389,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771410</v>
+        <v>127771421</v>
       </c>
       <c r="B54" t="n">
-        <v>98428</v>
+        <v>106746</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729272</v>
+        <v>729214</v>
       </c>
       <c r="R54" t="n">
-        <v>6367702</v>
+        <v>6367664</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6482,7 +6473,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6500,10 +6491,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771552</v>
+        <v>127771565</v>
       </c>
       <c r="B55" t="n">
-        <v>107335</v>
+        <v>106746</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6511,43 +6502,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729282</v>
+        <v>729264</v>
       </c>
       <c r="R55" t="n">
-        <v>6367498</v>
+        <v>6367501</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6611,45 +6593,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771421</v>
+        <v>127771410</v>
       </c>
       <c r="B56" t="n">
-        <v>106746</v>
+        <v>98428</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729214</v>
+        <v>729272</v>
       </c>
       <c r="R56" t="n">
-        <v>6367664</v>
+        <v>6367702</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6695,7 +6686,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6713,10 +6704,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771565</v>
+        <v>127771552</v>
       </c>
       <c r="B57" t="n">
-        <v>106746</v>
+        <v>107335</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6724,34 +6715,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729264</v>
+        <v>729282</v>
       </c>
       <c r="R57" t="n">
-        <v>6367501</v>
+        <v>6367498</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127771415</v>
+        <v>127771386</v>
       </c>
       <c r="B60" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7040,16 +7040,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>729205</v>
+        <v>729222</v>
       </c>
       <c r="R60" t="n">
-        <v>6367685</v>
+        <v>6367752</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127771386</v>
+        <v>127771415</v>
       </c>
       <c r="B61" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7142,16 +7142,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>729222</v>
+        <v>729205</v>
       </c>
       <c r="R61" t="n">
-        <v>6367752</v>
+        <v>6367685</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127771559</v>
+        <v>127771397</v>
       </c>
       <c r="B64" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7458,16 +7458,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>729273</v>
+        <v>729249</v>
       </c>
       <c r="R64" t="n">
-        <v>6367508</v>
+        <v>6367746</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127771397</v>
+        <v>127771463</v>
       </c>
       <c r="B65" t="n">
         <v>106292</v>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>729249</v>
+        <v>729143</v>
       </c>
       <c r="R65" t="n">
-        <v>6367746</v>
+        <v>6367517</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7651,10 +7651,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127771463</v>
+        <v>127771559</v>
       </c>
       <c r="B66" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>729143</v>
+        <v>729273</v>
       </c>
       <c r="R66" t="n">
-        <v>6367517</v>
+        <v>6367508</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7753,10 +7753,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127771371</v>
+        <v>127771605</v>
       </c>
       <c r="B67" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7764,16 +7764,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>729244</v>
+        <v>729264</v>
       </c>
       <c r="R67" t="n">
-        <v>6367780</v>
+        <v>6367467</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7855,10 +7855,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127771605</v>
+        <v>127771371</v>
       </c>
       <c r="B68" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>729264</v>
+        <v>729244</v>
       </c>
       <c r="R68" t="n">
-        <v>6367467</v>
+        <v>6367780</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127771401</v>
+        <v>127771593</v>
       </c>
       <c r="B69" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7968,16 +7968,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>729249</v>
+        <v>729273</v>
       </c>
       <c r="R69" t="n">
-        <v>6367753</v>
+        <v>6367480</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127771593</v>
+        <v>127771401</v>
       </c>
       <c r="B70" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8070,16 +8070,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>729273</v>
+        <v>729249</v>
       </c>
       <c r="R70" t="n">
-        <v>6367480</v>
+        <v>6367753</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8161,7 +8161,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127771387</v>
+        <v>127771588</v>
       </c>
       <c r="B71" t="n">
         <v>106292</v>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>729222</v>
+        <v>729260</v>
       </c>
       <c r="R71" t="n">
-        <v>6367752</v>
+        <v>6367474</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8263,7 +8263,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127771588</v>
+        <v>127771564</v>
       </c>
       <c r="B72" t="n">
         <v>106292</v>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>729260</v>
+        <v>729264</v>
       </c>
       <c r="R72" t="n">
-        <v>6367474</v>
+        <v>6367501</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8467,7 +8467,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127771564</v>
+        <v>127771387</v>
       </c>
       <c r="B74" t="n">
         <v>106292</v>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>729264</v>
+        <v>729222</v>
       </c>
       <c r="R74" t="n">
-        <v>6367501</v>
+        <v>6367752</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127771416</v>
+        <v>127771382</v>
       </c>
       <c r="B75" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8580,16 +8580,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729198</v>
+        <v>729236</v>
       </c>
       <c r="R75" t="n">
-        <v>6367656</v>
+        <v>6367761</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8671,7 +8671,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127771562</v>
+        <v>127771416</v>
       </c>
       <c r="B76" t="n">
         <v>106292</v>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>729266</v>
+        <v>729198</v>
       </c>
       <c r="R76" t="n">
-        <v>6367511</v>
+        <v>6367656</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8773,10 +8773,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127771382</v>
+        <v>127771562</v>
       </c>
       <c r="B77" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8784,16 +8784,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>729236</v>
+        <v>729266</v>
       </c>
       <c r="R77" t="n">
-        <v>6367761</v>
+        <v>6367511</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127771366</v>
+        <v>127771931</v>
       </c>
       <c r="B80" t="n">
-        <v>106746</v>
+        <v>57660</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9095,34 +9095,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729279</v>
+        <v>729268</v>
       </c>
       <c r="R80" t="n">
-        <v>6367813</v>
+        <v>6367746</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9157,6 +9162,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9168,7 +9178,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9288,7 +9298,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127771392</v>
+        <v>127771366</v>
       </c>
       <c r="B82" t="n">
         <v>106746</v>
@@ -9323,13 +9333,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729237</v>
+        <v>729279</v>
       </c>
       <c r="R82" t="n">
-        <v>6367741</v>
+        <v>6367813</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9372,7 +9382,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9390,10 +9400,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127771931</v>
+        <v>127771392</v>
       </c>
       <c r="B83" t="n">
-        <v>57660</v>
+        <v>106746</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9401,42 +9411,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>729268</v>
+        <v>729237</v>
       </c>
       <c r="R83" t="n">
-        <v>6367746</v>
+        <v>6367741</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9468,11 +9473,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9604,10 +9604,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127771584</v>
+        <v>127771575</v>
       </c>
       <c r="B85" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9615,16 +9615,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>729267</v>
+        <v>729271</v>
       </c>
       <c r="R85" t="n">
-        <v>6367487</v>
+        <v>6367489</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9808,7 +9808,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127771393</v>
+        <v>127771584</v>
       </c>
       <c r="B87" t="n">
         <v>106292</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>729237</v>
+        <v>729267</v>
       </c>
       <c r="R87" t="n">
-        <v>6367741</v>
+        <v>6367487</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127771575</v>
+        <v>127771393</v>
       </c>
       <c r="B89" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10023,16 +10023,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>729271</v>
+        <v>729237</v>
       </c>
       <c r="R89" t="n">
-        <v>6367489</v>
+        <v>6367741</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127771930</v>
+        <v>127771383</v>
       </c>
       <c r="B90" t="n">
-        <v>57676</v>
+        <v>106292</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10125,46 +10125,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100048</v>
+        <v>221903</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>729246</v>
+        <v>729236</v>
       </c>
       <c r="R90" t="n">
-        <v>6367767</v>
+        <v>6367761</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10207,7 +10198,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10225,10 +10216,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771383</v>
+        <v>127771556</v>
       </c>
       <c r="B91" t="n">
-        <v>106292</v>
+        <v>103906</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10236,21 +10227,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10260,10 +10251,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729236</v>
+        <v>729273</v>
       </c>
       <c r="R91" t="n">
-        <v>6367761</v>
+        <v>6367508</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10309,7 +10300,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10327,10 +10318,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127771556</v>
+        <v>127771930</v>
       </c>
       <c r="B92" t="n">
-        <v>103906</v>
+        <v>57676</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10338,37 +10329,46 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220164</v>
+        <v>100048</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>729273</v>
+        <v>729246</v>
       </c>
       <c r="R92" t="n">
-        <v>6367508</v>
+        <v>6367767</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10740,10 +10740,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127771429</v>
+        <v>127771929</v>
       </c>
       <c r="B96" t="n">
-        <v>106292</v>
+        <v>57660</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10751,34 +10751,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>729197</v>
+        <v>729237</v>
       </c>
       <c r="R96" t="n">
-        <v>6367641</v>
+        <v>6367741</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10813,6 +10818,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Födosöksspår i död tallåga med mycket rikligt med utgångshål för insekter.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10824,7 +10834,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -10842,7 +10852,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127771461</v>
+        <v>127771429</v>
       </c>
       <c r="B97" t="n">
         <v>106292</v>
@@ -10877,10 +10887,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>729130</v>
+        <v>729197</v>
       </c>
       <c r="R97" t="n">
-        <v>6367518</v>
+        <v>6367641</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10926,7 +10936,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11046,10 +11056,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127771929</v>
+        <v>127771461</v>
       </c>
       <c r="B99" t="n">
-        <v>57660</v>
+        <v>106292</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11057,39 +11067,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>729237</v>
+        <v>729130</v>
       </c>
       <c r="R99" t="n">
-        <v>6367741</v>
+        <v>6367518</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11124,11 +11129,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Födosöksspår i död tallåga med mycket rikligt med utgångshål för insekter.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11158,10 +11158,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127771604</v>
+        <v>127771378</v>
       </c>
       <c r="B100" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11169,16 +11169,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11193,10 +11193,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>729268</v>
+        <v>729229</v>
       </c>
       <c r="R100" t="n">
-        <v>6367470</v>
+        <v>6367768</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11362,7 +11362,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127771592</v>
+        <v>127771604</v>
       </c>
       <c r="B102" t="n">
         <v>106292</v>
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>729273</v>
+        <v>729268</v>
       </c>
       <c r="R102" t="n">
-        <v>6367480</v>
+        <v>6367470</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11566,10 +11566,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127771378</v>
+        <v>127771592</v>
       </c>
       <c r="B104" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11577,16 +11577,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11601,10 +11601,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>729229</v>
+        <v>729273</v>
       </c>
       <c r="R104" t="n">
-        <v>6367768</v>
+        <v>6367480</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -11668,7 +11668,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127771400</v>
+        <v>127771374</v>
       </c>
       <c r="B105" t="n">
         <v>106746</v>
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>729243</v>
+        <v>729236</v>
       </c>
       <c r="R105" t="n">
-        <v>6367748</v>
+        <v>6367778</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11770,10 +11770,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127771580</v>
+        <v>127771400</v>
       </c>
       <c r="B106" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11781,16 +11781,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>729272</v>
+        <v>729243</v>
       </c>
       <c r="R106" t="n">
-        <v>6367485</v>
+        <v>6367748</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12076,7 +12076,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127771435</v>
+        <v>127771580</v>
       </c>
       <c r="B109" t="n">
         <v>106292</v>
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>729159</v>
+        <v>729272</v>
       </c>
       <c r="R109" t="n">
-        <v>6367602</v>
+        <v>6367485</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127771389</v>
+        <v>127771435</v>
       </c>
       <c r="B110" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12189,16 +12189,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>729230</v>
+        <v>729159</v>
       </c>
       <c r="R110" t="n">
-        <v>6367743</v>
+        <v>6367602</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12280,7 +12280,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127771374</v>
+        <v>127771389</v>
       </c>
       <c r="B111" t="n">
         <v>106746</v>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>729236</v>
+        <v>729230</v>
       </c>
       <c r="R111" t="n">
-        <v>6367778</v>
+        <v>6367743</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771577</v>
+        <v>127771414</v>
       </c>
       <c r="B113" t="n">
-        <v>106292</v>
+        <v>106746</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12495,16 +12495,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12519,10 +12519,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729275</v>
+        <v>729205</v>
       </c>
       <c r="R113" t="n">
-        <v>6367487</v>
+        <v>6367685</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12586,10 +12586,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771414</v>
+        <v>127771558</v>
       </c>
       <c r="B114" t="n">
-        <v>106746</v>
+        <v>106292</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12597,16 +12597,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12621,10 +12621,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729205</v>
+        <v>729273</v>
       </c>
       <c r="R114" t="n">
-        <v>6367685</v>
+        <v>6367508</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12688,10 +12688,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771458</v>
+        <v>127771577</v>
       </c>
       <c r="B115" t="n">
-        <v>103906</v>
+        <v>106292</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12699,21 +12699,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729130</v>
+        <v>729275</v>
       </c>
       <c r="R115" t="n">
-        <v>6367518</v>
+        <v>6367487</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12772,7 +12772,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771439</v>
+        <v>127771396</v>
       </c>
       <c r="B116" t="n">
-        <v>103906</v>
+        <v>106746</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12801,21 +12801,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12825,10 +12825,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729123</v>
+        <v>729249</v>
       </c>
       <c r="R116" t="n">
-        <v>6367520</v>
+        <v>6367746</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12892,10 +12892,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771558</v>
+        <v>127771458</v>
       </c>
       <c r="B117" t="n">
-        <v>106292</v>
+        <v>103906</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12903,21 +12903,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12927,10 +12927,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729273</v>
+        <v>729130</v>
       </c>
       <c r="R117" t="n">
-        <v>6367508</v>
+        <v>6367518</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771396</v>
+        <v>127771936</v>
       </c>
       <c r="B118" t="n">
-        <v>106746</v>
+        <v>57660</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13005,37 +13005,46 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729249</v>
+        <v>729289</v>
       </c>
       <c r="R118" t="n">
-        <v>6367746</v>
+        <v>6367518</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13078,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13096,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771936</v>
+        <v>127771439</v>
       </c>
       <c r="B119" t="n">
-        <v>57660</v>
+        <v>103906</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13107,46 +13116,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>220164</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729289</v>
+        <v>729123</v>
       </c>
       <c r="R119" t="n">
-        <v>6367518</v>
+        <v>6367520</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -3279,7 +3279,7 @@
         <v>127130221</v>
       </c>
       <c r="B25" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>127130451</v>
       </c>
       <c r="B26" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>127130319</v>
       </c>
       <c r="B27" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>127130573</v>
       </c>
       <c r="B28" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>127270256</v>
       </c>
       <c r="B30" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127269410</v>
       </c>
       <c r="B31" t="n">
-        <v>98453</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>127295456</v>
       </c>
       <c r="B36" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>127771423</v>
       </c>
       <c r="B40" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>127771574</v>
       </c>
       <c r="B41" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>127771431</v>
       </c>
       <c r="B42" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127771437</v>
+        <v>127771857</v>
       </c>
       <c r="B43" t="n">
-        <v>106746</v>
+        <v>5493</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,21 +5259,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>101410</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729159</v>
+        <v>729268</v>
       </c>
       <c r="R43" t="n">
-        <v>6367602</v>
+        <v>6367746</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5321,6 +5321,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Tall med angrepp.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5332,7 +5337,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5350,10 +5355,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127771363</v>
+        <v>127771437</v>
       </c>
       <c r="B44" t="n">
-        <v>106292</v>
+        <v>106752</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5361,16 +5366,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5385,10 +5390,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>729296</v>
+        <v>729159</v>
       </c>
       <c r="R44" t="n">
-        <v>6367803</v>
+        <v>6367602</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5423,11 +5428,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Vid gräns mot Klints 1:9.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127771857</v>
+        <v>127771363</v>
       </c>
       <c r="B45" t="n">
-        <v>5493</v>
+        <v>106298</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5468,21 +5468,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101410</v>
+        <v>221903</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>729268</v>
+        <v>729296</v>
       </c>
       <c r="R45" t="n">
-        <v>6367746</v>
+        <v>6367803</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tall med angrepp.</t>
+          <t>Vid gräns mot Klints 1:9.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5567,7 +5567,7 @@
         <v>127771381</v>
       </c>
       <c r="B46" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127771570</v>
+        <v>127771608</v>
       </c>
       <c r="B47" t="n">
-        <v>106292</v>
+        <v>106752</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5686,16 +5686,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729262</v>
+        <v>729267</v>
       </c>
       <c r="R47" t="n">
-        <v>6367486</v>
+        <v>6367464</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127771573</v>
+        <v>127771570</v>
       </c>
       <c r="B48" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729265</v>
+        <v>729262</v>
       </c>
       <c r="R48" t="n">
-        <v>6367490</v>
+        <v>6367486</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5879,10 +5879,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127771405</v>
+        <v>127771367</v>
       </c>
       <c r="B49" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5914,13 +5914,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729259</v>
+        <v>729279</v>
       </c>
       <c r="R49" t="n">
-        <v>6367748</v>
+        <v>6367813</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127771608</v>
+        <v>127771419</v>
       </c>
       <c r="B50" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729267</v>
+        <v>729198</v>
       </c>
       <c r="R50" t="n">
-        <v>6367464</v>
+        <v>6367656</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127771419</v>
+        <v>127771573</v>
       </c>
       <c r="B51" t="n">
-        <v>106746</v>
+        <v>106298</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6094,16 +6094,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729198</v>
+        <v>729265</v>
       </c>
       <c r="R51" t="n">
-        <v>6367656</v>
+        <v>6367490</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127771367</v>
+        <v>127771405</v>
       </c>
       <c r="B52" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6220,13 +6220,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729279</v>
+        <v>729259</v>
       </c>
       <c r="R52" t="n">
-        <v>6367813</v>
+        <v>6367748</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6287,10 +6287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127771460</v>
+        <v>127771933</v>
       </c>
       <c r="B53" t="n">
-        <v>106746</v>
+        <v>57660</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6298,37 +6298,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729130</v>
+        <v>729149</v>
       </c>
       <c r="R53" t="n">
-        <v>6367518</v>
+        <v>6367526</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6360,6 +6365,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6371,7 +6381,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6389,45 +6399,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771421</v>
+        <v>127771410</v>
       </c>
       <c r="B54" t="n">
-        <v>106746</v>
+        <v>98434</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729214</v>
+        <v>729272</v>
       </c>
       <c r="R54" t="n">
-        <v>6367664</v>
+        <v>6367702</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6473,7 +6492,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6491,10 +6510,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771565</v>
+        <v>127771552</v>
       </c>
       <c r="B55" t="n">
-        <v>106746</v>
+        <v>107341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,34 +6521,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729264</v>
+        <v>729282</v>
       </c>
       <c r="R55" t="n">
-        <v>6367501</v>
+        <v>6367498</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6593,54 +6621,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771410</v>
+        <v>127771460</v>
       </c>
       <c r="B56" t="n">
-        <v>98428</v>
+        <v>106752</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729272</v>
+        <v>729130</v>
       </c>
       <c r="R56" t="n">
-        <v>6367702</v>
+        <v>6367518</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6686,7 +6705,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6704,10 +6723,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771552</v>
+        <v>127771421</v>
       </c>
       <c r="B57" t="n">
-        <v>107335</v>
+        <v>106752</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6715,43 +6734,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729282</v>
+        <v>729214</v>
       </c>
       <c r="R57" t="n">
-        <v>6367498</v>
+        <v>6367664</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6797,7 +6807,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6815,10 +6825,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127771933</v>
+        <v>127771565</v>
       </c>
       <c r="B58" t="n">
-        <v>57660</v>
+        <v>106752</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6826,42 +6836,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729149</v>
+        <v>729264</v>
       </c>
       <c r="R58" t="n">
-        <v>6367526</v>
+        <v>6367501</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6893,11 +6898,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6930,7 +6930,7 @@
         <v>127771440</v>
       </c>
       <c r="B59" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>127771386</v>
       </c>
       <c r="B60" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>127771415</v>
       </c>
       <c r="B61" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127771390</v>
       </c>
       <c r="B62" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>127771397</v>
       </c>
       <c r="B64" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>127771463</v>
       </c>
       <c r="B65" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>127771559</v>
       </c>
       <c r="B66" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7753,10 +7753,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127771605</v>
+        <v>127771371</v>
       </c>
       <c r="B67" t="n">
-        <v>106746</v>
+        <v>106298</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7764,16 +7764,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>729264</v>
+        <v>729244</v>
       </c>
       <c r="R67" t="n">
-        <v>6367467</v>
+        <v>6367780</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7855,10 +7855,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127771371</v>
+        <v>127771605</v>
       </c>
       <c r="B68" t="n">
-        <v>106292</v>
+        <v>106752</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>729244</v>
+        <v>729264</v>
       </c>
       <c r="R68" t="n">
-        <v>6367780</v>
+        <v>6367467</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7960,7 +7960,7 @@
         <v>127771593</v>
       </c>
       <c r="B69" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>127771401</v>
       </c>
       <c r="B70" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>127771588</v>
       </c>
       <c r="B71" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>127771564</v>
       </c>
       <c r="B72" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>127771590</v>
       </c>
       <c r="B73" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>127771387</v>
       </c>
       <c r="B74" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>127771382</v>
       </c>
       <c r="B75" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>127771416</v>
       </c>
       <c r="B76" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127771562</v>
       </c>
       <c r="B77" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>127771568</v>
       </c>
       <c r="B78" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>127771450</v>
       </c>
       <c r="B79" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>127771586</v>
       </c>
       <c r="B81" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>127771366</v>
       </c>
       <c r="B82" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>127771392</v>
       </c>
       <c r="B83" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>127771375</v>
       </c>
       <c r="B84" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>127771575</v>
       </c>
       <c r="B85" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>127771581</v>
       </c>
       <c r="B86" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>127771584</v>
       </c>
       <c r="B87" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127771466</v>
+        <v>127771393</v>
       </c>
       <c r="B88" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>729154</v>
+        <v>729237</v>
       </c>
       <c r="R88" t="n">
-        <v>6367521</v>
+        <v>6367741</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Kalkbarrskog , vid stig.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127771393</v>
+        <v>127771466</v>
       </c>
       <c r="B89" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>729237</v>
+        <v>729154</v>
       </c>
       <c r="R89" t="n">
-        <v>6367741</v>
+        <v>6367521</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog , vid stig.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127771383</v>
+        <v>127771556</v>
       </c>
       <c r="B90" t="n">
-        <v>106292</v>
+        <v>103912</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10125,21 +10125,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>729236</v>
+        <v>729273</v>
       </c>
       <c r="R90" t="n">
-        <v>6367761</v>
+        <v>6367508</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10216,10 +10216,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771556</v>
+        <v>127771578</v>
       </c>
       <c r="B91" t="n">
-        <v>103906</v>
+        <v>106752</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10227,21 +10227,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729273</v>
+        <v>729275</v>
       </c>
       <c r="R91" t="n">
-        <v>6367508</v>
+        <v>6367487</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10318,10 +10318,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127771930</v>
+        <v>127771383</v>
       </c>
       <c r="B92" t="n">
-        <v>57676</v>
+        <v>106298</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10329,46 +10329,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100048</v>
+        <v>221903</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>729246</v>
+        <v>729236</v>
       </c>
       <c r="R92" t="n">
-        <v>6367767</v>
+        <v>6367761</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10411,7 +10402,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10429,10 +10420,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771578</v>
+        <v>127771930</v>
       </c>
       <c r="B93" t="n">
-        <v>106746</v>
+        <v>57676</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10440,37 +10431,46 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221849</v>
+        <v>100048</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729275</v>
+        <v>729246</v>
       </c>
       <c r="R93" t="n">
-        <v>6367487</v>
+        <v>6367767</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127771365</v>
+        <v>127771379</v>
       </c>
       <c r="B94" t="n">
-        <v>106746</v>
+        <v>106298</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,16 +10542,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10566,10 +10566,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>729296</v>
+        <v>729229</v>
       </c>
       <c r="R94" t="n">
-        <v>6367803</v>
+        <v>6367768</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10602,11 +10602,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Vid gräns mot Klints 1:9.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10638,10 +10633,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127771379</v>
+        <v>127771365</v>
       </c>
       <c r="B95" t="n">
-        <v>106292</v>
+        <v>106752</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10649,16 +10644,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10673,10 +10668,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>729229</v>
+        <v>729296</v>
       </c>
       <c r="R95" t="n">
-        <v>6367768</v>
+        <v>6367803</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10709,6 +10704,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Vid gräns mot Klints 1:9.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10855,7 +10855,7 @@
         <v>127771429</v>
       </c>
       <c r="B97" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>127771607</v>
       </c>
       <c r="B98" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>127771461</v>
       </c>
       <c r="B99" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>127771378</v>
       </c>
       <c r="B100" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>127771412</v>
       </c>
       <c r="B101" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>127771604</v>
       </c>
       <c r="B102" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>127771554</v>
       </c>
       <c r="B103" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>127771592</v>
       </c>
       <c r="B104" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11668,10 +11668,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127771374</v>
+        <v>127771610</v>
       </c>
       <c r="B105" t="n">
-        <v>106746</v>
+        <v>106298</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11679,16 +11679,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>729236</v>
+        <v>729267</v>
       </c>
       <c r="R105" t="n">
-        <v>6367778</v>
+        <v>6367464</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -11770,10 +11770,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127771400</v>
+        <v>127771374</v>
       </c>
       <c r="B106" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>729243</v>
+        <v>729236</v>
       </c>
       <c r="R106" t="n">
-        <v>6367748</v>
+        <v>6367778</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11872,10 +11872,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127771462</v>
+        <v>127771580</v>
       </c>
       <c r="B107" t="n">
-        <v>106746</v>
+        <v>106298</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11883,16 +11883,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>729143</v>
+        <v>729272</v>
       </c>
       <c r="R107" t="n">
-        <v>6367517</v>
+        <v>6367485</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -11974,10 +11974,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127771610</v>
+        <v>127771400</v>
       </c>
       <c r="B108" t="n">
-        <v>106292</v>
+        <v>106752</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11985,16 +11985,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>729267</v>
+        <v>729243</v>
       </c>
       <c r="R108" t="n">
-        <v>6367464</v>
+        <v>6367748</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127771580</v>
+        <v>127771435</v>
       </c>
       <c r="B109" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>729272</v>
+        <v>729159</v>
       </c>
       <c r="R109" t="n">
-        <v>6367485</v>
+        <v>6367602</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127771435</v>
+        <v>127771389</v>
       </c>
       <c r="B110" t="n">
-        <v>106292</v>
+        <v>106752</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12189,16 +12189,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>729159</v>
+        <v>729230</v>
       </c>
       <c r="R110" t="n">
-        <v>6367602</v>
+        <v>6367743</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12280,10 +12280,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127771389</v>
+        <v>127771462</v>
       </c>
       <c r="B111" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>729230</v>
+        <v>729143</v>
       </c>
       <c r="R111" t="n">
-        <v>6367743</v>
+        <v>6367517</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12385,7 +12385,7 @@
         <v>127771555</v>
       </c>
       <c r="B112" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771414</v>
+        <v>127771458</v>
       </c>
       <c r="B113" t="n">
-        <v>106746</v>
+        <v>103912</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12495,21 +12495,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12519,10 +12519,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729205</v>
+        <v>729130</v>
       </c>
       <c r="R113" t="n">
-        <v>6367685</v>
+        <v>6367518</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12586,10 +12586,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771558</v>
+        <v>127771439</v>
       </c>
       <c r="B114" t="n">
-        <v>106292</v>
+        <v>103912</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12597,21 +12597,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12621,10 +12621,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729273</v>
+        <v>729123</v>
       </c>
       <c r="R114" t="n">
-        <v>6367508</v>
+        <v>6367520</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12688,10 +12688,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771577</v>
+        <v>127771414</v>
       </c>
       <c r="B115" t="n">
-        <v>106292</v>
+        <v>106752</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12699,16 +12699,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729275</v>
+        <v>729205</v>
       </c>
       <c r="R115" t="n">
-        <v>6367487</v>
+        <v>6367685</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12772,7 +12772,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771396</v>
+        <v>127771558</v>
       </c>
       <c r="B116" t="n">
-        <v>106746</v>
+        <v>106298</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12801,16 +12801,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12825,10 +12825,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729249</v>
+        <v>729273</v>
       </c>
       <c r="R116" t="n">
-        <v>6367746</v>
+        <v>6367508</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12892,10 +12892,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771458</v>
+        <v>127771577</v>
       </c>
       <c r="B117" t="n">
-        <v>103906</v>
+        <v>106298</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12903,21 +12903,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12927,10 +12927,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729130</v>
+        <v>729275</v>
       </c>
       <c r="R117" t="n">
-        <v>6367518</v>
+        <v>6367487</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771936</v>
+        <v>127771396</v>
       </c>
       <c r="B118" t="n">
-        <v>57660</v>
+        <v>106752</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13005,46 +13005,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729289</v>
+        <v>729249</v>
       </c>
       <c r="R118" t="n">
-        <v>6367518</v>
+        <v>6367746</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13087,7 +13078,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13105,10 +13096,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771439</v>
+        <v>127771936</v>
       </c>
       <c r="B119" t="n">
-        <v>103906</v>
+        <v>57660</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13116,37 +13107,46 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729123</v>
+        <v>729289</v>
       </c>
       <c r="R119" t="n">
-        <v>6367520</v>
+        <v>6367518</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -3279,7 +3279,7 @@
         <v>127130221</v>
       </c>
       <c r="B25" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>127130451</v>
       </c>
       <c r="B26" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>127130319</v>
       </c>
       <c r="B27" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>127130573</v>
       </c>
       <c r="B28" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>127167228</v>
       </c>
       <c r="B29" t="n">
-        <v>57609</v>
+        <v>57612</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>127270256</v>
       </c>
       <c r="B30" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127269410</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>98462</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>127296658</v>
       </c>
       <c r="B32" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127296627</v>
       </c>
       <c r="B35" t="n">
-        <v>43065</v>
+        <v>43066</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>127295456</v>
       </c>
       <c r="B36" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>127311062</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127771932</v>
+        <v>127771423</v>
       </c>
       <c r="B39" t="n">
-        <v>57660</v>
+        <v>106755</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,39 +4836,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729269</v>
+        <v>729206</v>
       </c>
       <c r="R39" t="n">
-        <v>6367727</v>
+        <v>6367643</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4905,7 +4900,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+          <t>Röjd skog mot O.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4919,7 +4914,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4937,10 +4932,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127771423</v>
+        <v>127771574</v>
       </c>
       <c r="B40" t="n">
-        <v>106752</v>
+        <v>106301</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4948,16 +4943,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4972,10 +4967,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729206</v>
+        <v>729271</v>
       </c>
       <c r="R40" t="n">
-        <v>6367643</v>
+        <v>6367489</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,11 +5005,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Röjd skog mot O.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5026,7 +5016,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5044,10 +5034,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127771574</v>
+        <v>127771431</v>
       </c>
       <c r="B41" t="n">
-        <v>106298</v>
+        <v>106755</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5055,16 +5045,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5079,10 +5069,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729271</v>
+        <v>729197</v>
       </c>
       <c r="R41" t="n">
-        <v>6367489</v>
+        <v>6367641</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5128,7 +5118,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5146,10 +5136,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127771431</v>
+        <v>127771932</v>
       </c>
       <c r="B42" t="n">
-        <v>106752</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5157,34 +5147,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729197</v>
+        <v>729269</v>
       </c>
       <c r="R42" t="n">
-        <v>6367641</v>
+        <v>6367727</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5219,6 +5214,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5358,7 +5358,7 @@
         <v>127771437</v>
       </c>
       <c r="B44" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>127771363</v>
       </c>
       <c r="B45" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>127771381</v>
       </c>
       <c r="B46" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>127771608</v>
       </c>
       <c r="B47" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>127771570</v>
       </c>
       <c r="B48" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>127771367</v>
       </c>
       <c r="B49" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>127771419</v>
       </c>
       <c r="B50" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>127771573</v>
       </c>
       <c r="B51" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>127771405</v>
       </c>
       <c r="B52" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>127771933</v>
       </c>
       <c r="B53" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6399,54 +6399,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771410</v>
+        <v>127771460</v>
       </c>
       <c r="B54" t="n">
-        <v>98434</v>
+        <v>106755</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729272</v>
+        <v>729130</v>
       </c>
       <c r="R54" t="n">
-        <v>6367702</v>
+        <v>6367518</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6492,7 +6483,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6510,10 +6501,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771552</v>
+        <v>127771421</v>
       </c>
       <c r="B55" t="n">
-        <v>107341</v>
+        <v>106755</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6521,43 +6512,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729282</v>
+        <v>729214</v>
       </c>
       <c r="R55" t="n">
-        <v>6367498</v>
+        <v>6367664</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6603,7 +6585,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6621,10 +6603,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771460</v>
+        <v>127771565</v>
       </c>
       <c r="B56" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6656,10 +6638,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729130</v>
+        <v>729264</v>
       </c>
       <c r="R56" t="n">
-        <v>6367518</v>
+        <v>6367501</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6705,7 +6687,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6723,45 +6705,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771421</v>
+        <v>127771410</v>
       </c>
       <c r="B57" t="n">
-        <v>106752</v>
+        <v>98437</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729214</v>
+        <v>729272</v>
       </c>
       <c r="R57" t="n">
-        <v>6367664</v>
+        <v>6367702</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6807,7 +6798,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6825,10 +6816,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127771565</v>
+        <v>127771552</v>
       </c>
       <c r="B58" t="n">
-        <v>106752</v>
+        <v>107344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6836,34 +6827,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729264</v>
+        <v>729282</v>
       </c>
       <c r="R58" t="n">
-        <v>6367501</v>
+        <v>6367498</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6930,7 +6930,7 @@
         <v>127771440</v>
       </c>
       <c r="B59" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>127771386</v>
       </c>
       <c r="B60" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>127771415</v>
       </c>
       <c r="B61" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127771390</v>
       </c>
       <c r="B62" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>127771935</v>
       </c>
       <c r="B63" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>127771397</v>
       </c>
       <c r="B64" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>127771463</v>
       </c>
       <c r="B65" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>127771559</v>
       </c>
       <c r="B66" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>127771371</v>
       </c>
       <c r="B67" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>127771605</v>
       </c>
       <c r="B68" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>127771593</v>
       </c>
       <c r="B69" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>127771401</v>
       </c>
       <c r="B70" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>127771588</v>
       </c>
       <c r="B71" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>127771564</v>
       </c>
       <c r="B72" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>127771590</v>
       </c>
       <c r="B73" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>127771387</v>
       </c>
       <c r="B74" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>127771382</v>
       </c>
       <c r="B75" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>127771416</v>
       </c>
       <c r="B76" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127771562</v>
       </c>
       <c r="B77" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>127771568</v>
       </c>
       <c r="B78" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>127771450</v>
       </c>
       <c r="B79" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127771931</v>
+        <v>127771586</v>
       </c>
       <c r="B80" t="n">
-        <v>57660</v>
+        <v>106301</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9095,39 +9095,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R80" t="n">
-        <v>6367746</v>
+        <v>6367485</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9162,11 +9157,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9178,7 +9168,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9196,10 +9186,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127771586</v>
+        <v>127771366</v>
       </c>
       <c r="B81" t="n">
-        <v>106298</v>
+        <v>106755</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9207,16 +9197,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9231,10 +9221,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729260</v>
+        <v>729279</v>
       </c>
       <c r="R81" t="n">
-        <v>6367485</v>
+        <v>6367813</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9280,7 +9270,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9298,10 +9288,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127771366</v>
+        <v>127771392</v>
       </c>
       <c r="B82" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9333,13 +9323,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729279</v>
+        <v>729237</v>
       </c>
       <c r="R82" t="n">
-        <v>6367813</v>
+        <v>6367741</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9382,7 +9372,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9400,10 +9390,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127771392</v>
+        <v>127771931</v>
       </c>
       <c r="B83" t="n">
-        <v>106752</v>
+        <v>57663</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9411,37 +9401,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>729237</v>
+        <v>729268</v>
       </c>
       <c r="R83" t="n">
-        <v>6367741</v>
+        <v>6367746</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9473,6 +9468,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9505,7 +9505,7 @@
         <v>127771375</v>
       </c>
       <c r="B84" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>127771575</v>
       </c>
       <c r="B85" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>127771581</v>
       </c>
       <c r="B86" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>127771584</v>
       </c>
       <c r="B87" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>127771393</v>
       </c>
       <c r="B88" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>127771466</v>
       </c>
       <c r="B89" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127771556</v>
+        <v>127771930</v>
       </c>
       <c r="B90" t="n">
-        <v>103912</v>
+        <v>57679</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10125,37 +10125,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220164</v>
+        <v>100048</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>729273</v>
+        <v>729246</v>
       </c>
       <c r="R90" t="n">
-        <v>6367508</v>
+        <v>6367767</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10198,7 +10207,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10219,7 +10228,7 @@
         <v>127771578</v>
       </c>
       <c r="B91" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10321,7 +10330,7 @@
         <v>127771383</v>
       </c>
       <c r="B92" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10420,10 +10429,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771930</v>
+        <v>127771556</v>
       </c>
       <c r="B93" t="n">
-        <v>57676</v>
+        <v>103915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10431,46 +10440,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100048</v>
+        <v>220164</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729246</v>
+        <v>729273</v>
       </c>
       <c r="R93" t="n">
-        <v>6367767</v>
+        <v>6367508</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10534,7 +10534,7 @@
         <v>127771379</v>
       </c>
       <c r="B94" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>127771365</v>
       </c>
       <c r="B95" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>127771929</v>
       </c>
       <c r="B96" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>127771429</v>
       </c>
       <c r="B97" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>127771607</v>
       </c>
       <c r="B98" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>127771461</v>
       </c>
       <c r="B99" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>127771378</v>
       </c>
       <c r="B100" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>127771412</v>
       </c>
       <c r="B101" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>127771604</v>
       </c>
       <c r="B102" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>127771554</v>
       </c>
       <c r="B103" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>127771592</v>
       </c>
       <c r="B104" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>127771610</v>
       </c>
       <c r="B105" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>127771374</v>
       </c>
       <c r="B106" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>127771580</v>
       </c>
       <c r="B107" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>127771400</v>
       </c>
       <c r="B108" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>127771435</v>
       </c>
       <c r="B109" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>127771389</v>
       </c>
       <c r="B110" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>127771462</v>
       </c>
       <c r="B111" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>127771555</v>
       </c>
       <c r="B112" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771458</v>
+        <v>127771936</v>
       </c>
       <c r="B113" t="n">
-        <v>103912</v>
+        <v>57663</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12495,37 +12495,46 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729130</v>
+        <v>729289</v>
       </c>
       <c r="R113" t="n">
         <v>6367518</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12568,7 +12577,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12586,10 +12595,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771439</v>
+        <v>127771414</v>
       </c>
       <c r="B114" t="n">
-        <v>103912</v>
+        <v>106755</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12597,21 +12606,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12621,10 +12630,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729123</v>
+        <v>729205</v>
       </c>
       <c r="R114" t="n">
-        <v>6367520</v>
+        <v>6367685</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12670,7 +12679,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12688,10 +12697,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771414</v>
+        <v>127771558</v>
       </c>
       <c r="B115" t="n">
-        <v>106752</v>
+        <v>106301</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12699,16 +12708,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12723,10 +12732,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729205</v>
+        <v>729273</v>
       </c>
       <c r="R115" t="n">
-        <v>6367685</v>
+        <v>6367508</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12772,7 +12781,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12790,10 +12799,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771558</v>
+        <v>127771577</v>
       </c>
       <c r="B116" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12825,10 +12834,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729273</v>
+        <v>729275</v>
       </c>
       <c r="R116" t="n">
-        <v>6367508</v>
+        <v>6367487</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12892,10 +12901,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771577</v>
+        <v>127771396</v>
       </c>
       <c r="B117" t="n">
-        <v>106298</v>
+        <v>106755</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12903,16 +12912,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12927,10 +12936,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729275</v>
+        <v>729249</v>
       </c>
       <c r="R117" t="n">
-        <v>6367487</v>
+        <v>6367746</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12976,7 +12985,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -12994,10 +13003,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771396</v>
+        <v>127771458</v>
       </c>
       <c r="B118" t="n">
-        <v>106752</v>
+        <v>103915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13005,21 +13014,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13029,10 +13038,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729249</v>
+        <v>729130</v>
       </c>
       <c r="R118" t="n">
-        <v>6367746</v>
+        <v>6367518</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13078,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13096,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771936</v>
+        <v>127771439</v>
       </c>
       <c r="B119" t="n">
-        <v>57660</v>
+        <v>103915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13107,46 +13116,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>220164</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729289</v>
+        <v>729123</v>
       </c>
       <c r="R119" t="n">
-        <v>6367518</v>
+        <v>6367520</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -3279,7 +3279,7 @@
         <v>127130221</v>
       </c>
       <c r="B25" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>127130451</v>
       </c>
       <c r="B26" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>127130319</v>
       </c>
       <c r="B27" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>127130573</v>
       </c>
       <c r="B28" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>127167228</v>
       </c>
       <c r="B29" t="n">
-        <v>57612</v>
+        <v>57618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>127270256</v>
       </c>
       <c r="B30" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127269410</v>
       </c>
       <c r="B31" t="n">
-        <v>98462</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>127296658</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,67 +4384,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127296627</v>
+        <v>127295456</v>
       </c>
       <c r="B35" t="n">
-        <v>43066</v>
+        <v>98445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729154</v>
+        <v>729163</v>
       </c>
       <c r="R35" t="n">
-        <v>6367594</v>
+        <v>6367820</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4487,7 +4477,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4505,57 +4495,67 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295456</v>
+        <v>127296627</v>
       </c>
       <c r="B36" t="n">
-        <v>98437</v>
+        <v>43066</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729163</v>
+        <v>729154</v>
       </c>
       <c r="R36" t="n">
-        <v>6367820</v>
+        <v>6367594</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>127311062</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127771423</v>
+        <v>127771932</v>
       </c>
       <c r="B39" t="n">
-        <v>106755</v>
+        <v>57669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,34 +4836,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729206</v>
+        <v>729269</v>
       </c>
       <c r="R39" t="n">
-        <v>6367643</v>
+        <v>6367727</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4900,7 +4905,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Röjd skog mot O.</t>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4914,7 +4919,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4932,10 +4937,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127771574</v>
+        <v>127771423</v>
       </c>
       <c r="B40" t="n">
-        <v>106301</v>
+        <v>106763</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4943,16 +4948,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4967,10 +4972,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729271</v>
+        <v>729206</v>
       </c>
       <c r="R40" t="n">
-        <v>6367489</v>
+        <v>6367643</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5005,6 +5010,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Röjd skog mot O.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5016,7 +5026,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5034,10 +5044,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127771431</v>
+        <v>127771574</v>
       </c>
       <c r="B41" t="n">
-        <v>106755</v>
+        <v>106309</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5045,16 +5055,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5069,10 +5079,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729197</v>
+        <v>729271</v>
       </c>
       <c r="R41" t="n">
-        <v>6367641</v>
+        <v>6367489</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5118,7 +5128,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5136,10 +5146,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127771932</v>
+        <v>127771431</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>106763</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5147,39 +5157,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729269</v>
+        <v>729197</v>
       </c>
       <c r="R42" t="n">
-        <v>6367727</v>
+        <v>6367641</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5214,11 +5219,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5358,7 +5358,7 @@
         <v>127771437</v>
       </c>
       <c r="B44" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>127771363</v>
       </c>
       <c r="B45" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>127771381</v>
       </c>
       <c r="B46" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>127771608</v>
       </c>
       <c r="B47" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>127771570</v>
       </c>
       <c r="B48" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>127771367</v>
       </c>
       <c r="B49" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>127771419</v>
       </c>
       <c r="B50" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>127771573</v>
       </c>
       <c r="B51" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>127771405</v>
       </c>
       <c r="B52" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6287,53 +6287,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127771933</v>
+        <v>127771410</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>98445</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729149</v>
+        <v>729272</v>
       </c>
       <c r="R53" t="n">
-        <v>6367526</v>
+        <v>6367702</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6365,11 +6369,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6381,7 +6380,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6399,10 +6398,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771460</v>
+        <v>127771552</v>
       </c>
       <c r="B54" t="n">
-        <v>106755</v>
+        <v>107352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6410,34 +6409,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729130</v>
+        <v>729282</v>
       </c>
       <c r="R54" t="n">
-        <v>6367518</v>
+        <v>6367498</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6483,7 +6491,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6501,10 +6509,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771421</v>
+        <v>127771933</v>
       </c>
       <c r="B55" t="n">
-        <v>106755</v>
+        <v>57669</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,37 +6520,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729214</v>
+        <v>729149</v>
       </c>
       <c r="R55" t="n">
-        <v>6367664</v>
+        <v>6367526</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6574,6 +6587,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6585,7 +6603,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6603,10 +6621,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771565</v>
+        <v>127771460</v>
       </c>
       <c r="B56" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6638,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729264</v>
+        <v>729130</v>
       </c>
       <c r="R56" t="n">
-        <v>6367501</v>
+        <v>6367518</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6687,7 +6705,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6705,54 +6723,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771410</v>
+        <v>127771421</v>
       </c>
       <c r="B57" t="n">
-        <v>98437</v>
+        <v>106763</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729272</v>
+        <v>729214</v>
       </c>
       <c r="R57" t="n">
-        <v>6367702</v>
+        <v>6367664</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6798,7 +6807,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6816,10 +6825,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127771552</v>
+        <v>127771565</v>
       </c>
       <c r="B58" t="n">
-        <v>107344</v>
+        <v>106763</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6827,43 +6836,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729282</v>
+        <v>729264</v>
       </c>
       <c r="R58" t="n">
-        <v>6367498</v>
+        <v>6367501</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6930,7 +6930,7 @@
         <v>127771440</v>
       </c>
       <c r="B59" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>127771386</v>
       </c>
       <c r="B60" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>127771415</v>
       </c>
       <c r="B61" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127771390</v>
       </c>
       <c r="B62" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7335,10 +7335,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127771935</v>
+        <v>127771397</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>106309</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,42 +7346,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>729189</v>
+        <v>729249</v>
       </c>
       <c r="R63" t="n">
-        <v>6367526</v>
+        <v>6367746</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7413,11 +7408,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre bo i nu fallen död tall.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7429,7 +7419,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7447,10 +7437,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127771397</v>
+        <v>127771463</v>
       </c>
       <c r="B64" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7482,10 +7472,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>729249</v>
+        <v>729143</v>
       </c>
       <c r="R64" t="n">
-        <v>6367746</v>
+        <v>6367517</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7531,7 +7521,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7549,10 +7539,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127771463</v>
+        <v>127771559</v>
       </c>
       <c r="B65" t="n">
-        <v>106301</v>
+        <v>106763</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7560,16 +7550,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7584,10 +7574,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>729143</v>
+        <v>729273</v>
       </c>
       <c r="R65" t="n">
-        <v>6367517</v>
+        <v>6367508</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7633,7 +7623,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7651,10 +7641,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127771559</v>
+        <v>127771935</v>
       </c>
       <c r="B66" t="n">
-        <v>106755</v>
+        <v>57669</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7662,37 +7652,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>729273</v>
+        <v>729189</v>
       </c>
       <c r="R66" t="n">
-        <v>6367508</v>
+        <v>6367526</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7724,6 +7719,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre bo i nu fallen död tall.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7756,7 +7756,7 @@
         <v>127771371</v>
       </c>
       <c r="B67" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>127771605</v>
       </c>
       <c r="B68" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>127771593</v>
       </c>
       <c r="B69" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>127771401</v>
       </c>
       <c r="B70" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>127771588</v>
       </c>
       <c r="B71" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>127771564</v>
       </c>
       <c r="B72" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>127771590</v>
       </c>
       <c r="B73" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>127771387</v>
       </c>
       <c r="B74" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>127771382</v>
       </c>
       <c r="B75" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>127771416</v>
       </c>
       <c r="B76" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127771562</v>
       </c>
       <c r="B77" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>127771568</v>
       </c>
       <c r="B78" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>127771450</v>
       </c>
       <c r="B79" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127771586</v>
+        <v>127771931</v>
       </c>
       <c r="B80" t="n">
-        <v>106301</v>
+        <v>57669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9095,34 +9095,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R80" t="n">
-        <v>6367485</v>
+        <v>6367746</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9157,6 +9162,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9168,7 +9178,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9186,10 +9196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127771366</v>
+        <v>127771586</v>
       </c>
       <c r="B81" t="n">
-        <v>106755</v>
+        <v>106309</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9197,16 +9207,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9221,10 +9231,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729279</v>
+        <v>729260</v>
       </c>
       <c r="R81" t="n">
-        <v>6367813</v>
+        <v>6367485</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9270,7 +9280,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9288,10 +9298,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127771392</v>
+        <v>127771366</v>
       </c>
       <c r="B82" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9323,13 +9333,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729237</v>
+        <v>729279</v>
       </c>
       <c r="R82" t="n">
-        <v>6367741</v>
+        <v>6367813</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9372,7 +9382,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9390,10 +9400,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127771931</v>
+        <v>127771392</v>
       </c>
       <c r="B83" t="n">
-        <v>57663</v>
+        <v>106763</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9401,42 +9411,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>729268</v>
+        <v>729237</v>
       </c>
       <c r="R83" t="n">
-        <v>6367746</v>
+        <v>6367741</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9468,11 +9473,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9505,7 +9505,7 @@
         <v>127771375</v>
       </c>
       <c r="B84" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>127771575</v>
       </c>
       <c r="B85" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>127771581</v>
       </c>
       <c r="B86" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>127771584</v>
       </c>
       <c r="B87" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>127771393</v>
       </c>
       <c r="B88" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>127771466</v>
       </c>
       <c r="B89" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>127771930</v>
       </c>
       <c r="B90" t="n">
-        <v>57679</v>
+        <v>57685</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10225,10 +10225,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771578</v>
+        <v>127771556</v>
       </c>
       <c r="B91" t="n">
-        <v>106755</v>
+        <v>103923</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10236,21 +10236,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10260,10 +10260,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729275</v>
+        <v>729273</v>
       </c>
       <c r="R91" t="n">
-        <v>6367487</v>
+        <v>6367508</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10327,10 +10327,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127771383</v>
+        <v>127771578</v>
       </c>
       <c r="B92" t="n">
-        <v>106301</v>
+        <v>106763</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10338,16 +10338,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10362,10 +10362,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>729236</v>
+        <v>729275</v>
       </c>
       <c r="R92" t="n">
-        <v>6367761</v>
+        <v>6367487</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10429,10 +10429,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771556</v>
+        <v>127771383</v>
       </c>
       <c r="B93" t="n">
-        <v>103915</v>
+        <v>106309</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729273</v>
+        <v>729236</v>
       </c>
       <c r="R93" t="n">
-        <v>6367508</v>
+        <v>6367761</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10534,7 +10534,7 @@
         <v>127771379</v>
       </c>
       <c r="B94" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>127771365</v>
       </c>
       <c r="B95" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>127771929</v>
       </c>
       <c r="B96" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>127771429</v>
       </c>
       <c r="B97" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>127771607</v>
       </c>
       <c r="B98" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>127771461</v>
       </c>
       <c r="B99" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>127771378</v>
       </c>
       <c r="B100" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>127771412</v>
       </c>
       <c r="B101" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>127771604</v>
       </c>
       <c r="B102" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>127771554</v>
       </c>
       <c r="B103" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>127771592</v>
       </c>
       <c r="B104" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>127771610</v>
       </c>
       <c r="B105" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>127771374</v>
       </c>
       <c r="B106" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>127771580</v>
       </c>
       <c r="B107" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>127771400</v>
       </c>
       <c r="B108" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>127771435</v>
       </c>
       <c r="B109" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>127771389</v>
       </c>
       <c r="B110" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>127771462</v>
       </c>
       <c r="B111" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>127771555</v>
       </c>
       <c r="B112" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>127771936</v>
       </c>
       <c r="B113" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12595,10 +12595,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771414</v>
+        <v>127771458</v>
       </c>
       <c r="B114" t="n">
-        <v>106755</v>
+        <v>103923</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12606,21 +12606,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729205</v>
+        <v>729130</v>
       </c>
       <c r="R114" t="n">
-        <v>6367685</v>
+        <v>6367518</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12697,10 +12697,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771558</v>
+        <v>127771439</v>
       </c>
       <c r="B115" t="n">
-        <v>106301</v>
+        <v>103923</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12708,21 +12708,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729273</v>
+        <v>729123</v>
       </c>
       <c r="R115" t="n">
-        <v>6367508</v>
+        <v>6367520</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12799,10 +12799,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771577</v>
+        <v>127771414</v>
       </c>
       <c r="B116" t="n">
-        <v>106301</v>
+        <v>106763</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12810,16 +12810,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12834,10 +12834,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729275</v>
+        <v>729205</v>
       </c>
       <c r="R116" t="n">
-        <v>6367487</v>
+        <v>6367685</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12901,10 +12901,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771396</v>
+        <v>127771558</v>
       </c>
       <c r="B117" t="n">
-        <v>106755</v>
+        <v>106309</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12912,16 +12912,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12936,10 +12936,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729249</v>
+        <v>729273</v>
       </c>
       <c r="R117" t="n">
-        <v>6367746</v>
+        <v>6367508</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771458</v>
+        <v>127771577</v>
       </c>
       <c r="B118" t="n">
-        <v>103915</v>
+        <v>106309</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13014,21 +13014,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729130</v>
+        <v>729275</v>
       </c>
       <c r="R118" t="n">
-        <v>6367518</v>
+        <v>6367487</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771439</v>
+        <v>127771396</v>
       </c>
       <c r="B119" t="n">
-        <v>103915</v>
+        <v>106763</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13116,21 +13116,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729123</v>
+        <v>729249</v>
       </c>
       <c r="R119" t="n">
-        <v>6367520</v>
+        <v>6367746</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -3844,7 +3844,7 @@
         <v>127270256</v>
       </c>
       <c r="B30" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127269410</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127295456</v>
       </c>
       <c r="B35" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>127771423</v>
       </c>
       <c r="B40" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>127771574</v>
       </c>
       <c r="B41" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>127771431</v>
       </c>
       <c r="B42" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>127771437</v>
       </c>
       <c r="B44" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>127771363</v>
       </c>
       <c r="B45" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>127771381</v>
       </c>
       <c r="B46" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>127771608</v>
       </c>
       <c r="B47" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>127771570</v>
       </c>
       <c r="B48" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>127771367</v>
       </c>
       <c r="B49" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>127771419</v>
       </c>
       <c r="B50" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>127771573</v>
       </c>
       <c r="B51" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>127771405</v>
       </c>
       <c r="B52" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6287,54 +6287,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127771410</v>
+        <v>127771460</v>
       </c>
       <c r="B53" t="n">
-        <v>98445</v>
+        <v>106764</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729272</v>
+        <v>729130</v>
       </c>
       <c r="R53" t="n">
-        <v>6367702</v>
+        <v>6367518</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6380,7 +6371,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6398,10 +6389,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771552</v>
+        <v>127771421</v>
       </c>
       <c r="B54" t="n">
-        <v>107352</v>
+        <v>106764</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6409,43 +6400,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729282</v>
+        <v>729214</v>
       </c>
       <c r="R54" t="n">
-        <v>6367498</v>
+        <v>6367664</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6491,7 +6473,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6509,10 +6491,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771933</v>
+        <v>127771565</v>
       </c>
       <c r="B55" t="n">
-        <v>57669</v>
+        <v>106764</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6520,42 +6502,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729149</v>
+        <v>729264</v>
       </c>
       <c r="R55" t="n">
-        <v>6367526</v>
+        <v>6367501</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6587,11 +6564,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6603,7 +6575,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6621,10 +6593,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771460</v>
+        <v>127771933</v>
       </c>
       <c r="B56" t="n">
-        <v>106763</v>
+        <v>57669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6632,37 +6604,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729130</v>
+        <v>729149</v>
       </c>
       <c r="R56" t="n">
-        <v>6367518</v>
+        <v>6367526</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6694,6 +6671,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6705,7 +6687,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6723,45 +6705,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771421</v>
+        <v>127771410</v>
       </c>
       <c r="B57" t="n">
-        <v>106763</v>
+        <v>98446</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729214</v>
+        <v>729272</v>
       </c>
       <c r="R57" t="n">
-        <v>6367664</v>
+        <v>6367702</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6807,7 +6798,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6825,10 +6816,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127771565</v>
+        <v>127771552</v>
       </c>
       <c r="B58" t="n">
-        <v>106763</v>
+        <v>107353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6836,34 +6827,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729264</v>
+        <v>729282</v>
       </c>
       <c r="R58" t="n">
-        <v>6367501</v>
+        <v>6367498</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6930,7 +6930,7 @@
         <v>127771440</v>
       </c>
       <c r="B59" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>127771386</v>
       </c>
       <c r="B60" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>127771415</v>
       </c>
       <c r="B61" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127771390</v>
       </c>
       <c r="B62" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>127771397</v>
       </c>
       <c r="B63" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>127771463</v>
       </c>
       <c r="B64" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>127771559</v>
       </c>
       <c r="B65" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>127771371</v>
       </c>
       <c r="B67" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>127771605</v>
       </c>
       <c r="B68" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>127771593</v>
       </c>
       <c r="B69" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>127771401</v>
       </c>
       <c r="B70" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>127771588</v>
       </c>
       <c r="B71" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>127771564</v>
       </c>
       <c r="B72" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>127771590</v>
       </c>
       <c r="B73" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>127771387</v>
       </c>
       <c r="B74" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>127771382</v>
       </c>
       <c r="B75" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>127771416</v>
       </c>
       <c r="B76" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127771562</v>
       </c>
       <c r="B77" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>127771568</v>
       </c>
       <c r="B78" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>127771450</v>
       </c>
       <c r="B79" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127771931</v>
+        <v>127771586</v>
       </c>
       <c r="B80" t="n">
-        <v>57669</v>
+        <v>106310</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9095,39 +9095,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R80" t="n">
-        <v>6367746</v>
+        <v>6367485</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9162,11 +9157,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9178,7 +9168,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9196,10 +9186,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127771586</v>
+        <v>127771366</v>
       </c>
       <c r="B81" t="n">
-        <v>106309</v>
+        <v>106764</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9207,16 +9197,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9231,10 +9221,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729260</v>
+        <v>729279</v>
       </c>
       <c r="R81" t="n">
-        <v>6367485</v>
+        <v>6367813</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9280,7 +9270,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9298,10 +9288,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127771366</v>
+        <v>127771392</v>
       </c>
       <c r="B82" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9333,13 +9323,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729279</v>
+        <v>729237</v>
       </c>
       <c r="R82" t="n">
-        <v>6367813</v>
+        <v>6367741</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9382,7 +9372,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9400,10 +9390,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127771392</v>
+        <v>127771931</v>
       </c>
       <c r="B83" t="n">
-        <v>106763</v>
+        <v>57669</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9411,37 +9401,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>729237</v>
+        <v>729268</v>
       </c>
       <c r="R83" t="n">
-        <v>6367741</v>
+        <v>6367746</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9473,6 +9468,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9505,7 +9505,7 @@
         <v>127771375</v>
       </c>
       <c r="B84" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>127771575</v>
       </c>
       <c r="B85" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>127771581</v>
       </c>
       <c r="B86" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>127771584</v>
       </c>
       <c r="B87" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>127771393</v>
       </c>
       <c r="B88" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>127771466</v>
       </c>
       <c r="B89" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10225,10 +10225,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771556</v>
+        <v>127771578</v>
       </c>
       <c r="B91" t="n">
-        <v>103923</v>
+        <v>106764</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10236,21 +10236,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10260,10 +10260,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729273</v>
+        <v>729275</v>
       </c>
       <c r="R91" t="n">
-        <v>6367508</v>
+        <v>6367487</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10327,10 +10327,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127771578</v>
+        <v>127771383</v>
       </c>
       <c r="B92" t="n">
-        <v>106763</v>
+        <v>106310</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10338,16 +10338,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10362,10 +10362,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>729275</v>
+        <v>729236</v>
       </c>
       <c r="R92" t="n">
-        <v>6367487</v>
+        <v>6367761</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10429,10 +10429,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771383</v>
+        <v>127771556</v>
       </c>
       <c r="B93" t="n">
-        <v>106309</v>
+        <v>103924</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729236</v>
+        <v>729273</v>
       </c>
       <c r="R93" t="n">
-        <v>6367761</v>
+        <v>6367508</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10534,7 +10534,7 @@
         <v>127771379</v>
       </c>
       <c r="B94" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>127771365</v>
       </c>
       <c r="B95" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>127771429</v>
       </c>
       <c r="B97" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>127771607</v>
       </c>
       <c r="B98" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>127771461</v>
       </c>
       <c r="B99" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>127771378</v>
       </c>
       <c r="B100" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>127771412</v>
       </c>
       <c r="B101" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>127771604</v>
       </c>
       <c r="B102" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>127771554</v>
       </c>
       <c r="B103" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>127771592</v>
       </c>
       <c r="B104" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>127771610</v>
       </c>
       <c r="B105" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>127771374</v>
       </c>
       <c r="B106" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>127771580</v>
       </c>
       <c r="B107" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>127771400</v>
       </c>
       <c r="B108" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>127771435</v>
       </c>
       <c r="B109" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>127771389</v>
       </c>
       <c r="B110" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>127771462</v>
       </c>
       <c r="B111" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>127771555</v>
       </c>
       <c r="B112" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771936</v>
+        <v>127771458</v>
       </c>
       <c r="B113" t="n">
-        <v>57669</v>
+        <v>103924</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12495,46 +12495,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>220164</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729289</v>
+        <v>729130</v>
       </c>
       <c r="R113" t="n">
         <v>6367518</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12577,7 +12568,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12595,10 +12586,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771458</v>
+        <v>127771439</v>
       </c>
       <c r="B114" t="n">
-        <v>103923</v>
+        <v>103924</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12630,10 +12621,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729130</v>
+        <v>729123</v>
       </c>
       <c r="R114" t="n">
-        <v>6367518</v>
+        <v>6367520</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12679,7 +12670,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12697,10 +12688,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771439</v>
+        <v>127771936</v>
       </c>
       <c r="B115" t="n">
-        <v>103923</v>
+        <v>57669</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12708,37 +12699,46 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729123</v>
+        <v>729289</v>
       </c>
       <c r="R115" t="n">
-        <v>6367520</v>
+        <v>6367518</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12802,7 +12802,7 @@
         <v>127771414</v>
       </c>
       <c r="B116" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>127771558</v>
       </c>
       <c r="B117" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>127771577</v>
       </c>
       <c r="B118" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>127771396</v>
       </c>
       <c r="B119" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -5248,10 +5248,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127771857</v>
+        <v>127771437</v>
       </c>
       <c r="B43" t="n">
-        <v>5493</v>
+        <v>106764</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,21 +5259,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101410</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729268</v>
+        <v>729159</v>
       </c>
       <c r="R43" t="n">
-        <v>6367746</v>
+        <v>6367602</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5321,11 +5321,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Tall med angrepp.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5337,7 +5332,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5355,10 +5350,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127771437</v>
+        <v>127771363</v>
       </c>
       <c r="B44" t="n">
-        <v>106764</v>
+        <v>106310</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5366,16 +5361,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5390,10 +5385,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>729159</v>
+        <v>729296</v>
       </c>
       <c r="R44" t="n">
-        <v>6367602</v>
+        <v>6367803</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5428,6 +5423,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Vid gräns mot Klints 1:9.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127771363</v>
+        <v>127771857</v>
       </c>
       <c r="B45" t="n">
-        <v>106310</v>
+        <v>5493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5468,21 +5468,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221903</v>
+        <v>101410</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>729296</v>
+        <v>729268</v>
       </c>
       <c r="R45" t="n">
-        <v>6367803</v>
+        <v>6367746</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Vid gräns mot Klints 1:9.</t>
+          <t>Tall med angrepp.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6287,10 +6287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127771460</v>
+        <v>127771933</v>
       </c>
       <c r="B53" t="n">
-        <v>106764</v>
+        <v>57669</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6298,37 +6298,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729130</v>
+        <v>729149</v>
       </c>
       <c r="R53" t="n">
-        <v>6367518</v>
+        <v>6367526</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6360,6 +6365,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6371,7 +6381,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6389,7 +6399,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771421</v>
+        <v>127771460</v>
       </c>
       <c r="B54" t="n">
         <v>106764</v>
@@ -6424,10 +6434,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729214</v>
+        <v>729130</v>
       </c>
       <c r="R54" t="n">
-        <v>6367664</v>
+        <v>6367518</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6473,7 +6483,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6491,7 +6501,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771565</v>
+        <v>127771421</v>
       </c>
       <c r="B55" t="n">
         <v>106764</v>
@@ -6526,10 +6536,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729264</v>
+        <v>729214</v>
       </c>
       <c r="R55" t="n">
-        <v>6367501</v>
+        <v>6367664</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6575,7 +6585,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6593,10 +6603,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771933</v>
+        <v>127771565</v>
       </c>
       <c r="B56" t="n">
-        <v>57669</v>
+        <v>106764</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6604,42 +6614,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729149</v>
+        <v>729264</v>
       </c>
       <c r="R56" t="n">
-        <v>6367526</v>
+        <v>6367501</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6671,11 +6676,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127771586</v>
+        <v>127771931</v>
       </c>
       <c r="B80" t="n">
-        <v>106310</v>
+        <v>57669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9095,34 +9095,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R80" t="n">
-        <v>6367485</v>
+        <v>6367746</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9157,6 +9162,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9168,7 +9178,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9186,10 +9196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127771366</v>
+        <v>127771586</v>
       </c>
       <c r="B81" t="n">
-        <v>106764</v>
+        <v>106310</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9197,16 +9207,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9221,10 +9231,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729279</v>
+        <v>729260</v>
       </c>
       <c r="R81" t="n">
-        <v>6367813</v>
+        <v>6367485</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9270,7 +9280,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9288,7 +9298,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127771392</v>
+        <v>127771366</v>
       </c>
       <c r="B82" t="n">
         <v>106764</v>
@@ -9323,13 +9333,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729237</v>
+        <v>729279</v>
       </c>
       <c r="R82" t="n">
-        <v>6367741</v>
+        <v>6367813</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9372,7 +9382,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9390,10 +9400,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127771931</v>
+        <v>127771392</v>
       </c>
       <c r="B83" t="n">
-        <v>57669</v>
+        <v>106764</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9401,42 +9411,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>729268</v>
+        <v>729237</v>
       </c>
       <c r="R83" t="n">
-        <v>6367746</v>
+        <v>6367741</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9468,11 +9473,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10740,10 +10740,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127771929</v>
+        <v>127771429</v>
       </c>
       <c r="B96" t="n">
-        <v>57669</v>
+        <v>106310</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10751,39 +10751,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>729237</v>
+        <v>729197</v>
       </c>
       <c r="R96" t="n">
-        <v>6367741</v>
+        <v>6367641</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10818,11 +10813,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Födosöksspår i död tallåga med mycket rikligt med utgångshål för insekter.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10834,7 +10824,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -10852,7 +10842,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127771429</v>
+        <v>127771607</v>
       </c>
       <c r="B97" t="n">
         <v>106310</v>
@@ -10887,10 +10877,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>729197</v>
+        <v>729264</v>
       </c>
       <c r="R97" t="n">
-        <v>6367641</v>
+        <v>6367467</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10936,7 +10926,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -10954,7 +10944,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127771607</v>
+        <v>127771461</v>
       </c>
       <c r="B98" t="n">
         <v>106310</v>
@@ -10989,10 +10979,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>729264</v>
+        <v>729130</v>
       </c>
       <c r="R98" t="n">
-        <v>6367467</v>
+        <v>6367518</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11038,7 +11028,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11056,10 +11046,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127771461</v>
+        <v>127771929</v>
       </c>
       <c r="B99" t="n">
-        <v>106310</v>
+        <v>57669</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11067,34 +11057,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>729130</v>
+        <v>729237</v>
       </c>
       <c r="R99" t="n">
-        <v>6367518</v>
+        <v>6367741</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11129,6 +11124,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Födosöksspår i död tallåga med mycket rikligt med utgångshål för insekter.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771458</v>
+        <v>127771414</v>
       </c>
       <c r="B113" t="n">
-        <v>103924</v>
+        <v>106764</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12495,21 +12495,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12519,10 +12519,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729130</v>
+        <v>729205</v>
       </c>
       <c r="R113" t="n">
-        <v>6367518</v>
+        <v>6367685</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12586,10 +12586,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771439</v>
+        <v>127771558</v>
       </c>
       <c r="B114" t="n">
-        <v>103924</v>
+        <v>106310</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12597,21 +12597,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12621,10 +12621,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729123</v>
+        <v>729273</v>
       </c>
       <c r="R114" t="n">
-        <v>6367520</v>
+        <v>6367508</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12688,10 +12688,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771936</v>
+        <v>127771577</v>
       </c>
       <c r="B115" t="n">
-        <v>57669</v>
+        <v>106310</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12699,46 +12699,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729289</v>
+        <v>729275</v>
       </c>
       <c r="R115" t="n">
-        <v>6367518</v>
+        <v>6367487</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12781,7 +12772,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12799,7 +12790,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771414</v>
+        <v>127771396</v>
       </c>
       <c r="B116" t="n">
         <v>106764</v>
@@ -12834,10 +12825,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729205</v>
+        <v>729249</v>
       </c>
       <c r="R116" t="n">
-        <v>6367685</v>
+        <v>6367746</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12883,7 +12874,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12901,10 +12892,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771558</v>
+        <v>127771458</v>
       </c>
       <c r="B117" t="n">
-        <v>106310</v>
+        <v>103924</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12912,21 +12903,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12936,10 +12927,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729273</v>
+        <v>729130</v>
       </c>
       <c r="R117" t="n">
-        <v>6367508</v>
+        <v>6367518</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12985,7 +12976,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13003,10 +12994,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771577</v>
+        <v>127771439</v>
       </c>
       <c r="B118" t="n">
-        <v>106310</v>
+        <v>103924</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13014,21 +13005,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13038,10 +13029,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729275</v>
+        <v>729123</v>
       </c>
       <c r="R118" t="n">
-        <v>6367487</v>
+        <v>6367520</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13087,7 +13078,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13105,10 +13096,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771396</v>
+        <v>127771936</v>
       </c>
       <c r="B119" t="n">
-        <v>106764</v>
+        <v>57669</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13116,37 +13107,46 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729249</v>
+        <v>729289</v>
       </c>
       <c r="R119" t="n">
-        <v>6367746</v>
+        <v>6367518</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4174,7 +4174,7 @@
         <v>127295470</v>
       </c>
       <c r="B33" t="n">
-        <v>107353</v>
+        <v>107354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127295468</v>
       </c>
       <c r="B34" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,57 +4384,67 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295456</v>
+        <v>127296627</v>
       </c>
       <c r="B35" t="n">
-        <v>98446</v>
+        <v>43066</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729163</v>
+        <v>729154</v>
       </c>
       <c r="R35" t="n">
-        <v>6367820</v>
+        <v>6367594</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4477,7 +4487,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4495,67 +4505,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127296627</v>
+        <v>127295456</v>
       </c>
       <c r="B36" t="n">
-        <v>43066</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2) A 4572-2026, Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2) A 4572-2028, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729154</v>
+        <v>729163</v>
       </c>
       <c r="R36" t="n">
-        <v>6367594</v>
+        <v>6367820</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Alvar, igenväxande med buskar. Fortfarande gott om backtimjan.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v>127295467</v>
       </c>
       <c r="B37" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>127771423</v>
       </c>
       <c r="B40" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>127771574</v>
       </c>
       <c r="B41" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>127771431</v>
       </c>
       <c r="B42" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127771437</v>
+        <v>127771857</v>
       </c>
       <c r="B43" t="n">
-        <v>106764</v>
+        <v>5493</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,21 +5259,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>101410</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729159</v>
+        <v>729268</v>
       </c>
       <c r="R43" t="n">
-        <v>6367602</v>
+        <v>6367746</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5321,6 +5321,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Tall med angrepp.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5332,7 +5337,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5350,10 +5355,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127771363</v>
+        <v>127771437</v>
       </c>
       <c r="B44" t="n">
-        <v>106310</v>
+        <v>106765</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5361,16 +5366,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5385,10 +5390,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>729296</v>
+        <v>729159</v>
       </c>
       <c r="R44" t="n">
-        <v>6367803</v>
+        <v>6367602</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5423,11 +5428,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Vid gräns mot Klints 1:9.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127771857</v>
+        <v>127771363</v>
       </c>
       <c r="B45" t="n">
-        <v>5493</v>
+        <v>106311</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5468,21 +5468,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101410</v>
+        <v>221903</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>729268</v>
+        <v>729296</v>
       </c>
       <c r="R45" t="n">
-        <v>6367746</v>
+        <v>6367803</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tall med angrepp.</t>
+          <t>Vid gräns mot Klints 1:9.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5567,7 +5567,7 @@
         <v>127771381</v>
       </c>
       <c r="B46" t="n">
-        <v>107353</v>
+        <v>107354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>127771608</v>
       </c>
       <c r="B47" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>127771570</v>
       </c>
       <c r="B48" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>127771367</v>
       </c>
       <c r="B49" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>127771419</v>
       </c>
       <c r="B50" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>127771573</v>
       </c>
       <c r="B51" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>127771405</v>
       </c>
       <c r="B52" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,45 +6399,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771460</v>
+        <v>127771410</v>
       </c>
       <c r="B54" t="n">
-        <v>106764</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729130</v>
+        <v>729272</v>
       </c>
       <c r="R54" t="n">
-        <v>6367518</v>
+        <v>6367702</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6483,7 +6492,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6501,10 +6510,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771421</v>
+        <v>127771552</v>
       </c>
       <c r="B55" t="n">
-        <v>106764</v>
+        <v>107354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,34 +6521,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729214</v>
+        <v>729282</v>
       </c>
       <c r="R55" t="n">
-        <v>6367664</v>
+        <v>6367498</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6585,7 +6603,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6603,10 +6621,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771565</v>
+        <v>127771460</v>
       </c>
       <c r="B56" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6638,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729264</v>
+        <v>729130</v>
       </c>
       <c r="R56" t="n">
-        <v>6367501</v>
+        <v>6367518</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6687,7 +6705,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6705,54 +6723,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771410</v>
+        <v>127771421</v>
       </c>
       <c r="B57" t="n">
-        <v>98446</v>
+        <v>106765</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729272</v>
+        <v>729214</v>
       </c>
       <c r="R57" t="n">
-        <v>6367702</v>
+        <v>6367664</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6798,7 +6807,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6816,10 +6825,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127771552</v>
+        <v>127771565</v>
       </c>
       <c r="B58" t="n">
-        <v>107353</v>
+        <v>106765</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6827,43 +6836,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729282</v>
+        <v>729264</v>
       </c>
       <c r="R58" t="n">
-        <v>6367498</v>
+        <v>6367501</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6930,7 +6930,7 @@
         <v>127771440</v>
       </c>
       <c r="B59" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>127771386</v>
       </c>
       <c r="B60" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>127771415</v>
       </c>
       <c r="B61" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127771390</v>
       </c>
       <c r="B62" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>127771397</v>
       </c>
       <c r="B63" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>127771463</v>
       </c>
       <c r="B64" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>127771559</v>
       </c>
       <c r="B65" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>127771371</v>
       </c>
       <c r="B67" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>127771605</v>
       </c>
       <c r="B68" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>127771593</v>
       </c>
       <c r="B69" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>127771401</v>
       </c>
       <c r="B70" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>127771588</v>
       </c>
       <c r="B71" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>127771564</v>
       </c>
       <c r="B72" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>127771590</v>
       </c>
       <c r="B73" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>127771387</v>
       </c>
       <c r="B74" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>127771382</v>
       </c>
       <c r="B75" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>127771416</v>
       </c>
       <c r="B76" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127771562</v>
       </c>
       <c r="B77" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>127771568</v>
       </c>
       <c r="B78" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>127771450</v>
       </c>
       <c r="B79" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>127771586</v>
       </c>
       <c r="B81" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>127771366</v>
       </c>
       <c r="B82" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>127771392</v>
       </c>
       <c r="B83" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>127771375</v>
       </c>
       <c r="B84" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>127771575</v>
       </c>
       <c r="B85" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>127771581</v>
       </c>
       <c r="B86" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>127771584</v>
       </c>
       <c r="B87" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>127771393</v>
       </c>
       <c r="B88" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>127771466</v>
       </c>
       <c r="B89" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10225,10 +10225,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771578</v>
+        <v>127771556</v>
       </c>
       <c r="B91" t="n">
-        <v>106764</v>
+        <v>103925</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10236,21 +10236,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10260,10 +10260,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729275</v>
+        <v>729273</v>
       </c>
       <c r="R91" t="n">
-        <v>6367487</v>
+        <v>6367508</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10327,10 +10327,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127771383</v>
+        <v>127771578</v>
       </c>
       <c r="B92" t="n">
-        <v>106310</v>
+        <v>106765</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10338,16 +10338,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10362,10 +10362,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>729236</v>
+        <v>729275</v>
       </c>
       <c r="R92" t="n">
-        <v>6367761</v>
+        <v>6367487</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10429,10 +10429,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771556</v>
+        <v>127771383</v>
       </c>
       <c r="B93" t="n">
-        <v>103924</v>
+        <v>106311</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729273</v>
+        <v>729236</v>
       </c>
       <c r="R93" t="n">
-        <v>6367508</v>
+        <v>6367761</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10534,7 +10534,7 @@
         <v>127771379</v>
       </c>
       <c r="B94" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>127771365</v>
       </c>
       <c r="B95" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>127771429</v>
       </c>
       <c r="B96" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>127771607</v>
       </c>
       <c r="B97" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>127771461</v>
       </c>
       <c r="B98" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>127771378</v>
       </c>
       <c r="B100" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>127771412</v>
       </c>
       <c r="B101" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>127771604</v>
       </c>
       <c r="B102" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>127771554</v>
       </c>
       <c r="B103" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>127771592</v>
       </c>
       <c r="B104" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>127771610</v>
       </c>
       <c r="B105" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>127771374</v>
       </c>
       <c r="B106" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>127771580</v>
       </c>
       <c r="B107" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>127771400</v>
       </c>
       <c r="B108" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>127771435</v>
       </c>
       <c r="B109" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>127771389</v>
       </c>
       <c r="B110" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>127771462</v>
       </c>
       <c r="B111" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>127771555</v>
       </c>
       <c r="B112" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771414</v>
+        <v>127771396</v>
       </c>
       <c r="B113" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12519,10 +12519,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729205</v>
+        <v>729249</v>
       </c>
       <c r="R113" t="n">
-        <v>6367685</v>
+        <v>6367746</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12586,10 +12586,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771558</v>
+        <v>127771414</v>
       </c>
       <c r="B114" t="n">
-        <v>106310</v>
+        <v>106765</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12597,16 +12597,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12621,10 +12621,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729273</v>
+        <v>729205</v>
       </c>
       <c r="R114" t="n">
-        <v>6367508</v>
+        <v>6367685</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12688,10 +12688,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771577</v>
+        <v>127771558</v>
       </c>
       <c r="B115" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729275</v>
+        <v>729273</v>
       </c>
       <c r="R115" t="n">
-        <v>6367487</v>
+        <v>6367508</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12790,10 +12790,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771396</v>
+        <v>127771577</v>
       </c>
       <c r="B116" t="n">
-        <v>106764</v>
+        <v>106311</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12801,16 +12801,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12825,10 +12825,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729249</v>
+        <v>729275</v>
       </c>
       <c r="R116" t="n">
-        <v>6367746</v>
+        <v>6367487</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12892,10 +12892,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771458</v>
+        <v>127771439</v>
       </c>
       <c r="B117" t="n">
-        <v>103924</v>
+        <v>103925</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12927,10 +12927,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729130</v>
+        <v>729123</v>
       </c>
       <c r="R117" t="n">
-        <v>6367518</v>
+        <v>6367520</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771439</v>
+        <v>127771936</v>
       </c>
       <c r="B118" t="n">
-        <v>103924</v>
+        <v>57669</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13005,37 +13005,46 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729123</v>
+        <v>729289</v>
       </c>
       <c r="R118" t="n">
-        <v>6367520</v>
+        <v>6367518</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13078,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13096,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771936</v>
+        <v>127771458</v>
       </c>
       <c r="B119" t="n">
-        <v>57669</v>
+        <v>103925</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13107,46 +13116,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>220164</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729289</v>
+        <v>729130</v>
       </c>
       <c r="R119" t="n">
         <v>6367518</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4940,7 +4940,7 @@
         <v>127771423</v>
       </c>
       <c r="B40" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>127771574</v>
       </c>
       <c r="B41" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>127771431</v>
       </c>
       <c r="B42" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>127771437</v>
       </c>
       <c r="B44" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>127771363</v>
       </c>
       <c r="B45" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>127771381</v>
       </c>
       <c r="B46" t="n">
-        <v>107354</v>
+        <v>107355</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>127771608</v>
       </c>
       <c r="B47" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127771570</v>
+        <v>127771367</v>
       </c>
       <c r="B48" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729262</v>
+        <v>729279</v>
       </c>
       <c r="R48" t="n">
-        <v>6367486</v>
+        <v>6367813</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127771367</v>
+        <v>127771419</v>
       </c>
       <c r="B49" t="n">
-        <v>106311</v>
+        <v>106766</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5914,13 +5914,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729279</v>
+        <v>729198</v>
       </c>
       <c r="R49" t="n">
-        <v>6367813</v>
+        <v>6367656</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127771419</v>
+        <v>127771573</v>
       </c>
       <c r="B50" t="n">
-        <v>106765</v>
+        <v>106312</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,16 +5992,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729198</v>
+        <v>729265</v>
       </c>
       <c r="R50" t="n">
-        <v>6367656</v>
+        <v>6367490</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127771573</v>
+        <v>127771570</v>
       </c>
       <c r="B51" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729265</v>
+        <v>729262</v>
       </c>
       <c r="R51" t="n">
-        <v>6367490</v>
+        <v>6367486</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6188,7 +6188,7 @@
         <v>127771405</v>
       </c>
       <c r="B52" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>127771410</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>127771552</v>
       </c>
       <c r="B55" t="n">
-        <v>107354</v>
+        <v>107355</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>127771460</v>
       </c>
       <c r="B56" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127771421</v>
       </c>
       <c r="B57" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>127771565</v>
       </c>
       <c r="B58" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127771440</v>
+        <v>127771386</v>
       </c>
       <c r="B59" t="n">
-        <v>106311</v>
+        <v>106766</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6938,16 +6938,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>729123</v>
+        <v>729222</v>
       </c>
       <c r="R59" t="n">
-        <v>6367520</v>
+        <v>6367752</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127771386</v>
+        <v>127771440</v>
       </c>
       <c r="B60" t="n">
-        <v>106765</v>
+        <v>106312</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7040,16 +7040,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>729222</v>
+        <v>729123</v>
       </c>
       <c r="R60" t="n">
-        <v>6367752</v>
+        <v>6367520</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7134,7 +7134,7 @@
         <v>127771415</v>
       </c>
       <c r="B61" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127771390</v>
       </c>
       <c r="B62" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7335,10 +7335,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127771397</v>
+        <v>127771935</v>
       </c>
       <c r="B63" t="n">
-        <v>106311</v>
+        <v>57669</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,37 +7346,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>729249</v>
+        <v>729189</v>
       </c>
       <c r="R63" t="n">
-        <v>6367746</v>
+        <v>6367526</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7408,6 +7413,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre bo i nu fallen död tall.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7419,7 +7429,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7437,10 +7447,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127771463</v>
+        <v>127771397</v>
       </c>
       <c r="B64" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7472,10 +7482,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>729143</v>
+        <v>729249</v>
       </c>
       <c r="R64" t="n">
-        <v>6367517</v>
+        <v>6367746</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7521,7 +7531,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7539,10 +7549,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127771559</v>
+        <v>127771463</v>
       </c>
       <c r="B65" t="n">
-        <v>106765</v>
+        <v>106312</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7550,16 +7560,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7574,10 +7584,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>729273</v>
+        <v>729143</v>
       </c>
       <c r="R65" t="n">
-        <v>6367508</v>
+        <v>6367517</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7623,7 +7633,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7641,10 +7651,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127771935</v>
+        <v>127771559</v>
       </c>
       <c r="B66" t="n">
-        <v>57669</v>
+        <v>106766</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7652,42 +7662,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>729189</v>
+        <v>729273</v>
       </c>
       <c r="R66" t="n">
-        <v>6367526</v>
+        <v>6367508</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7719,11 +7724,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre bo i nu fallen död tall.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7756,7 +7756,7 @@
         <v>127771371</v>
       </c>
       <c r="B67" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>127771605</v>
       </c>
       <c r="B68" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>127771593</v>
       </c>
       <c r="B69" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>127771401</v>
       </c>
       <c r="B70" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>127771588</v>
       </c>
       <c r="B71" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127771564</v>
+        <v>127771387</v>
       </c>
       <c r="B72" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>729264</v>
+        <v>729222</v>
       </c>
       <c r="R72" t="n">
-        <v>6367501</v>
+        <v>6367752</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127771590</v>
+        <v>127771382</v>
       </c>
       <c r="B73" t="n">
-        <v>106311</v>
+        <v>106766</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>729268</v>
+        <v>729236</v>
       </c>
       <c r="R73" t="n">
-        <v>6367477</v>
+        <v>6367761</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8467,10 +8467,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127771387</v>
+        <v>127771562</v>
       </c>
       <c r="B74" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>729222</v>
+        <v>729266</v>
       </c>
       <c r="R74" t="n">
-        <v>6367752</v>
+        <v>6367511</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127771382</v>
+        <v>127771416</v>
       </c>
       <c r="B75" t="n">
-        <v>106765</v>
+        <v>106312</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8580,16 +8580,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729236</v>
+        <v>729198</v>
       </c>
       <c r="R75" t="n">
-        <v>6367761</v>
+        <v>6367656</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127771416</v>
+        <v>127771564</v>
       </c>
       <c r="B76" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>729198</v>
+        <v>729264</v>
       </c>
       <c r="R76" t="n">
-        <v>6367656</v>
+        <v>6367501</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8773,10 +8773,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127771562</v>
+        <v>127771590</v>
       </c>
       <c r="B77" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>729266</v>
+        <v>729268</v>
       </c>
       <c r="R77" t="n">
-        <v>6367511</v>
+        <v>6367477</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8878,7 +8878,7 @@
         <v>127771568</v>
       </c>
       <c r="B78" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>127771450</v>
       </c>
       <c r="B79" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9196,10 +9196,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127771586</v>
+        <v>127771366</v>
       </c>
       <c r="B81" t="n">
-        <v>106311</v>
+        <v>106766</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9207,16 +9207,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729260</v>
+        <v>729279</v>
       </c>
       <c r="R81" t="n">
-        <v>6367485</v>
+        <v>6367813</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9298,10 +9298,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127771366</v>
+        <v>127771392</v>
       </c>
       <c r="B82" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9333,13 +9333,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729279</v>
+        <v>729237</v>
       </c>
       <c r="R82" t="n">
-        <v>6367813</v>
+        <v>6367741</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9400,10 +9400,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127771392</v>
+        <v>127771586</v>
       </c>
       <c r="B83" t="n">
-        <v>106765</v>
+        <v>106312</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9411,16 +9411,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9435,13 +9435,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>729237</v>
+        <v>729260</v>
       </c>
       <c r="R83" t="n">
-        <v>6367741</v>
+        <v>6367485</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9505,7 +9505,7 @@
         <v>127771375</v>
       </c>
       <c r="B84" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>127771575</v>
       </c>
       <c r="B85" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>127771581</v>
       </c>
       <c r="B86" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>127771584</v>
       </c>
       <c r="B87" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127771393</v>
+        <v>127771466</v>
       </c>
       <c r="B88" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>729237</v>
+        <v>729154</v>
       </c>
       <c r="R88" t="n">
-        <v>6367741</v>
+        <v>6367521</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog , vid stig.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127771466</v>
+        <v>127771393</v>
       </c>
       <c r="B89" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>729154</v>
+        <v>729237</v>
       </c>
       <c r="R89" t="n">
-        <v>6367521</v>
+        <v>6367741</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkbarrskog , vid stig.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10228,7 +10228,7 @@
         <v>127771556</v>
       </c>
       <c r="B91" t="n">
-        <v>103925</v>
+        <v>103926</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>127771578</v>
       </c>
       <c r="B92" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>127771383</v>
       </c>
       <c r="B93" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>127771379</v>
       </c>
       <c r="B94" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>127771365</v>
       </c>
       <c r="B95" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10740,10 +10740,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127771429</v>
+        <v>127771929</v>
       </c>
       <c r="B96" t="n">
-        <v>106311</v>
+        <v>57669</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10751,34 +10751,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>729197</v>
+        <v>729237</v>
       </c>
       <c r="R96" t="n">
-        <v>6367641</v>
+        <v>6367741</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10813,6 +10818,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Födosöksspår i död tallåga med mycket rikligt med utgångshål för insekter.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10824,7 +10834,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -10842,10 +10852,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127771607</v>
+        <v>127771429</v>
       </c>
       <c r="B97" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10877,10 +10887,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>729264</v>
+        <v>729197</v>
       </c>
       <c r="R97" t="n">
-        <v>6367467</v>
+        <v>6367641</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10926,7 +10936,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -10944,10 +10954,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127771461</v>
+        <v>127771607</v>
       </c>
       <c r="B98" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10979,10 +10989,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>729130</v>
+        <v>729264</v>
       </c>
       <c r="R98" t="n">
-        <v>6367518</v>
+        <v>6367467</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11028,7 +11038,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11046,10 +11056,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127771929</v>
+        <v>127771461</v>
       </c>
       <c r="B99" t="n">
-        <v>57669</v>
+        <v>106312</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11057,39 +11067,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>729237</v>
+        <v>729130</v>
       </c>
       <c r="R99" t="n">
-        <v>6367741</v>
+        <v>6367518</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11124,11 +11129,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Födosöksspår i död tallåga med mycket rikligt med utgångshål för insekter.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11158,10 +11158,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127771378</v>
+        <v>127771604</v>
       </c>
       <c r="B100" t="n">
-        <v>106765</v>
+        <v>106312</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11169,16 +11169,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11193,10 +11193,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>729229</v>
+        <v>729268</v>
       </c>
       <c r="R100" t="n">
-        <v>6367768</v>
+        <v>6367470</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127771412</v>
+        <v>127771378</v>
       </c>
       <c r="B101" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11295,10 +11295,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>729227</v>
+        <v>729229</v>
       </c>
       <c r="R101" t="n">
-        <v>6367700</v>
+        <v>6367768</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127771604</v>
+        <v>127771412</v>
       </c>
       <c r="B102" t="n">
-        <v>106311</v>
+        <v>106766</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11373,16 +11373,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>729268</v>
+        <v>729227</v>
       </c>
       <c r="R102" t="n">
-        <v>6367470</v>
+        <v>6367700</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11467,7 +11467,7 @@
         <v>127771554</v>
       </c>
       <c r="B103" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>127771592</v>
       </c>
       <c r="B104" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>127771610</v>
       </c>
       <c r="B105" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>127771374</v>
       </c>
       <c r="B106" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>127771580</v>
       </c>
       <c r="B107" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>127771400</v>
       </c>
       <c r="B108" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12076,10 +12076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127771435</v>
+        <v>127771389</v>
       </c>
       <c r="B109" t="n">
-        <v>106311</v>
+        <v>106766</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12087,16 +12087,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>729159</v>
+        <v>729230</v>
       </c>
       <c r="R109" t="n">
-        <v>6367602</v>
+        <v>6367743</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127771389</v>
+        <v>127771462</v>
       </c>
       <c r="B110" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>729230</v>
+        <v>729143</v>
       </c>
       <c r="R110" t="n">
-        <v>6367743</v>
+        <v>6367517</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12280,10 +12280,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127771462</v>
+        <v>127771435</v>
       </c>
       <c r="B111" t="n">
-        <v>106765</v>
+        <v>106312</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12291,16 +12291,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>729143</v>
+        <v>729159</v>
       </c>
       <c r="R111" t="n">
-        <v>6367517</v>
+        <v>6367602</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12385,7 +12385,7 @@
         <v>127771555</v>
       </c>
       <c r="B112" t="n">
-        <v>106765</v>
+        <v>106766</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771396</v>
+        <v>127771936</v>
       </c>
       <c r="B113" t="n">
-        <v>106765</v>
+        <v>57669</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12495,37 +12495,46 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729249</v>
+        <v>729289</v>
       </c>
       <c r="R113" t="n">
-        <v>6367746</v>
+        <v>6367518</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12568,7 +12577,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12586,10 +12595,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771414</v>
+        <v>127771458</v>
       </c>
       <c r="B114" t="n">
-        <v>106765</v>
+        <v>103926</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12597,21 +12606,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12621,10 +12630,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729205</v>
+        <v>729130</v>
       </c>
       <c r="R114" t="n">
-        <v>6367685</v>
+        <v>6367518</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12670,7 +12679,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12688,10 +12697,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771558</v>
+        <v>127771439</v>
       </c>
       <c r="B115" t="n">
-        <v>106311</v>
+        <v>103926</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12699,21 +12708,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12723,10 +12732,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729273</v>
+        <v>729123</v>
       </c>
       <c r="R115" t="n">
-        <v>6367508</v>
+        <v>6367520</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12772,7 +12781,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12790,10 +12799,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771577</v>
+        <v>127771414</v>
       </c>
       <c r="B116" t="n">
-        <v>106311</v>
+        <v>106766</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12801,16 +12810,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12825,10 +12834,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729275</v>
+        <v>729205</v>
       </c>
       <c r="R116" t="n">
-        <v>6367487</v>
+        <v>6367685</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12874,7 +12883,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12892,10 +12901,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771439</v>
+        <v>127771396</v>
       </c>
       <c r="B117" t="n">
-        <v>103925</v>
+        <v>106766</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12903,21 +12912,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12927,10 +12936,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729123</v>
+        <v>729249</v>
       </c>
       <c r="R117" t="n">
-        <v>6367520</v>
+        <v>6367746</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12976,7 +12985,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -12994,10 +13003,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771936</v>
+        <v>127771558</v>
       </c>
       <c r="B118" t="n">
-        <v>57669</v>
+        <v>106312</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13005,46 +13014,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729289</v>
+        <v>729273</v>
       </c>
       <c r="R118" t="n">
-        <v>6367518</v>
+        <v>6367508</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771458</v>
+        <v>127771577</v>
       </c>
       <c r="B119" t="n">
-        <v>103925</v>
+        <v>106312</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13116,21 +13116,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729130</v>
+        <v>729275</v>
       </c>
       <c r="R119" t="n">
-        <v>6367518</v>
+        <v>6367487</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4825,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127771932</v>
+        <v>127771574</v>
       </c>
       <c r="B39" t="n">
-        <v>57669</v>
+        <v>106312</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,39 +4836,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729269</v>
+        <v>729271</v>
       </c>
       <c r="R39" t="n">
-        <v>6367727</v>
+        <v>6367489</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4903,11 +4898,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4919,7 +4909,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4937,7 +4927,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127771423</v>
+        <v>127771431</v>
       </c>
       <c r="B40" t="n">
         <v>106766</v>
@@ -4972,10 +4962,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729206</v>
+        <v>729197</v>
       </c>
       <c r="R40" t="n">
-        <v>6367643</v>
+        <v>6367641</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,11 +5000,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Röjd skog mot O.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5026,7 +5011,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5044,10 +5029,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127771574</v>
+        <v>127771932</v>
       </c>
       <c r="B41" t="n">
-        <v>106312</v>
+        <v>57669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5055,34 +5040,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729271</v>
+        <v>729269</v>
       </c>
       <c r="R41" t="n">
-        <v>6367489</v>
+        <v>6367727</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5117,6 +5107,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,7 +5123,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5146,7 +5141,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127771431</v>
+        <v>127771423</v>
       </c>
       <c r="B42" t="n">
         <v>106766</v>
@@ -5181,10 +5176,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729197</v>
+        <v>729206</v>
       </c>
       <c r="R42" t="n">
-        <v>6367641</v>
+        <v>6367643</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5219,6 +5214,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Röjd skog mot O.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127771367</v>
+        <v>127771570</v>
       </c>
       <c r="B48" t="n">
         <v>106312</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729279</v>
+        <v>729262</v>
       </c>
       <c r="R48" t="n">
-        <v>6367813</v>
+        <v>6367486</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127771419</v>
+        <v>127771367</v>
       </c>
       <c r="B49" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5914,13 +5914,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729198</v>
+        <v>729279</v>
       </c>
       <c r="R49" t="n">
-        <v>6367656</v>
+        <v>6367813</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127771573</v>
+        <v>127771419</v>
       </c>
       <c r="B50" t="n">
-        <v>106312</v>
+        <v>106766</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,16 +5992,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729265</v>
+        <v>729198</v>
       </c>
       <c r="R50" t="n">
-        <v>6367490</v>
+        <v>6367656</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6083,7 +6083,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127771570</v>
+        <v>127771573</v>
       </c>
       <c r="B51" t="n">
         <v>106312</v>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729262</v>
+        <v>729265</v>
       </c>
       <c r="R51" t="n">
-        <v>6367486</v>
+        <v>6367490</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6287,10 +6287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127771933</v>
+        <v>127771552</v>
       </c>
       <c r="B53" t="n">
-        <v>57669</v>
+        <v>107355</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6298,42 +6298,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729149</v>
+        <v>729282</v>
       </c>
       <c r="R53" t="n">
-        <v>6367526</v>
+        <v>6367498</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6365,11 +6369,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6381,7 +6380,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6510,10 +6509,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771552</v>
+        <v>127771933</v>
       </c>
       <c r="B55" t="n">
-        <v>107355</v>
+        <v>57669</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6521,46 +6520,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729282</v>
+        <v>729149</v>
       </c>
       <c r="R55" t="n">
-        <v>6367498</v>
+        <v>6367526</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6592,6 +6587,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127771386</v>
+        <v>127771440</v>
       </c>
       <c r="B59" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6938,16 +6938,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>729222</v>
+        <v>729123</v>
       </c>
       <c r="R59" t="n">
-        <v>6367752</v>
+        <v>6367520</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127771440</v>
+        <v>127771386</v>
       </c>
       <c r="B60" t="n">
-        <v>106312</v>
+        <v>106766</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7040,16 +7040,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>729123</v>
+        <v>729222</v>
       </c>
       <c r="R60" t="n">
-        <v>6367520</v>
+        <v>6367752</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8263,7 +8263,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127771387</v>
+        <v>127771564</v>
       </c>
       <c r="B72" t="n">
         <v>106312</v>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>729222</v>
+        <v>729264</v>
       </c>
       <c r="R72" t="n">
-        <v>6367752</v>
+        <v>6367501</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127771382</v>
+        <v>127771590</v>
       </c>
       <c r="B73" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>729236</v>
+        <v>729268</v>
       </c>
       <c r="R73" t="n">
-        <v>6367761</v>
+        <v>6367477</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8467,7 +8467,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127771562</v>
+        <v>127771387</v>
       </c>
       <c r="B74" t="n">
         <v>106312</v>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>729266</v>
+        <v>729222</v>
       </c>
       <c r="R74" t="n">
-        <v>6367511</v>
+        <v>6367752</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127771416</v>
+        <v>127771382</v>
       </c>
       <c r="B75" t="n">
-        <v>106312</v>
+        <v>106766</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8580,16 +8580,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729198</v>
+        <v>729236</v>
       </c>
       <c r="R75" t="n">
-        <v>6367656</v>
+        <v>6367761</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8671,7 +8671,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127771564</v>
+        <v>127771416</v>
       </c>
       <c r="B76" t="n">
         <v>106312</v>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>729264</v>
+        <v>729198</v>
       </c>
       <c r="R76" t="n">
-        <v>6367501</v>
+        <v>6367656</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8773,7 +8773,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127771590</v>
+        <v>127771562</v>
       </c>
       <c r="B77" t="n">
         <v>106312</v>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>729268</v>
+        <v>729266</v>
       </c>
       <c r="R77" t="n">
-        <v>6367477</v>
+        <v>6367511</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127771931</v>
+        <v>127771586</v>
       </c>
       <c r="B80" t="n">
-        <v>57669</v>
+        <v>106312</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9095,39 +9095,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R80" t="n">
-        <v>6367746</v>
+        <v>6367485</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9162,11 +9157,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9178,7 +9168,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9400,10 +9390,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127771586</v>
+        <v>127771931</v>
       </c>
       <c r="B83" t="n">
-        <v>106312</v>
+        <v>57669</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9411,34 +9401,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R83" t="n">
-        <v>6367485</v>
+        <v>6367746</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9473,6 +9468,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9910,7 +9910,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127771466</v>
+        <v>127771393</v>
       </c>
       <c r="B88" t="n">
         <v>106312</v>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>729154</v>
+        <v>729237</v>
       </c>
       <c r="R88" t="n">
-        <v>6367521</v>
+        <v>6367741</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Kalkbarrskog , vid stig.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10012,7 +10012,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127771393</v>
+        <v>127771466</v>
       </c>
       <c r="B89" t="n">
         <v>106312</v>
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>729237</v>
+        <v>729154</v>
       </c>
       <c r="R89" t="n">
-        <v>6367741</v>
+        <v>6367521</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog , vid stig.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11158,10 +11158,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127771604</v>
+        <v>127771378</v>
       </c>
       <c r="B100" t="n">
-        <v>106312</v>
+        <v>106766</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11169,16 +11169,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11193,10 +11193,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>729268</v>
+        <v>729229</v>
       </c>
       <c r="R100" t="n">
-        <v>6367470</v>
+        <v>6367768</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11260,7 +11260,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127771378</v>
+        <v>127771412</v>
       </c>
       <c r="B101" t="n">
         <v>106766</v>
@@ -11295,10 +11295,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>729229</v>
+        <v>729227</v>
       </c>
       <c r="R101" t="n">
-        <v>6367768</v>
+        <v>6367700</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127771412</v>
+        <v>127771604</v>
       </c>
       <c r="B102" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11373,16 +11373,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>729227</v>
+        <v>729268</v>
       </c>
       <c r="R102" t="n">
-        <v>6367700</v>
+        <v>6367470</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127771389</v>
+        <v>127771435</v>
       </c>
       <c r="B109" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12087,16 +12087,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>729230</v>
+        <v>729159</v>
       </c>
       <c r="R109" t="n">
-        <v>6367743</v>
+        <v>6367602</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12178,7 +12178,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127771462</v>
+        <v>127771389</v>
       </c>
       <c r="B110" t="n">
         <v>106766</v>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>729143</v>
+        <v>729230</v>
       </c>
       <c r="R110" t="n">
-        <v>6367517</v>
+        <v>6367743</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12280,10 +12280,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127771435</v>
+        <v>127771462</v>
       </c>
       <c r="B111" t="n">
-        <v>106312</v>
+        <v>106766</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12291,16 +12291,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>729159</v>
+        <v>729143</v>
       </c>
       <c r="R111" t="n">
-        <v>6367602</v>
+        <v>6367517</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12595,10 +12595,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771458</v>
+        <v>127771414</v>
       </c>
       <c r="B114" t="n">
-        <v>103926</v>
+        <v>106766</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12606,21 +12606,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729130</v>
+        <v>729205</v>
       </c>
       <c r="R114" t="n">
-        <v>6367518</v>
+        <v>6367685</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12697,10 +12697,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771439</v>
+        <v>127771558</v>
       </c>
       <c r="B115" t="n">
-        <v>103926</v>
+        <v>106312</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12708,21 +12708,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729123</v>
+        <v>729273</v>
       </c>
       <c r="R115" t="n">
-        <v>6367520</v>
+        <v>6367508</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12799,10 +12799,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771414</v>
+        <v>127771577</v>
       </c>
       <c r="B116" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12810,16 +12810,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12834,10 +12834,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729205</v>
+        <v>729275</v>
       </c>
       <c r="R116" t="n">
-        <v>6367685</v>
+        <v>6367487</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771558</v>
+        <v>127771458</v>
       </c>
       <c r="B118" t="n">
-        <v>106312</v>
+        <v>103926</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13014,21 +13014,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729273</v>
+        <v>729130</v>
       </c>
       <c r="R118" t="n">
-        <v>6367508</v>
+        <v>6367518</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771577</v>
+        <v>127771439</v>
       </c>
       <c r="B119" t="n">
-        <v>106312</v>
+        <v>103926</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13116,21 +13116,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729275</v>
+        <v>729123</v>
       </c>
       <c r="R119" t="n">
-        <v>6367487</v>
+        <v>6367520</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -6287,10 +6287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127771552</v>
+        <v>127771933</v>
       </c>
       <c r="B53" t="n">
-        <v>107355</v>
+        <v>57669</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6298,46 +6298,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729282</v>
+        <v>729149</v>
       </c>
       <c r="R53" t="n">
-        <v>6367498</v>
+        <v>6367526</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6369,6 +6365,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6380,7 +6381,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6398,32 +6399,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771410</v>
+        <v>127771552</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>107355</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6442,10 +6443,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729272</v>
+        <v>729282</v>
       </c>
       <c r="R54" t="n">
-        <v>6367702</v>
+        <v>6367498</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6491,7 +6492,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6509,53 +6510,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771933</v>
+        <v>127771410</v>
       </c>
       <c r="B55" t="n">
-        <v>57669</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729149</v>
+        <v>729272</v>
       </c>
       <c r="R55" t="n">
-        <v>6367526</v>
+        <v>6367702</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6587,11 +6592,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -12595,10 +12595,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771414</v>
+        <v>127771458</v>
       </c>
       <c r="B114" t="n">
-        <v>106766</v>
+        <v>103926</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12606,21 +12606,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729205</v>
+        <v>729130</v>
       </c>
       <c r="R114" t="n">
-        <v>6367685</v>
+        <v>6367518</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12697,10 +12697,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771558</v>
+        <v>127771439</v>
       </c>
       <c r="B115" t="n">
-        <v>106312</v>
+        <v>103926</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12708,21 +12708,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729273</v>
+        <v>729123</v>
       </c>
       <c r="R115" t="n">
-        <v>6367508</v>
+        <v>6367520</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12799,10 +12799,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771577</v>
+        <v>127771414</v>
       </c>
       <c r="B116" t="n">
-        <v>106312</v>
+        <v>106766</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12810,16 +12810,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12834,10 +12834,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729275</v>
+        <v>729205</v>
       </c>
       <c r="R116" t="n">
-        <v>6367487</v>
+        <v>6367685</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12901,10 +12901,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771396</v>
+        <v>127771558</v>
       </c>
       <c r="B117" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12912,16 +12912,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12936,10 +12936,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729249</v>
+        <v>729273</v>
       </c>
       <c r="R117" t="n">
-        <v>6367746</v>
+        <v>6367508</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771458</v>
+        <v>127771577</v>
       </c>
       <c r="B118" t="n">
-        <v>103926</v>
+        <v>106312</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13014,21 +13014,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729130</v>
+        <v>729275</v>
       </c>
       <c r="R118" t="n">
-        <v>6367518</v>
+        <v>6367487</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771439</v>
+        <v>127771396</v>
       </c>
       <c r="B119" t="n">
-        <v>103926</v>
+        <v>106766</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13116,21 +13116,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729123</v>
+        <v>729249</v>
       </c>
       <c r="R119" t="n">
-        <v>6367520</v>
+        <v>6367746</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4825,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127771574</v>
+        <v>127771932</v>
       </c>
       <c r="B39" t="n">
-        <v>106312</v>
+        <v>57669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,34 +4836,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729271</v>
+        <v>729269</v>
       </c>
       <c r="R39" t="n">
-        <v>6367489</v>
+        <v>6367727</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4898,6 +4903,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4909,7 +4919,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4927,7 +4937,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127771431</v>
+        <v>127771423</v>
       </c>
       <c r="B40" t="n">
         <v>106766</v>
@@ -4962,10 +4972,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729197</v>
+        <v>729206</v>
       </c>
       <c r="R40" t="n">
-        <v>6367641</v>
+        <v>6367643</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5000,6 +5010,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Röjd skog mot O.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5011,7 +5026,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5029,10 +5044,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127771932</v>
+        <v>127771574</v>
       </c>
       <c r="B41" t="n">
-        <v>57669</v>
+        <v>106312</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5040,39 +5055,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729269</v>
+        <v>729271</v>
       </c>
       <c r="R41" t="n">
-        <v>6367727</v>
+        <v>6367489</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5107,11 +5117,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5123,7 +5128,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5141,7 +5146,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127771423</v>
+        <v>127771431</v>
       </c>
       <c r="B42" t="n">
         <v>106766</v>
@@ -5176,10 +5181,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729206</v>
+        <v>729197</v>
       </c>
       <c r="R42" t="n">
-        <v>6367643</v>
+        <v>6367641</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5214,11 +5219,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Röjd skog mot O.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -12595,10 +12595,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771458</v>
+        <v>127771414</v>
       </c>
       <c r="B114" t="n">
-        <v>103926</v>
+        <v>106766</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12606,21 +12606,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729130</v>
+        <v>729205</v>
       </c>
       <c r="R114" t="n">
-        <v>6367518</v>
+        <v>6367685</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12697,10 +12697,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771439</v>
+        <v>127771558</v>
       </c>
       <c r="B115" t="n">
-        <v>103926</v>
+        <v>106312</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12708,21 +12708,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729123</v>
+        <v>729273</v>
       </c>
       <c r="R115" t="n">
-        <v>6367520</v>
+        <v>6367508</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12799,10 +12799,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771414</v>
+        <v>127771577</v>
       </c>
       <c r="B116" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12810,16 +12810,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12834,10 +12834,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729205</v>
+        <v>729275</v>
       </c>
       <c r="R116" t="n">
-        <v>6367685</v>
+        <v>6367487</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12901,10 +12901,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771558</v>
+        <v>127771396</v>
       </c>
       <c r="B117" t="n">
-        <v>106312</v>
+        <v>106766</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12912,16 +12912,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12936,10 +12936,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729273</v>
+        <v>729249</v>
       </c>
       <c r="R117" t="n">
-        <v>6367508</v>
+        <v>6367746</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771577</v>
+        <v>127771458</v>
       </c>
       <c r="B118" t="n">
-        <v>106312</v>
+        <v>103926</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13014,21 +13014,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729275</v>
+        <v>729130</v>
       </c>
       <c r="R118" t="n">
-        <v>6367487</v>
+        <v>6367518</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771396</v>
+        <v>127771439</v>
       </c>
       <c r="B119" t="n">
-        <v>106766</v>
+        <v>103926</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13116,21 +13116,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729249</v>
+        <v>729123</v>
       </c>
       <c r="R119" t="n">
-        <v>6367746</v>
+        <v>6367520</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4825,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127771932</v>
+        <v>127771574</v>
       </c>
       <c r="B39" t="n">
-        <v>57669</v>
+        <v>106312</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,39 +4836,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729269</v>
+        <v>729271</v>
       </c>
       <c r="R39" t="n">
-        <v>6367727</v>
+        <v>6367489</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4903,11 +4898,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4919,7 +4909,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4937,7 +4927,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127771423</v>
+        <v>127771431</v>
       </c>
       <c r="B40" t="n">
         <v>106766</v>
@@ -4972,10 +4962,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729206</v>
+        <v>729197</v>
       </c>
       <c r="R40" t="n">
-        <v>6367643</v>
+        <v>6367641</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,11 +5000,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Röjd skog mot O.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5026,7 +5011,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5044,10 +5029,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127771574</v>
+        <v>127771932</v>
       </c>
       <c r="B41" t="n">
-        <v>106312</v>
+        <v>57669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5055,34 +5040,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729271</v>
+        <v>729269</v>
       </c>
       <c r="R41" t="n">
-        <v>6367489</v>
+        <v>6367727</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5117,6 +5107,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,7 +5123,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5146,7 +5141,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127771431</v>
+        <v>127771423</v>
       </c>
       <c r="B42" t="n">
         <v>106766</v>
@@ -5181,10 +5176,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729197</v>
+        <v>729206</v>
       </c>
       <c r="R42" t="n">
-        <v>6367641</v>
+        <v>6367643</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5219,6 +5214,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Röjd skog mot O.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -10225,10 +10225,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771556</v>
+        <v>127771578</v>
       </c>
       <c r="B91" t="n">
-        <v>103926</v>
+        <v>106766</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10236,21 +10236,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10260,10 +10260,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729273</v>
+        <v>729275</v>
       </c>
       <c r="R91" t="n">
-        <v>6367508</v>
+        <v>6367487</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10327,10 +10327,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127771578</v>
+        <v>127771383</v>
       </c>
       <c r="B92" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10338,16 +10338,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10362,10 +10362,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>729275</v>
+        <v>729236</v>
       </c>
       <c r="R92" t="n">
-        <v>6367487</v>
+        <v>6367761</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10429,10 +10429,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771383</v>
+        <v>127771556</v>
       </c>
       <c r="B93" t="n">
-        <v>106312</v>
+        <v>103926</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729236</v>
+        <v>729273</v>
       </c>
       <c r="R93" t="n">
-        <v>6367761</v>
+        <v>6367508</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -12595,10 +12595,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771414</v>
+        <v>127771458</v>
       </c>
       <c r="B114" t="n">
-        <v>106766</v>
+        <v>103926</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12606,21 +12606,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729205</v>
+        <v>729130</v>
       </c>
       <c r="R114" t="n">
-        <v>6367685</v>
+        <v>6367518</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12697,10 +12697,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771558</v>
+        <v>127771439</v>
       </c>
       <c r="B115" t="n">
-        <v>106312</v>
+        <v>103926</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12708,21 +12708,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729273</v>
+        <v>729123</v>
       </c>
       <c r="R115" t="n">
-        <v>6367508</v>
+        <v>6367520</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12799,10 +12799,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771577</v>
+        <v>127771414</v>
       </c>
       <c r="B116" t="n">
-        <v>106312</v>
+        <v>106766</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12810,16 +12810,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12834,10 +12834,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729275</v>
+        <v>729205</v>
       </c>
       <c r="R116" t="n">
-        <v>6367487</v>
+        <v>6367685</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12901,10 +12901,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771396</v>
+        <v>127771558</v>
       </c>
       <c r="B117" t="n">
-        <v>106766</v>
+        <v>106312</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12912,16 +12912,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12936,10 +12936,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729249</v>
+        <v>729273</v>
       </c>
       <c r="R117" t="n">
-        <v>6367746</v>
+        <v>6367508</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771458</v>
+        <v>127771577</v>
       </c>
       <c r="B118" t="n">
-        <v>103926</v>
+        <v>106312</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13014,21 +13014,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729130</v>
+        <v>729275</v>
       </c>
       <c r="R118" t="n">
-        <v>6367518</v>
+        <v>6367487</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771439</v>
+        <v>127771396</v>
       </c>
       <c r="B119" t="n">
-        <v>103926</v>
+        <v>106766</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13116,21 +13116,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729123</v>
+        <v>729249</v>
       </c>
       <c r="R119" t="n">
-        <v>6367520</v>
+        <v>6367746</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY119"/>
+  <dimension ref="A1:AY121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4825,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127771932</v>
+        <v>127771574</v>
       </c>
       <c r="B39" t="n">
-        <v>57669</v>
+        <v>106312</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,39 +4836,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729269</v>
+        <v>729271</v>
       </c>
       <c r="R39" t="n">
-        <v>6367727</v>
+        <v>6367489</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4903,11 +4898,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4919,7 +4909,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4937,7 +4927,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127771423</v>
+        <v>127771431</v>
       </c>
       <c r="B40" t="n">
         <v>106766</v>
@@ -4972,10 +4962,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729206</v>
+        <v>729197</v>
       </c>
       <c r="R40" t="n">
-        <v>6367643</v>
+        <v>6367641</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,11 +5000,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Röjd skog mot O.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5026,7 +5011,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5044,10 +5029,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127771574</v>
+        <v>127771932</v>
       </c>
       <c r="B41" t="n">
-        <v>106312</v>
+        <v>57669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5055,34 +5040,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729271</v>
+        <v>729269</v>
       </c>
       <c r="R41" t="n">
-        <v>6367489</v>
+        <v>6367727</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5117,6 +5107,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,7 +5123,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5146,7 +5141,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127771431</v>
+        <v>127771423</v>
       </c>
       <c r="B42" t="n">
         <v>106766</v>
@@ -5181,10 +5176,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729197</v>
+        <v>729206</v>
       </c>
       <c r="R42" t="n">
-        <v>6367641</v>
+        <v>6367643</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5219,6 +5214,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Röjd skog mot O.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -13205,6 +13205,220 @@
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128472799</v>
+      </c>
+      <c r="B120" t="n">
+        <v>86845</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>449</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6367544</v>
+      </c>
+      <c r="S120" t="n">
+        <v>50</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Lisa Wallström</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Lisa Wallström</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128473008</v>
+      </c>
+      <c r="B121" t="n">
+        <v>86786</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6367544</v>
+      </c>
+      <c r="S121" t="n">
+        <v>50</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Lisa Wallström</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Lisa Wallström</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4825,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127771574</v>
+        <v>127771932</v>
       </c>
       <c r="B39" t="n">
-        <v>106312</v>
+        <v>57670</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,34 +4836,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729271</v>
+        <v>729269</v>
       </c>
       <c r="R39" t="n">
-        <v>6367489</v>
+        <v>6367727</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4898,6 +4903,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4909,7 +4919,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4927,10 +4937,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127771431</v>
+        <v>127771574</v>
       </c>
       <c r="B40" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4938,16 +4948,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4962,10 +4972,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729197</v>
+        <v>729271</v>
       </c>
       <c r="R40" t="n">
-        <v>6367641</v>
+        <v>6367489</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5011,7 +5021,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5029,10 +5039,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127771932</v>
+        <v>127771423</v>
       </c>
       <c r="B41" t="n">
-        <v>57669</v>
+        <v>106774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5040,39 +5050,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729269</v>
+        <v>729206</v>
       </c>
       <c r="R41" t="n">
-        <v>6367727</v>
+        <v>6367643</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5109,7 +5114,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+          <t>Röjd skog mot O.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5123,7 +5128,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5141,10 +5146,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127771423</v>
+        <v>127771431</v>
       </c>
       <c r="B42" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5176,10 +5181,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729206</v>
+        <v>729197</v>
       </c>
       <c r="R42" t="n">
-        <v>6367643</v>
+        <v>6367641</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5214,11 +5219,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Röjd skog mot O.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127771857</v>
+        <v>127771437</v>
       </c>
       <c r="B43" t="n">
-        <v>5493</v>
+        <v>106774</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,21 +5259,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101410</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729268</v>
+        <v>729159</v>
       </c>
       <c r="R43" t="n">
-        <v>6367746</v>
+        <v>6367602</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5321,11 +5321,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Tall med angrepp.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5337,7 +5332,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5355,10 +5350,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127771437</v>
+        <v>127771857</v>
       </c>
       <c r="B44" t="n">
-        <v>106766</v>
+        <v>5493</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5366,21 +5361,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221849</v>
+        <v>101410</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5390,10 +5385,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>729159</v>
+        <v>729268</v>
       </c>
       <c r="R44" t="n">
-        <v>6367602</v>
+        <v>6367746</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5428,6 +5423,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Tall med angrepp.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5460,7 +5460,7 @@
         <v>127771363</v>
       </c>
       <c r="B45" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>127771381</v>
       </c>
       <c r="B46" t="n">
-        <v>107355</v>
+        <v>107363</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127771608</v>
+        <v>127771570</v>
       </c>
       <c r="B47" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5686,16 +5686,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729267</v>
+        <v>729262</v>
       </c>
       <c r="R47" t="n">
-        <v>6367464</v>
+        <v>6367486</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127771570</v>
+        <v>127771573</v>
       </c>
       <c r="B48" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729262</v>
+        <v>729265</v>
       </c>
       <c r="R48" t="n">
-        <v>6367486</v>
+        <v>6367490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5879,10 +5879,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127771367</v>
+        <v>127771405</v>
       </c>
       <c r="B49" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5914,13 +5914,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729279</v>
+        <v>729259</v>
       </c>
       <c r="R49" t="n">
-        <v>6367813</v>
+        <v>6367748</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127771419</v>
+        <v>127771608</v>
       </c>
       <c r="B50" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729198</v>
+        <v>729267</v>
       </c>
       <c r="R50" t="n">
-        <v>6367656</v>
+        <v>6367464</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127771573</v>
+        <v>127771367</v>
       </c>
       <c r="B51" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,13 +6118,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729265</v>
+        <v>729279</v>
       </c>
       <c r="R51" t="n">
-        <v>6367490</v>
+        <v>6367813</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127771405</v>
+        <v>127771419</v>
       </c>
       <c r="B52" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6196,16 +6196,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6220,10 +6220,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R52" t="n">
-        <v>6367748</v>
+        <v>6367656</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6287,53 +6287,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127771933</v>
+        <v>127771410</v>
       </c>
       <c r="B53" t="n">
-        <v>57669</v>
+        <v>98456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729149</v>
+        <v>729272</v>
       </c>
       <c r="R53" t="n">
-        <v>6367526</v>
+        <v>6367702</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6365,11 +6369,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6381,7 +6380,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6399,10 +6398,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771552</v>
+        <v>127771460</v>
       </c>
       <c r="B54" t="n">
-        <v>107355</v>
+        <v>106774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6410,43 +6409,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729282</v>
+        <v>729130</v>
       </c>
       <c r="R54" t="n">
-        <v>6367498</v>
+        <v>6367518</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6492,7 +6482,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6510,54 +6500,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771410</v>
+        <v>127771421</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>106774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729272</v>
+        <v>729214</v>
       </c>
       <c r="R55" t="n">
-        <v>6367702</v>
+        <v>6367664</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6603,7 +6584,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6621,10 +6602,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771460</v>
+        <v>127771565</v>
       </c>
       <c r="B56" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6656,10 +6637,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729130</v>
+        <v>729264</v>
       </c>
       <c r="R56" t="n">
-        <v>6367518</v>
+        <v>6367501</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6705,7 +6686,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6723,10 +6704,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771421</v>
+        <v>127771552</v>
       </c>
       <c r="B57" t="n">
-        <v>106766</v>
+        <v>107363</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6734,34 +6715,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729214</v>
+        <v>729282</v>
       </c>
       <c r="R57" t="n">
-        <v>6367664</v>
+        <v>6367498</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6807,7 +6797,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6825,10 +6815,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127771565</v>
+        <v>127771933</v>
       </c>
       <c r="B58" t="n">
-        <v>106766</v>
+        <v>57670</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6836,37 +6826,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729264</v>
+        <v>729149</v>
       </c>
       <c r="R58" t="n">
-        <v>6367501</v>
+        <v>6367526</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6898,6 +6893,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6930,7 +6930,7 @@
         <v>127771440</v>
       </c>
       <c r="B59" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127771386</v>
+        <v>127771415</v>
       </c>
       <c r="B60" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7040,16 +7040,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>729222</v>
+        <v>729205</v>
       </c>
       <c r="R60" t="n">
-        <v>6367752</v>
+        <v>6367685</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127771415</v>
+        <v>127771386</v>
       </c>
       <c r="B61" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7142,16 +7142,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>729205</v>
+        <v>729222</v>
       </c>
       <c r="R61" t="n">
-        <v>6367685</v>
+        <v>6367752</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
         <v>127771390</v>
       </c>
       <c r="B62" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7335,10 +7335,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127771935</v>
+        <v>127771559</v>
       </c>
       <c r="B63" t="n">
-        <v>57669</v>
+        <v>106774</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,42 +7346,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>729189</v>
+        <v>729273</v>
       </c>
       <c r="R63" t="n">
-        <v>6367526</v>
+        <v>6367508</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7413,11 +7408,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre bo i nu fallen död tall.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7429,7 +7419,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7450,7 +7440,7 @@
         <v>127771397</v>
       </c>
       <c r="B64" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7552,7 +7542,7 @@
         <v>127771463</v>
       </c>
       <c r="B65" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7651,10 +7641,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127771559</v>
+        <v>127771935</v>
       </c>
       <c r="B66" t="n">
-        <v>106766</v>
+        <v>57670</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7662,37 +7652,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>729273</v>
+        <v>729189</v>
       </c>
       <c r="R66" t="n">
-        <v>6367508</v>
+        <v>6367526</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7724,6 +7719,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre bo i nu fallen död tall.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7753,10 +7753,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127771371</v>
+        <v>127771401</v>
       </c>
       <c r="B67" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>729244</v>
+        <v>729249</v>
       </c>
       <c r="R67" t="n">
-        <v>6367780</v>
+        <v>6367753</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7855,10 +7855,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127771605</v>
+        <v>127771371</v>
       </c>
       <c r="B68" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>729264</v>
+        <v>729244</v>
       </c>
       <c r="R68" t="n">
-        <v>6367467</v>
+        <v>6367780</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7957,10 +7957,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127771593</v>
+        <v>127771605</v>
       </c>
       <c r="B69" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>729273</v>
+        <v>729264</v>
       </c>
       <c r="R69" t="n">
-        <v>6367480</v>
+        <v>6367467</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127771401</v>
+        <v>127771593</v>
       </c>
       <c r="B70" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8070,16 +8070,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>729249</v>
+        <v>729273</v>
       </c>
       <c r="R70" t="n">
-        <v>6367753</v>
+        <v>6367480</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8164,7 +8164,7 @@
         <v>127771588</v>
       </c>
       <c r="B71" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>127771564</v>
       </c>
       <c r="B72" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>127771590</v>
       </c>
       <c r="B73" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>127771387</v>
       </c>
       <c r="B74" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127771382</v>
+        <v>127771562</v>
       </c>
       <c r="B75" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8580,16 +8580,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729236</v>
+        <v>729266</v>
       </c>
       <c r="R75" t="n">
-        <v>6367761</v>
+        <v>6367511</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127771416</v>
+        <v>127771382</v>
       </c>
       <c r="B76" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8682,16 +8682,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>729198</v>
+        <v>729236</v>
       </c>
       <c r="R76" t="n">
-        <v>6367656</v>
+        <v>6367761</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8773,10 +8773,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127771562</v>
+        <v>127771416</v>
       </c>
       <c r="B77" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>729266</v>
+        <v>729198</v>
       </c>
       <c r="R77" t="n">
-        <v>6367511</v>
+        <v>6367656</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8878,7 +8878,7 @@
         <v>127771568</v>
       </c>
       <c r="B78" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>127771450</v>
       </c>
       <c r="B79" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127771586</v>
+        <v>127771366</v>
       </c>
       <c r="B80" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9095,16 +9095,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729260</v>
+        <v>729279</v>
       </c>
       <c r="R80" t="n">
-        <v>6367485</v>
+        <v>6367813</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9186,10 +9186,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127771366</v>
+        <v>127771392</v>
       </c>
       <c r="B81" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9221,13 +9221,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729279</v>
+        <v>729237</v>
       </c>
       <c r="R81" t="n">
-        <v>6367813</v>
+        <v>6367741</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127771392</v>
+        <v>127771586</v>
       </c>
       <c r="B82" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9299,16 +9299,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9323,13 +9323,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729237</v>
+        <v>729260</v>
       </c>
       <c r="R82" t="n">
-        <v>6367741</v>
+        <v>6367485</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9393,7 +9393,7 @@
         <v>127771931</v>
       </c>
       <c r="B83" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>127771375</v>
       </c>
       <c r="B84" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9604,10 +9604,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127771575</v>
+        <v>127771584</v>
       </c>
       <c r="B85" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9615,16 +9615,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>729271</v>
+        <v>729267</v>
       </c>
       <c r="R85" t="n">
-        <v>6367489</v>
+        <v>6367487</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9706,10 +9706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127771581</v>
+        <v>127771393</v>
       </c>
       <c r="B86" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9717,16 +9717,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>729272</v>
+        <v>729237</v>
       </c>
       <c r="R86" t="n">
-        <v>6367485</v>
+        <v>6367741</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127771584</v>
+        <v>127771466</v>
       </c>
       <c r="B87" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>729267</v>
+        <v>729154</v>
       </c>
       <c r="R87" t="n">
-        <v>6367487</v>
+        <v>6367521</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog , vid stig.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127771393</v>
+        <v>127771575</v>
       </c>
       <c r="B88" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9921,16 +9921,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>729237</v>
+        <v>729271</v>
       </c>
       <c r="R88" t="n">
-        <v>6367741</v>
+        <v>6367489</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127771466</v>
+        <v>127771581</v>
       </c>
       <c r="B89" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10023,16 +10023,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>729154</v>
+        <v>729272</v>
       </c>
       <c r="R89" t="n">
-        <v>6367521</v>
+        <v>6367485</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkbarrskog , vid stig.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127771930</v>
+        <v>127771556</v>
       </c>
       <c r="B90" t="n">
-        <v>57685</v>
+        <v>103934</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10125,46 +10125,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100048</v>
+        <v>220164</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>729246</v>
+        <v>729273</v>
       </c>
       <c r="R90" t="n">
-        <v>6367767</v>
+        <v>6367508</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10207,7 +10198,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10225,10 +10216,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771578</v>
+        <v>127771383</v>
       </c>
       <c r="B91" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10236,16 +10227,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10260,10 +10251,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729275</v>
+        <v>729236</v>
       </c>
       <c r="R91" t="n">
-        <v>6367487</v>
+        <v>6367761</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10309,7 +10300,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10327,10 +10318,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127771383</v>
+        <v>127771578</v>
       </c>
       <c r="B92" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10338,16 +10329,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10362,10 +10353,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>729236</v>
+        <v>729275</v>
       </c>
       <c r="R92" t="n">
-        <v>6367761</v>
+        <v>6367487</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10411,7 +10402,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10429,10 +10420,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771556</v>
+        <v>127771930</v>
       </c>
       <c r="B93" t="n">
-        <v>103926</v>
+        <v>57686</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10440,37 +10431,46 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220164</v>
+        <v>100048</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729273</v>
+        <v>729246</v>
       </c>
       <c r="R93" t="n">
-        <v>6367508</v>
+        <v>6367767</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10534,7 +10534,7 @@
         <v>127771379</v>
       </c>
       <c r="B94" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>127771365</v>
       </c>
       <c r="B95" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>127771929</v>
       </c>
       <c r="B96" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>127771429</v>
       </c>
       <c r="B97" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>127771607</v>
       </c>
       <c r="B98" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>127771461</v>
       </c>
       <c r="B99" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11158,10 +11158,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127771378</v>
+        <v>127771604</v>
       </c>
       <c r="B100" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11169,16 +11169,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11193,10 +11193,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>729229</v>
+        <v>729268</v>
       </c>
       <c r="R100" t="n">
-        <v>6367768</v>
+        <v>6367470</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127771412</v>
+        <v>127771554</v>
       </c>
       <c r="B101" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11295,10 +11295,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>729227</v>
+        <v>729277</v>
       </c>
       <c r="R101" t="n">
-        <v>6367700</v>
+        <v>6367499</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127771604</v>
+        <v>127771592</v>
       </c>
       <c r="B102" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>729268</v>
+        <v>729273</v>
       </c>
       <c r="R102" t="n">
-        <v>6367470</v>
+        <v>6367480</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11464,10 +11464,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127771554</v>
+        <v>127771378</v>
       </c>
       <c r="B103" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11475,16 +11475,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>729277</v>
+        <v>729229</v>
       </c>
       <c r="R103" t="n">
-        <v>6367499</v>
+        <v>6367768</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -11566,10 +11566,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127771592</v>
+        <v>127771412</v>
       </c>
       <c r="B104" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11577,16 +11577,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11601,10 +11601,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>729273</v>
+        <v>729227</v>
       </c>
       <c r="R104" t="n">
-        <v>6367480</v>
+        <v>6367700</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -11668,10 +11668,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127771610</v>
+        <v>127771580</v>
       </c>
       <c r="B105" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>729267</v>
+        <v>729272</v>
       </c>
       <c r="R105" t="n">
-        <v>6367464</v>
+        <v>6367485</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11770,10 +11770,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127771374</v>
+        <v>127771610</v>
       </c>
       <c r="B106" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11781,16 +11781,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>729236</v>
+        <v>729267</v>
       </c>
       <c r="R106" t="n">
-        <v>6367778</v>
+        <v>6367464</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -11872,10 +11872,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127771580</v>
+        <v>127771435</v>
       </c>
       <c r="B107" t="n">
-        <v>106312</v>
+        <v>106320</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>729272</v>
+        <v>729159</v>
       </c>
       <c r="R107" t="n">
-        <v>6367485</v>
+        <v>6367602</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -11974,10 +11974,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127771400</v>
+        <v>127771374</v>
       </c>
       <c r="B108" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>729243</v>
+        <v>729236</v>
       </c>
       <c r="R108" t="n">
-        <v>6367748</v>
+        <v>6367778</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12076,10 +12076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127771435</v>
+        <v>127771400</v>
       </c>
       <c r="B109" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12087,16 +12087,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>729159</v>
+        <v>729243</v>
       </c>
       <c r="R109" t="n">
-        <v>6367602</v>
+        <v>6367748</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12181,7 +12181,7 @@
         <v>127771389</v>
       </c>
       <c r="B110" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>127771462</v>
       </c>
       <c r="B111" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>127771555</v>
       </c>
       <c r="B112" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771936</v>
+        <v>127771558</v>
       </c>
       <c r="B113" t="n">
-        <v>57669</v>
+        <v>106320</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12495,46 +12495,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729289</v>
+        <v>729273</v>
       </c>
       <c r="R113" t="n">
-        <v>6367518</v>
+        <v>6367508</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12577,7 +12568,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12595,10 +12586,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771414</v>
+        <v>127771577</v>
       </c>
       <c r="B114" t="n">
-        <v>106766</v>
+        <v>106320</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12606,16 +12597,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12630,10 +12621,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729205</v>
+        <v>729275</v>
       </c>
       <c r="R114" t="n">
-        <v>6367685</v>
+        <v>6367487</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12679,7 +12670,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12697,10 +12688,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771558</v>
+        <v>127771414</v>
       </c>
       <c r="B115" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12708,16 +12699,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12732,10 +12723,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729273</v>
+        <v>729205</v>
       </c>
       <c r="R115" t="n">
-        <v>6367508</v>
+        <v>6367685</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12781,7 +12772,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12799,10 +12790,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771577</v>
+        <v>127771396</v>
       </c>
       <c r="B116" t="n">
-        <v>106312</v>
+        <v>106774</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12810,16 +12801,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12834,10 +12825,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729275</v>
+        <v>729249</v>
       </c>
       <c r="R116" t="n">
-        <v>6367487</v>
+        <v>6367746</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12883,7 +12874,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12901,10 +12892,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771396</v>
+        <v>127771936</v>
       </c>
       <c r="B117" t="n">
-        <v>106766</v>
+        <v>57670</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12912,37 +12903,46 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729249</v>
+        <v>729289</v>
       </c>
       <c r="R117" t="n">
-        <v>6367746</v>
+        <v>6367518</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13006,7 +13006,7 @@
         <v>127771458</v>
       </c>
       <c r="B118" t="n">
-        <v>103926</v>
+        <v>103934</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>127771439</v>
       </c>
       <c r="B119" t="n">
-        <v>103926</v>
+        <v>103934</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -6287,57 +6287,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127771410</v>
+        <v>127771933</v>
       </c>
       <c r="B53" t="n">
-        <v>98456</v>
+        <v>57670</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729272</v>
+        <v>729149</v>
       </c>
       <c r="R53" t="n">
-        <v>6367702</v>
+        <v>6367526</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6369,6 +6365,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6380,7 +6381,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6398,45 +6399,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771460</v>
+        <v>127771410</v>
       </c>
       <c r="B54" t="n">
-        <v>106774</v>
+        <v>98456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729130</v>
+        <v>729272</v>
       </c>
       <c r="R54" t="n">
-        <v>6367518</v>
+        <v>6367702</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6482,7 +6492,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6500,7 +6510,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771421</v>
+        <v>127771460</v>
       </c>
       <c r="B55" t="n">
         <v>106774</v>
@@ -6535,10 +6545,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729214</v>
+        <v>729130</v>
       </c>
       <c r="R55" t="n">
-        <v>6367664</v>
+        <v>6367518</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6584,7 +6594,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6602,7 +6612,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771565</v>
+        <v>127771421</v>
       </c>
       <c r="B56" t="n">
         <v>106774</v>
@@ -6637,10 +6647,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729264</v>
+        <v>729214</v>
       </c>
       <c r="R56" t="n">
-        <v>6367501</v>
+        <v>6367664</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6686,7 +6696,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6704,10 +6714,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771552</v>
+        <v>127771565</v>
       </c>
       <c r="B57" t="n">
-        <v>107363</v>
+        <v>106774</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6715,43 +6725,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729282</v>
+        <v>729264</v>
       </c>
       <c r="R57" t="n">
-        <v>6367498</v>
+        <v>6367501</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6815,10 +6816,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127771933</v>
+        <v>127771552</v>
       </c>
       <c r="B58" t="n">
-        <v>57670</v>
+        <v>107363</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6826,42 +6827,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729149</v>
+        <v>729282</v>
       </c>
       <c r="R58" t="n">
-        <v>6367526</v>
+        <v>6367498</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6893,11 +6898,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7335,10 +7335,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127771559</v>
+        <v>127771397</v>
       </c>
       <c r="B63" t="n">
-        <v>106774</v>
+        <v>106320</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,16 +7346,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>729273</v>
+        <v>729249</v>
       </c>
       <c r="R63" t="n">
-        <v>6367508</v>
+        <v>6367746</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127771397</v>
+        <v>127771463</v>
       </c>
       <c r="B64" t="n">
         <v>106320</v>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>729249</v>
+        <v>729143</v>
       </c>
       <c r="R64" t="n">
-        <v>6367746</v>
+        <v>6367517</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127771463</v>
+        <v>127771559</v>
       </c>
       <c r="B65" t="n">
-        <v>106320</v>
+        <v>106774</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7550,16 +7550,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7574,10 +7574,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>729143</v>
+        <v>729273</v>
       </c>
       <c r="R65" t="n">
-        <v>6367517</v>
+        <v>6367508</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127771556</v>
+        <v>127771383</v>
       </c>
       <c r="B90" t="n">
-        <v>103934</v>
+        <v>106320</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10125,21 +10125,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>729273</v>
+        <v>729236</v>
       </c>
       <c r="R90" t="n">
-        <v>6367508</v>
+        <v>6367761</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10216,10 +10216,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771383</v>
+        <v>127771930</v>
       </c>
       <c r="B91" t="n">
-        <v>106320</v>
+        <v>57686</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10227,37 +10227,46 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221903</v>
+        <v>100048</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729236</v>
+        <v>729246</v>
       </c>
       <c r="R91" t="n">
-        <v>6367761</v>
+        <v>6367767</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10300,7 +10309,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10318,10 +10327,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127771578</v>
+        <v>127771556</v>
       </c>
       <c r="B92" t="n">
-        <v>106774</v>
+        <v>103934</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10329,21 +10338,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10353,10 +10362,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>729275</v>
+        <v>729273</v>
       </c>
       <c r="R92" t="n">
-        <v>6367487</v>
+        <v>6367508</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10420,10 +10429,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771930</v>
+        <v>127771578</v>
       </c>
       <c r="B93" t="n">
-        <v>57686</v>
+        <v>106774</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10431,46 +10440,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100048</v>
+        <v>221849</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729246</v>
+        <v>729275</v>
       </c>
       <c r="R93" t="n">
-        <v>6367767</v>
+        <v>6367487</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AY130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4828,7 +4828,7 @@
         <v>127771932</v>
       </c>
       <c r="B39" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>127771574</v>
       </c>
       <c r="B40" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>127771423</v>
       </c>
       <c r="B41" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>127771431</v>
       </c>
       <c r="B42" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127771437</v>
+        <v>127771857</v>
       </c>
       <c r="B43" t="n">
-        <v>106774</v>
+        <v>5493</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,21 +5259,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>101410</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729159</v>
+        <v>729268</v>
       </c>
       <c r="R43" t="n">
-        <v>6367602</v>
+        <v>6367746</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5321,6 +5321,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Tall med angrepp.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5332,7 +5337,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5350,10 +5355,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127771857</v>
+        <v>127771437</v>
       </c>
       <c r="B44" t="n">
-        <v>5493</v>
+        <v>106867</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5361,21 +5366,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>101410</v>
+        <v>221849</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5385,10 +5390,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>729268</v>
+        <v>729159</v>
       </c>
       <c r="R44" t="n">
-        <v>6367746</v>
+        <v>6367602</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5423,11 +5428,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Tall med angrepp.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5460,7 +5460,7 @@
         <v>127771363</v>
       </c>
       <c r="B45" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>127771381</v>
       </c>
       <c r="B46" t="n">
-        <v>107363</v>
+        <v>107456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127771570</v>
+        <v>127771608</v>
       </c>
       <c r="B47" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5686,16 +5686,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729262</v>
+        <v>729267</v>
       </c>
       <c r="R47" t="n">
-        <v>6367486</v>
+        <v>6367464</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127771573</v>
+        <v>127771419</v>
       </c>
       <c r="B48" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5788,16 +5788,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729265</v>
+        <v>729198</v>
       </c>
       <c r="R48" t="n">
-        <v>6367490</v>
+        <v>6367656</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127771405</v>
+        <v>127771570</v>
       </c>
       <c r="B49" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729259</v>
+        <v>729262</v>
       </c>
       <c r="R49" t="n">
-        <v>6367748</v>
+        <v>6367486</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127771608</v>
+        <v>127771367</v>
       </c>
       <c r="B50" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,16 +5992,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6016,13 +6016,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729267</v>
+        <v>729279</v>
       </c>
       <c r="R50" t="n">
-        <v>6367464</v>
+        <v>6367813</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127771367</v>
+        <v>127771573</v>
       </c>
       <c r="B51" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,13 +6118,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729279</v>
+        <v>729265</v>
       </c>
       <c r="R51" t="n">
-        <v>6367813</v>
+        <v>6367490</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127771419</v>
+        <v>127771405</v>
       </c>
       <c r="B52" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6196,16 +6196,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6220,10 +6220,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729198</v>
+        <v>729259</v>
       </c>
       <c r="R52" t="n">
-        <v>6367656</v>
+        <v>6367748</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6287,53 +6287,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127771933</v>
+        <v>127771410</v>
       </c>
       <c r="B53" t="n">
-        <v>57670</v>
+        <v>98549</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729149</v>
+        <v>729272</v>
       </c>
       <c r="R53" t="n">
-        <v>6367526</v>
+        <v>6367702</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6365,11 +6369,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6381,7 +6380,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6399,54 +6398,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771410</v>
+        <v>127771460</v>
       </c>
       <c r="B54" t="n">
-        <v>98456</v>
+        <v>106867</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729272</v>
+        <v>729130</v>
       </c>
       <c r="R54" t="n">
-        <v>6367702</v>
+        <v>6367518</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6492,7 +6482,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6510,10 +6500,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771460</v>
+        <v>127771421</v>
       </c>
       <c r="B55" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6545,10 +6535,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729130</v>
+        <v>729214</v>
       </c>
       <c r="R55" t="n">
-        <v>6367518</v>
+        <v>6367664</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6594,7 +6584,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6612,10 +6602,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771421</v>
+        <v>127771565</v>
       </c>
       <c r="B56" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6647,10 +6637,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729214</v>
+        <v>729264</v>
       </c>
       <c r="R56" t="n">
-        <v>6367664</v>
+        <v>6367501</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6696,7 +6686,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6714,10 +6704,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771565</v>
+        <v>127771552</v>
       </c>
       <c r="B57" t="n">
-        <v>106774</v>
+        <v>107456</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6725,34 +6715,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729264</v>
+        <v>729282</v>
       </c>
       <c r="R57" t="n">
-        <v>6367501</v>
+        <v>6367498</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6816,10 +6815,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127771552</v>
+        <v>127771933</v>
       </c>
       <c r="B58" t="n">
-        <v>107363</v>
+        <v>57682</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6827,46 +6826,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
+          <t>Gammelgarn Skogby 1:16 (2), littorinagränsvall N., Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729282</v>
+        <v>729149</v>
       </c>
       <c r="R58" t="n">
-        <v>6367498</v>
+        <v>6367526</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6898,6 +6893,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Tallar med mycket gott om utgångshål för insekter samt ett träd med fräscht bohål av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127771440</v>
+        <v>127771386</v>
       </c>
       <c r="B59" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6938,16 +6938,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>729123</v>
+        <v>729222</v>
       </c>
       <c r="R59" t="n">
-        <v>6367520</v>
+        <v>6367752</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127771415</v>
+        <v>127771440</v>
       </c>
       <c r="B60" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>729205</v>
+        <v>729123</v>
       </c>
       <c r="R60" t="n">
-        <v>6367685</v>
+        <v>6367520</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127771386</v>
+        <v>127771415</v>
       </c>
       <c r="B61" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7142,16 +7142,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>729222</v>
+        <v>729205</v>
       </c>
       <c r="R61" t="n">
-        <v>6367752</v>
+        <v>6367685</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
         <v>127771390</v>
       </c>
       <c r="B62" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7335,10 +7335,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127771397</v>
+        <v>127771559</v>
       </c>
       <c r="B63" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,16 +7346,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>729249</v>
+        <v>729273</v>
       </c>
       <c r="R63" t="n">
-        <v>6367746</v>
+        <v>6367508</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7437,10 +7437,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127771463</v>
+        <v>127771935</v>
       </c>
       <c r="B64" t="n">
-        <v>106320</v>
+        <v>57682</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7448,37 +7448,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>729143</v>
+        <v>729189</v>
       </c>
       <c r="R64" t="n">
-        <v>6367517</v>
+        <v>6367526</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7510,6 +7515,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre bo i nu fallen död tall.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7521,7 +7531,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7539,10 +7549,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127771559</v>
+        <v>127771397</v>
       </c>
       <c r="B65" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7550,16 +7560,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7574,10 +7584,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>729273</v>
+        <v>729249</v>
       </c>
       <c r="R65" t="n">
-        <v>6367508</v>
+        <v>6367746</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7623,7 +7633,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7641,10 +7651,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127771935</v>
+        <v>127771463</v>
       </c>
       <c r="B66" t="n">
-        <v>57670</v>
+        <v>106413</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7652,42 +7662,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>729189</v>
+        <v>729143</v>
       </c>
       <c r="R66" t="n">
-        <v>6367526</v>
+        <v>6367517</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7719,11 +7724,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre bo i nu fallen död tall.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7753,10 +7753,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127771401</v>
+        <v>127771371</v>
       </c>
       <c r="B67" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>729249</v>
+        <v>729244</v>
       </c>
       <c r="R67" t="n">
-        <v>6367753</v>
+        <v>6367780</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7855,10 +7855,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127771371</v>
+        <v>127771401</v>
       </c>
       <c r="B68" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>729244</v>
+        <v>729249</v>
       </c>
       <c r="R68" t="n">
-        <v>6367780</v>
+        <v>6367753</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7960,7 +7960,7 @@
         <v>127771605</v>
       </c>
       <c r="B69" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>127771593</v>
       </c>
       <c r="B70" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8161,10 +8161,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127771588</v>
+        <v>127771382</v>
       </c>
       <c r="B71" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8172,16 +8172,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>729260</v>
+        <v>729236</v>
       </c>
       <c r="R71" t="n">
-        <v>6367474</v>
+        <v>6367761</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8266,7 +8266,7 @@
         <v>127771564</v>
       </c>
       <c r="B72" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127771590</v>
+        <v>127771387</v>
       </c>
       <c r="B73" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>729268</v>
+        <v>729222</v>
       </c>
       <c r="R73" t="n">
-        <v>6367477</v>
+        <v>6367752</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8467,10 +8467,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127771387</v>
+        <v>127771416</v>
       </c>
       <c r="B74" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>729222</v>
+        <v>729198</v>
       </c>
       <c r="R74" t="n">
-        <v>6367752</v>
+        <v>6367656</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127771562</v>
+        <v>127771588</v>
       </c>
       <c r="B75" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729266</v>
+        <v>729260</v>
       </c>
       <c r="R75" t="n">
-        <v>6367511</v>
+        <v>6367474</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8671,10 +8671,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127771382</v>
+        <v>127771590</v>
       </c>
       <c r="B76" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8682,16 +8682,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>729236</v>
+        <v>729268</v>
       </c>
       <c r="R76" t="n">
-        <v>6367761</v>
+        <v>6367477</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8773,10 +8773,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127771416</v>
+        <v>127771562</v>
       </c>
       <c r="B77" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>729198</v>
+        <v>729266</v>
       </c>
       <c r="R77" t="n">
-        <v>6367656</v>
+        <v>6367511</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8878,7 +8878,7 @@
         <v>127771568</v>
       </c>
       <c r="B78" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>127771450</v>
       </c>
       <c r="B79" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>127771366</v>
       </c>
       <c r="B80" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>127771392</v>
       </c>
       <c r="B81" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>127771586</v>
       </c>
       <c r="B82" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>127771931</v>
       </c>
       <c r="B83" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9502,10 +9502,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127771375</v>
+        <v>127771575</v>
       </c>
       <c r="B84" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9513,16 +9513,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9537,10 +9537,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>729236</v>
+        <v>729271</v>
       </c>
       <c r="R84" t="n">
-        <v>6367778</v>
+        <v>6367489</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9604,10 +9604,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127771584</v>
+        <v>127771581</v>
       </c>
       <c r="B85" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9615,16 +9615,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>729267</v>
+        <v>729272</v>
       </c>
       <c r="R85" t="n">
-        <v>6367487</v>
+        <v>6367485</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9706,10 +9706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127771393</v>
+        <v>127771375</v>
       </c>
       <c r="B86" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>729237</v>
+        <v>729236</v>
       </c>
       <c r="R86" t="n">
-        <v>6367741</v>
+        <v>6367778</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127771466</v>
+        <v>127771584</v>
       </c>
       <c r="B87" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>729154</v>
+        <v>729267</v>
       </c>
       <c r="R87" t="n">
-        <v>6367521</v>
+        <v>6367487</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkbarrskog , vid stig.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127771575</v>
+        <v>127771393</v>
       </c>
       <c r="B88" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9921,16 +9921,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>729271</v>
+        <v>729237</v>
       </c>
       <c r="R88" t="n">
-        <v>6367489</v>
+        <v>6367741</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127771581</v>
+        <v>127771466</v>
       </c>
       <c r="B89" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10023,16 +10023,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>729272</v>
+        <v>729154</v>
       </c>
       <c r="R89" t="n">
-        <v>6367485</v>
+        <v>6367521</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog , vid stig.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127771383</v>
+        <v>127771578</v>
       </c>
       <c r="B90" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10125,16 +10125,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>729236</v>
+        <v>729275</v>
       </c>
       <c r="R90" t="n">
-        <v>6367761</v>
+        <v>6367487</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10216,10 +10216,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771930</v>
+        <v>127771383</v>
       </c>
       <c r="B91" t="n">
-        <v>57686</v>
+        <v>106413</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10227,46 +10227,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100048</v>
+        <v>221903</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729246</v>
+        <v>729236</v>
       </c>
       <c r="R91" t="n">
-        <v>6367767</v>
+        <v>6367761</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10309,7 +10300,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10330,7 +10321,7 @@
         <v>127771556</v>
       </c>
       <c r="B92" t="n">
-        <v>103934</v>
+        <v>104027</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10429,10 +10420,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771578</v>
+        <v>127771930</v>
       </c>
       <c r="B93" t="n">
-        <v>106774</v>
+        <v>57698</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10440,37 +10431,46 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221849</v>
+        <v>100048</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729275</v>
+        <v>729246</v>
       </c>
       <c r="R93" t="n">
-        <v>6367487</v>
+        <v>6367767</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10534,7 +10534,7 @@
         <v>127771379</v>
       </c>
       <c r="B94" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>127771365</v>
       </c>
       <c r="B95" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>127771929</v>
       </c>
       <c r="B96" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>127771429</v>
       </c>
       <c r="B97" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>127771607</v>
       </c>
       <c r="B98" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>127771461</v>
       </c>
       <c r="B99" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11158,10 +11158,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127771604</v>
+        <v>127771378</v>
       </c>
       <c r="B100" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11169,16 +11169,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11193,10 +11193,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>729268</v>
+        <v>729229</v>
       </c>
       <c r="R100" t="n">
-        <v>6367470</v>
+        <v>6367768</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127771554</v>
+        <v>127771412</v>
       </c>
       <c r="B101" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11295,10 +11295,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>729277</v>
+        <v>729227</v>
       </c>
       <c r="R101" t="n">
-        <v>6367499</v>
+        <v>6367700</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127771592</v>
+        <v>127771604</v>
       </c>
       <c r="B102" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>729273</v>
+        <v>729268</v>
       </c>
       <c r="R102" t="n">
-        <v>6367480</v>
+        <v>6367470</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11464,10 +11464,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127771378</v>
+        <v>127771554</v>
       </c>
       <c r="B103" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11475,16 +11475,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>729229</v>
+        <v>729277</v>
       </c>
       <c r="R103" t="n">
-        <v>6367768</v>
+        <v>6367499</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -11566,10 +11566,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127771412</v>
+        <v>127771592</v>
       </c>
       <c r="B104" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11577,16 +11577,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11601,10 +11601,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>729227</v>
+        <v>729273</v>
       </c>
       <c r="R104" t="n">
-        <v>6367700</v>
+        <v>6367480</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -11668,10 +11668,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127771580</v>
+        <v>127771374</v>
       </c>
       <c r="B105" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11679,16 +11679,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>729272</v>
+        <v>729236</v>
       </c>
       <c r="R105" t="n">
-        <v>6367485</v>
+        <v>6367778</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -11770,10 +11770,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127771610</v>
+        <v>127771400</v>
       </c>
       <c r="B106" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11781,16 +11781,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>729267</v>
+        <v>729243</v>
       </c>
       <c r="R106" t="n">
-        <v>6367464</v>
+        <v>6367748</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -11872,10 +11872,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127771435</v>
+        <v>127771389</v>
       </c>
       <c r="B107" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11883,16 +11883,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>729159</v>
+        <v>729230</v>
       </c>
       <c r="R107" t="n">
-        <v>6367602</v>
+        <v>6367743</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -11974,10 +11974,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127771374</v>
+        <v>127771462</v>
       </c>
       <c r="B108" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>729236</v>
+        <v>729143</v>
       </c>
       <c r="R108" t="n">
-        <v>6367778</v>
+        <v>6367517</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12076,10 +12076,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127771400</v>
+        <v>127771610</v>
       </c>
       <c r="B109" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12087,16 +12087,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>729243</v>
+        <v>729267</v>
       </c>
       <c r="R109" t="n">
-        <v>6367748</v>
+        <v>6367464</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127771389</v>
+        <v>127771580</v>
       </c>
       <c r="B110" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12189,16 +12189,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>729230</v>
+        <v>729272</v>
       </c>
       <c r="R110" t="n">
-        <v>6367743</v>
+        <v>6367485</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12280,10 +12280,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127771462</v>
+        <v>127771435</v>
       </c>
       <c r="B111" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12291,16 +12291,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>729143</v>
+        <v>729159</v>
       </c>
       <c r="R111" t="n">
-        <v>6367517</v>
+        <v>6367602</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12385,7 +12385,7 @@
         <v>127771555</v>
       </c>
       <c r="B112" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771558</v>
+        <v>127771414</v>
       </c>
       <c r="B113" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12495,16 +12495,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12519,10 +12519,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729273</v>
+        <v>729205</v>
       </c>
       <c r="R113" t="n">
-        <v>6367508</v>
+        <v>6367685</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12586,10 +12586,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771577</v>
+        <v>127771396</v>
       </c>
       <c r="B114" t="n">
-        <v>106320</v>
+        <v>106867</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12597,16 +12597,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12621,10 +12621,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729275</v>
+        <v>729249</v>
       </c>
       <c r="R114" t="n">
-        <v>6367487</v>
+        <v>6367746</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12688,10 +12688,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771414</v>
+        <v>127771558</v>
       </c>
       <c r="B115" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12699,16 +12699,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12723,10 +12723,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729205</v>
+        <v>729273</v>
       </c>
       <c r="R115" t="n">
-        <v>6367685</v>
+        <v>6367508</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12772,7 +12772,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771396</v>
+        <v>127771577</v>
       </c>
       <c r="B116" t="n">
-        <v>106774</v>
+        <v>106413</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12801,16 +12801,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12825,10 +12825,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729249</v>
+        <v>729275</v>
       </c>
       <c r="R116" t="n">
-        <v>6367746</v>
+        <v>6367487</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12892,10 +12892,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771936</v>
+        <v>127771458</v>
       </c>
       <c r="B117" t="n">
-        <v>57670</v>
+        <v>104027</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12903,46 +12903,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>220164</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729289</v>
+        <v>729130</v>
       </c>
       <c r="R117" t="n">
         <v>6367518</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12985,7 +12976,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13003,10 +12994,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771458</v>
+        <v>127771439</v>
       </c>
       <c r="B118" t="n">
-        <v>103934</v>
+        <v>104027</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13038,10 +13029,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729130</v>
+        <v>729123</v>
       </c>
       <c r="R118" t="n">
-        <v>6367518</v>
+        <v>6367520</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13087,7 +13078,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13105,10 +13096,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771439</v>
+        <v>127771936</v>
       </c>
       <c r="B119" t="n">
-        <v>103934</v>
+        <v>57682</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13116,37 +13107,46 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729123</v>
+        <v>729289</v>
       </c>
       <c r="R119" t="n">
-        <v>6367520</v>
+        <v>6367518</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13210,7 +13210,7 @@
         <v>128472799</v>
       </c>
       <c r="B120" t="n">
-        <v>86845</v>
+        <v>86937</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>128473008</v>
       </c>
       <c r="B121" t="n">
-        <v>86786</v>
+        <v>86878</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13418,6 +13418,890 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128520851</v>
+      </c>
+      <c r="B122" t="n">
+        <v>86740</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6367544</v>
+      </c>
+      <c r="S122" t="n">
+        <v>50</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Lisa Wallström</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Lisa Wallström</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128512739</v>
+      </c>
+      <c r="B123" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>729262</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6367574</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128512744</v>
+      </c>
+      <c r="B124" t="n">
+        <v>90987</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>729265</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6367561</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128512741</v>
+      </c>
+      <c r="B125" t="n">
+        <v>86915</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>729263</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6367562</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128512749</v>
+      </c>
+      <c r="B126" t="n">
+        <v>90874</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>729274</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6367544</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128512743</v>
+      </c>
+      <c r="B127" t="n">
+        <v>90987</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>729250</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6367591</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128512738</v>
+      </c>
+      <c r="B128" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>729258</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6367577</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128512742</v>
+      </c>
+      <c r="B129" t="n">
+        <v>90987</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>729258</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6367590</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128512747</v>
+      </c>
+      <c r="B130" t="n">
+        <v>90882</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>729262</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6367574</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -4825,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127771932</v>
+        <v>127771423</v>
       </c>
       <c r="B39" t="n">
-        <v>57682</v>
+        <v>106867</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4836,39 +4836,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729269</v>
+        <v>729206</v>
       </c>
       <c r="R39" t="n">
-        <v>6367727</v>
+        <v>6367643</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4905,7 +4900,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+          <t>Röjd skog mot O.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4919,7 +4914,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5039,7 +5034,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127771423</v>
+        <v>127771431</v>
       </c>
       <c r="B41" t="n">
         <v>106867</v>
@@ -5074,10 +5069,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729206</v>
+        <v>729197</v>
       </c>
       <c r="R41" t="n">
-        <v>6367643</v>
+        <v>6367641</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5112,11 +5107,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Röjd skog mot O.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,7 +5118,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5146,10 +5136,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127771431</v>
+        <v>127771932</v>
       </c>
       <c r="B42" t="n">
-        <v>106867</v>
+        <v>57682</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5157,34 +5147,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729197</v>
+        <v>729269</v>
       </c>
       <c r="R42" t="n">
-        <v>6367641</v>
+        <v>6367727</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5219,6 +5214,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Bilder! Tallar med mycket gott om utgångshål för insekter samt ett träd med fodösk av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127771857</v>
+        <v>127771437</v>
       </c>
       <c r="B43" t="n">
-        <v>5493</v>
+        <v>106867</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,21 +5259,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101410</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729268</v>
+        <v>729159</v>
       </c>
       <c r="R43" t="n">
-        <v>6367746</v>
+        <v>6367602</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5321,11 +5321,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Tall med angrepp.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5337,7 +5332,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5355,10 +5350,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127771437</v>
+        <v>127771363</v>
       </c>
       <c r="B44" t="n">
-        <v>106867</v>
+        <v>106413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5366,16 +5361,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5390,10 +5385,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>729159</v>
+        <v>729296</v>
       </c>
       <c r="R44" t="n">
-        <v>6367602</v>
+        <v>6367803</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5428,6 +5423,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Vid gräns mot Klints 1:9.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127771363</v>
+        <v>127771857</v>
       </c>
       <c r="B45" t="n">
-        <v>106413</v>
+        <v>5493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5468,21 +5468,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221903</v>
+        <v>101410</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>729296</v>
+        <v>729268</v>
       </c>
       <c r="R45" t="n">
-        <v>6367803</v>
+        <v>6367746</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Vid gräns mot Klints 1:9.</t>
+          <t>Tall med angrepp.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127771419</v>
+        <v>127771570</v>
       </c>
       <c r="B48" t="n">
-        <v>106867</v>
+        <v>106413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5788,16 +5788,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729198</v>
+        <v>729262</v>
       </c>
       <c r="R48" t="n">
-        <v>6367656</v>
+        <v>6367486</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127771570</v>
+        <v>127771367</v>
       </c>
       <c r="B49" t="n">
         <v>106413</v>
@@ -5914,13 +5914,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729262</v>
+        <v>729279</v>
       </c>
       <c r="R49" t="n">
-        <v>6367486</v>
+        <v>6367813</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127771367</v>
+        <v>127771419</v>
       </c>
       <c r="B50" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,16 +5992,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6016,13 +6016,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729279</v>
+        <v>729198</v>
       </c>
       <c r="R50" t="n">
-        <v>6367813</v>
+        <v>6367656</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127771460</v>
+        <v>127771552</v>
       </c>
       <c r="B54" t="n">
-        <v>106867</v>
+        <v>107456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6409,34 +6409,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729130</v>
+        <v>729282</v>
       </c>
       <c r="R54" t="n">
-        <v>6367518</v>
+        <v>6367498</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6482,7 +6491,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6500,7 +6509,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127771421</v>
+        <v>127771460</v>
       </c>
       <c r="B55" t="n">
         <v>106867</v>
@@ -6535,10 +6544,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729214</v>
+        <v>729130</v>
       </c>
       <c r="R55" t="n">
-        <v>6367664</v>
+        <v>6367518</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6584,7 +6593,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6602,7 +6611,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127771565</v>
+        <v>127771421</v>
       </c>
       <c r="B56" t="n">
         <v>106867</v>
@@ -6637,10 +6646,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729264</v>
+        <v>729214</v>
       </c>
       <c r="R56" t="n">
-        <v>6367501</v>
+        <v>6367664</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6686,7 +6695,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6704,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127771552</v>
+        <v>127771565</v>
       </c>
       <c r="B57" t="n">
-        <v>107456</v>
+        <v>106867</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6715,43 +6724,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729282</v>
+        <v>729264</v>
       </c>
       <c r="R57" t="n">
-        <v>6367498</v>
+        <v>6367501</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127771386</v>
+        <v>127771440</v>
       </c>
       <c r="B59" t="n">
-        <v>106867</v>
+        <v>106413</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6938,16 +6938,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>729222</v>
+        <v>729123</v>
       </c>
       <c r="R59" t="n">
-        <v>6367752</v>
+        <v>6367520</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127771440</v>
+        <v>127771386</v>
       </c>
       <c r="B60" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7040,16 +7040,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>729123</v>
+        <v>729222</v>
       </c>
       <c r="R60" t="n">
-        <v>6367520</v>
+        <v>6367752</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7335,10 +7335,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127771559</v>
+        <v>127771935</v>
       </c>
       <c r="B63" t="n">
-        <v>106867</v>
+        <v>57682</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,37 +7346,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>729273</v>
+        <v>729189</v>
       </c>
       <c r="R63" t="n">
-        <v>6367508</v>
+        <v>6367526</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7408,6 +7413,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre bo i nu fallen död tall.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7419,7 +7429,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7437,10 +7447,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127771935</v>
+        <v>127771397</v>
       </c>
       <c r="B64" t="n">
-        <v>57682</v>
+        <v>106413</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7448,42 +7458,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>221903</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>729189</v>
+        <v>729249</v>
       </c>
       <c r="R64" t="n">
-        <v>6367526</v>
+        <v>6367746</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7515,11 +7520,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre bo i nu fallen död tall.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127771397</v>
+        <v>127771463</v>
       </c>
       <c r="B65" t="n">
         <v>106413</v>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>729249</v>
+        <v>729143</v>
       </c>
       <c r="R65" t="n">
-        <v>6367746</v>
+        <v>6367517</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7651,10 +7651,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127771463</v>
+        <v>127771559</v>
       </c>
       <c r="B66" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>729143</v>
+        <v>729273</v>
       </c>
       <c r="R66" t="n">
-        <v>6367517</v>
+        <v>6367508</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7855,10 +7855,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127771401</v>
+        <v>127771605</v>
       </c>
       <c r="B68" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>729249</v>
+        <v>729264</v>
       </c>
       <c r="R68" t="n">
-        <v>6367753</v>
+        <v>6367467</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7957,7 +7957,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127771605</v>
+        <v>127771593</v>
       </c>
       <c r="B69" t="n">
         <v>106867</v>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>729264</v>
+        <v>729273</v>
       </c>
       <c r="R69" t="n">
-        <v>6367467</v>
+        <v>6367480</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127771593</v>
+        <v>127771401</v>
       </c>
       <c r="B70" t="n">
-        <v>106867</v>
+        <v>106413</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8070,16 +8070,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>729273</v>
+        <v>729249</v>
       </c>
       <c r="R70" t="n">
-        <v>6367480</v>
+        <v>6367753</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8161,10 +8161,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127771382</v>
+        <v>127771588</v>
       </c>
       <c r="B71" t="n">
-        <v>106867</v>
+        <v>106413</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8172,16 +8172,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>729236</v>
+        <v>729260</v>
       </c>
       <c r="R71" t="n">
-        <v>6367761</v>
+        <v>6367474</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127771387</v>
+        <v>127771590</v>
       </c>
       <c r="B73" t="n">
         <v>106413</v>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>729222</v>
+        <v>729268</v>
       </c>
       <c r="R73" t="n">
-        <v>6367752</v>
+        <v>6367477</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8467,7 +8467,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127771416</v>
+        <v>127771387</v>
       </c>
       <c r="B74" t="n">
         <v>106413</v>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>729198</v>
+        <v>729222</v>
       </c>
       <c r="R74" t="n">
-        <v>6367656</v>
+        <v>6367752</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127771588</v>
+        <v>127771382</v>
       </c>
       <c r="B75" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8580,16 +8580,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729260</v>
+        <v>729236</v>
       </c>
       <c r="R75" t="n">
-        <v>6367474</v>
+        <v>6367761</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8671,7 +8671,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127771590</v>
+        <v>127771416</v>
       </c>
       <c r="B76" t="n">
         <v>106413</v>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>729268</v>
+        <v>729198</v>
       </c>
       <c r="R76" t="n">
-        <v>6367477</v>
+        <v>6367656</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127771366</v>
+        <v>127771586</v>
       </c>
       <c r="B80" t="n">
-        <v>106867</v>
+        <v>106413</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9095,16 +9095,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729279</v>
+        <v>729260</v>
       </c>
       <c r="R80" t="n">
-        <v>6367813</v>
+        <v>6367485</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkhäll med karst i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9186,7 +9186,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127771392</v>
+        <v>127771366</v>
       </c>
       <c r="B81" t="n">
         <v>106867</v>
@@ -9221,13 +9221,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729237</v>
+        <v>729279</v>
       </c>
       <c r="R81" t="n">
-        <v>6367741</v>
+        <v>6367813</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkhäll med karst i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127771586</v>
+        <v>127771392</v>
       </c>
       <c r="B82" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9299,16 +9299,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9323,13 +9323,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729260</v>
+        <v>729237</v>
       </c>
       <c r="R82" t="n">
-        <v>6367485</v>
+        <v>6367741</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9502,10 +9502,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127771575</v>
+        <v>127771375</v>
       </c>
       <c r="B84" t="n">
-        <v>106867</v>
+        <v>106413</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9513,16 +9513,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9537,10 +9537,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>729271</v>
+        <v>729236</v>
       </c>
       <c r="R84" t="n">
-        <v>6367489</v>
+        <v>6367778</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9604,7 +9604,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127771581</v>
+        <v>127771575</v>
       </c>
       <c r="B85" t="n">
         <v>106867</v>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>729272</v>
+        <v>729271</v>
       </c>
       <c r="R85" t="n">
-        <v>6367485</v>
+        <v>6367489</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9706,10 +9706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127771375</v>
+        <v>127771581</v>
       </c>
       <c r="B86" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9717,16 +9717,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>729236</v>
+        <v>729272</v>
       </c>
       <c r="R86" t="n">
-        <v>6367778</v>
+        <v>6367485</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127771578</v>
+        <v>127771930</v>
       </c>
       <c r="B90" t="n">
-        <v>106867</v>
+        <v>57698</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10125,37 +10125,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221849</v>
+        <v>100048</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>729275</v>
+        <v>729246</v>
       </c>
       <c r="R90" t="n">
-        <v>6367487</v>
+        <v>6367767</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10198,7 +10207,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10216,10 +10225,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127771383</v>
+        <v>127771556</v>
       </c>
       <c r="B91" t="n">
-        <v>106413</v>
+        <v>104027</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10227,21 +10236,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10251,10 +10260,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>729236</v>
+        <v>729273</v>
       </c>
       <c r="R91" t="n">
-        <v>6367761</v>
+        <v>6367508</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10300,7 +10309,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10318,10 +10327,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127771556</v>
+        <v>127771578</v>
       </c>
       <c r="B92" t="n">
-        <v>104027</v>
+        <v>106867</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10329,21 +10338,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10353,10 +10362,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>729273</v>
+        <v>729275</v>
       </c>
       <c r="R92" t="n">
-        <v>6367508</v>
+        <v>6367487</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10420,10 +10429,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127771930</v>
+        <v>127771383</v>
       </c>
       <c r="B93" t="n">
-        <v>57698</v>
+        <v>106413</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10431,46 +10440,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100048</v>
+        <v>221903</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>729246</v>
+        <v>729236</v>
       </c>
       <c r="R93" t="n">
-        <v>6367767</v>
+        <v>6367761</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med grova tallar, varav en stor del döda.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11668,10 +11668,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127771374</v>
+        <v>127771610</v>
       </c>
       <c r="B105" t="n">
-        <v>106867</v>
+        <v>106413</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11679,16 +11679,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>729236</v>
+        <v>729267</v>
       </c>
       <c r="R105" t="n">
-        <v>6367778</v>
+        <v>6367464</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127771400</v>
+        <v>127771374</v>
       </c>
       <c r="B106" t="n">
         <v>106867</v>
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>729243</v>
+        <v>729236</v>
       </c>
       <c r="R106" t="n">
-        <v>6367748</v>
+        <v>6367778</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11872,10 +11872,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127771389</v>
+        <v>127771580</v>
       </c>
       <c r="B107" t="n">
-        <v>106867</v>
+        <v>106413</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11883,16 +11883,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>729230</v>
+        <v>729272</v>
       </c>
       <c r="R107" t="n">
-        <v>6367743</v>
+        <v>6367485</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -11974,7 +11974,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127771462</v>
+        <v>127771400</v>
       </c>
       <c r="B108" t="n">
         <v>106867</v>
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>729143</v>
+        <v>729243</v>
       </c>
       <c r="R108" t="n">
-        <v>6367517</v>
+        <v>6367748</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12076,7 +12076,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127771610</v>
+        <v>127771435</v>
       </c>
       <c r="B109" t="n">
         <v>106413</v>
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>729267</v>
+        <v>729159</v>
       </c>
       <c r="R109" t="n">
-        <v>6367464</v>
+        <v>6367602</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127771580</v>
+        <v>127771389</v>
       </c>
       <c r="B110" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12189,16 +12189,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>729272</v>
+        <v>729230</v>
       </c>
       <c r="R110" t="n">
-        <v>6367485</v>
+        <v>6367743</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12280,10 +12280,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127771435</v>
+        <v>127771462</v>
       </c>
       <c r="B111" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12291,16 +12291,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>729159</v>
+        <v>729143</v>
       </c>
       <c r="R111" t="n">
-        <v>6367602</v>
+        <v>6367517</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127771414</v>
+        <v>127771936</v>
       </c>
       <c r="B113" t="n">
-        <v>106867</v>
+        <v>57682</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12495,37 +12495,46 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>729205</v>
+        <v>729289</v>
       </c>
       <c r="R113" t="n">
-        <v>6367685</v>
+        <v>6367518</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12568,7 +12577,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Alvarglänta med karstsprickor.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12586,10 +12595,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127771396</v>
+        <v>127771458</v>
       </c>
       <c r="B114" t="n">
-        <v>106867</v>
+        <v>104027</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12597,21 +12606,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12621,10 +12630,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>729249</v>
+        <v>729130</v>
       </c>
       <c r="R114" t="n">
-        <v>6367746</v>
+        <v>6367518</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12670,7 +12679,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Alvarglänta, kalkhäll.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12688,10 +12697,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127771558</v>
+        <v>127771439</v>
       </c>
       <c r="B115" t="n">
-        <v>106413</v>
+        <v>104027</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12699,21 +12708,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12723,10 +12732,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>729273</v>
+        <v>729123</v>
       </c>
       <c r="R115" t="n">
-        <v>6367508</v>
+        <v>6367520</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12772,7 +12781,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -12790,10 +12799,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127771577</v>
+        <v>127771414</v>
       </c>
       <c r="B116" t="n">
-        <v>106413</v>
+        <v>106867</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12801,16 +12810,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12825,10 +12834,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>729275</v>
+        <v>729205</v>
       </c>
       <c r="R116" t="n">
-        <v>6367487</v>
+        <v>6367685</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12874,7 +12883,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
+          <t>Alvarglänta med karstsprickor.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -12892,10 +12901,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127771458</v>
+        <v>127771558</v>
       </c>
       <c r="B117" t="n">
-        <v>104027</v>
+        <v>106413</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12903,21 +12912,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12927,10 +12936,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>729130</v>
+        <v>729273</v>
       </c>
       <c r="R117" t="n">
-        <v>6367518</v>
+        <v>6367508</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12976,7 +12985,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhäll.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -12994,10 +13003,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127771439</v>
+        <v>127771577</v>
       </c>
       <c r="B118" t="n">
-        <v>104027</v>
+        <v>106413</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13005,21 +13014,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13029,10 +13038,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>729123</v>
+        <v>729275</v>
       </c>
       <c r="R118" t="n">
-        <v>6367520</v>
+        <v>6367487</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13078,7 +13087,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Alvarglänta med öppna karstsprickor och strängväxtlighet över sprickor.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13096,10 +13105,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127771936</v>
+        <v>127771396</v>
       </c>
       <c r="B119" t="n">
-        <v>57682</v>
+        <v>106867</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13107,46 +13116,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gammelgarn Skogby 1:16 (2), Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>729289</v>
+        <v>729249</v>
       </c>
       <c r="R119" t="n">
-        <v>6367518</v>
+        <v>6367746</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B128" t="n">
-        <v>92387</v>
+        <v>90987</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B129" t="n">
-        <v>90987</v>
+        <v>92387</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13424,7 +13424,7 @@
         <v>128520851</v>
       </c>
       <c r="B122" t="n">
-        <v>86740</v>
+        <v>86745</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>90987</v>
+        <v>90993</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>128512741</v>
       </c>
       <c r="B125" t="n">
-        <v>86915</v>
+        <v>86919</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90874</v>
+        <v>90880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>90987</v>
+        <v>90993</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>128512742</v>
       </c>
       <c r="B128" t="n">
-        <v>90987</v>
+        <v>90993</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>128512738</v>
       </c>
       <c r="B129" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90882</v>
+        <v>90888</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY130"/>
+  <dimension ref="A1:AY171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13210,7 +13210,7 @@
         <v>128472799</v>
       </c>
       <c r="B120" t="n">
-        <v>86937</v>
+        <v>86947</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>128473008</v>
       </c>
       <c r="B121" t="n">
-        <v>86878</v>
+        <v>86888</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>128520851</v>
       </c>
       <c r="B122" t="n">
-        <v>86745</v>
+        <v>86751</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>90993</v>
+        <v>90999</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>128512741</v>
       </c>
       <c r="B125" t="n">
-        <v>86919</v>
+        <v>86925</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90880</v>
+        <v>90886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>90993</v>
+        <v>90999</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B128" t="n">
-        <v>90993</v>
+        <v>92399</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B129" t="n">
-        <v>92393</v>
+        <v>90999</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90888</v>
+        <v>90894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14302,6 +14302,4056 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128693341</v>
+      </c>
+      <c r="B131" t="n">
+        <v>86751</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>729192</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6367827</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128693331</v>
+      </c>
+      <c r="B132" t="n">
+        <v>90897</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>729278</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6367590</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128693337</v>
+      </c>
+      <c r="B133" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>729276</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6367578</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128698487</v>
+      </c>
+      <c r="B134" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>729255</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6367567</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128693300</v>
+      </c>
+      <c r="B135" t="n">
+        <v>92766</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>729311</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6367609</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128698483</v>
+      </c>
+      <c r="B136" t="n">
+        <v>105630</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>729260</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6367646</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128698489</v>
+      </c>
+      <c r="B137" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6367618</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128700405</v>
+      </c>
+      <c r="B138" t="n">
+        <v>86925</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>729300</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6367577</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128698472</v>
+      </c>
+      <c r="B139" t="n">
+        <v>86925</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>729284</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6367626</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128698459</v>
+      </c>
+      <c r="B140" t="n">
+        <v>86970</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>729257</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6367641</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128693303</v>
+      </c>
+      <c r="B141" t="n">
+        <v>86925</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>729311</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6367596</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128693342</v>
+      </c>
+      <c r="B142" t="n">
+        <v>86751</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>729241</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6367592</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128693299</v>
+      </c>
+      <c r="B143" t="n">
+        <v>92766</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>729191</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6367801</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128698473</v>
+      </c>
+      <c r="B144" t="n">
+        <v>86925</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>729278</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6367631</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128698494</v>
+      </c>
+      <c r="B145" t="n">
+        <v>86912</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Narrspindling</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Cortinarius pseudoarcuatorum</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>729262</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6367640</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128698471</v>
+      </c>
+      <c r="B146" t="n">
+        <v>86925</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>729291</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6367618</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128693333</v>
+      </c>
+      <c r="B147" t="n">
+        <v>90886</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>729244</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6367576</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128693297</v>
+      </c>
+      <c r="B148" t="n">
+        <v>86773</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>424</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>729184</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6367808</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>128693293</v>
+      </c>
+      <c r="B149" t="n">
+        <v>86970</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>729196</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6367804</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>128693307</v>
+      </c>
+      <c r="B150" t="n">
+        <v>90999</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>729261</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6367585</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>128693327</v>
+      </c>
+      <c r="B151" t="n">
+        <v>86947</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>449</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>729261</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6367585</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>128693335</v>
+      </c>
+      <c r="B152" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>729198</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6367846</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>128698475</v>
+      </c>
+      <c r="B153" t="n">
+        <v>86912</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Narrspindling</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Cortinarius pseudoarcuatorum</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>729259</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6367635</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>128698476</v>
+      </c>
+      <c r="B154" t="n">
+        <v>86912</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Narrspindling</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Cortinarius pseudoarcuatorum</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>729270</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6367626</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>128700660</v>
+      </c>
+      <c r="B155" t="n">
+        <v>86925</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>729278</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6367669</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>128698488</v>
+      </c>
+      <c r="B156" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>729159</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6367521</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>128698484</v>
+      </c>
+      <c r="B157" t="n">
+        <v>86947</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>449</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>729261</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6367615</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>128700501</v>
+      </c>
+      <c r="B158" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>729268</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6367544</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>128693295</v>
+      </c>
+      <c r="B159" t="n">
+        <v>88660</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Toppvaxing</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>729221</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6367854</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>128693336</v>
+      </c>
+      <c r="B160" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>729237</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6367593</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>128700626</v>
+      </c>
+      <c r="B161" t="n">
+        <v>98607</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>729278</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6367669</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>128693324</v>
+      </c>
+      <c r="B162" t="n">
+        <v>91883</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>729284</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6367580</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>128693326</v>
+      </c>
+      <c r="B163" t="n">
+        <v>86947</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>449</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>729164</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6367575</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>128700430</v>
+      </c>
+      <c r="B164" t="n">
+        <v>86925</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>729302</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6367546</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>128693328</v>
+      </c>
+      <c r="B165" t="n">
+        <v>86947</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>449</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>729292</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6367593</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>128693340</v>
+      </c>
+      <c r="B166" t="n">
+        <v>86751</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>729188</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6367797</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>128693330</v>
+      </c>
+      <c r="B167" t="n">
+        <v>86947</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>449</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>729294</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6367598</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>128693294</v>
+      </c>
+      <c r="B168" t="n">
+        <v>86970</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Kalktallskog V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>729183</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6367808</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>128698490</v>
+      </c>
+      <c r="B169" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>729277</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6367576</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>128698465</v>
+      </c>
+      <c r="B170" t="n">
+        <v>90898</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Rödbrun jordstjärna</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Geastrum rufescens</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>729275</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6367651</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>128698485</v>
+      </c>
+      <c r="B171" t="n">
+        <v>86947</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>449</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>V Skogby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>729283</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6367586</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY171"/>
+  <dimension ref="A1:AY172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B128" t="n">
-        <v>92399</v>
+        <v>90999</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B129" t="n">
-        <v>90999</v>
+        <v>92399</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B134" t="n">
-        <v>92788</v>
+        <v>92766</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R134" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B135" t="n">
-        <v>92766</v>
+        <v>92788</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R135" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,12 +14782,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14988,7 +14988,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128700405</v>
+        <v>128698472</v>
       </c>
       <c r="B138" t="n">
         <v>86925</v>
@@ -15019,14 +15019,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729300</v>
+        <v>729284</v>
       </c>
       <c r="R138" t="n">
-        <v>6367577</v>
+        <v>6367626</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,71 +15056,62 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698472</v>
+        <v>128698459</v>
       </c>
       <c r="B139" t="n">
-        <v>86925</v>
+        <v>86970</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15130,10 +15121,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729284</v>
+        <v>729257</v>
       </c>
       <c r="R139" t="n">
-        <v>6367626</v>
+        <v>6367641</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15174,7 +15165,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15193,45 +15183,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128698459</v>
+        <v>128700405</v>
       </c>
       <c r="B140" t="n">
-        <v>86970</v>
+        <v>86925</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729257</v>
+        <v>729300</v>
       </c>
       <c r="R140" t="n">
-        <v>6367641</v>
+        <v>6367577</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15261,9 +15251,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15278,12 +15278,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15680,45 +15680,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698494</v>
+        <v>128693333</v>
       </c>
       <c r="B145" t="n">
-        <v>86912</v>
+        <v>90886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3599</v>
+        <v>4188</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729262</v>
+        <v>729244</v>
       </c>
       <c r="R145" t="n">
-        <v>6367640</v>
+        <v>6367576</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15765,57 +15765,57 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128698471</v>
+        <v>128693297</v>
       </c>
       <c r="B146" t="n">
-        <v>86925</v>
+        <v>86773</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729291</v>
+        <v>729184</v>
       </c>
       <c r="R146" t="n">
-        <v>6367618</v>
+        <v>6367808</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15856,51 +15856,50 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693333</v>
+        <v>128693293</v>
       </c>
       <c r="B147" t="n">
-        <v>90886</v>
+        <v>86970</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4188</v>
+        <v>3767</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15910,10 +15909,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729244</v>
+        <v>729196</v>
       </c>
       <c r="R147" t="n">
-        <v>6367576</v>
+        <v>6367804</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15972,10 +15971,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693297</v>
+        <v>128693307</v>
       </c>
       <c r="B148" t="n">
-        <v>86773</v>
+        <v>90999</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15983,21 +15982,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>424</v>
+        <v>5747</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16007,10 +16006,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729184</v>
+        <v>729261</v>
       </c>
       <c r="R148" t="n">
-        <v>6367808</v>
+        <v>6367585</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16069,10 +16068,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128693293</v>
+        <v>128698494</v>
       </c>
       <c r="B149" t="n">
-        <v>86970</v>
+        <v>86912</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16080,34 +16079,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729196</v>
+        <v>729262</v>
       </c>
       <c r="R149" t="n">
-        <v>6367804</v>
+        <v>6367640</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16154,57 +16153,57 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693307</v>
+        <v>128698471</v>
       </c>
       <c r="B150" t="n">
-        <v>90999</v>
+        <v>86925</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729261</v>
+        <v>729291</v>
       </c>
       <c r="R150" t="n">
-        <v>6367585</v>
+        <v>6367618</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16245,18 +16244,19 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -18353,6 +18353,113 @@
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>128717177</v>
+      </c>
+      <c r="B172" t="n">
+        <v>86753</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>729190</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6367463</v>
+      </c>
+      <c r="S172" t="n">
+        <v>20</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13210,7 +13210,7 @@
         <v>128472799</v>
       </c>
       <c r="B120" t="n">
-        <v>86947</v>
+        <v>86949</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>128473008</v>
       </c>
       <c r="B121" t="n">
-        <v>86888</v>
+        <v>86890</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>128520851</v>
       </c>
       <c r="B122" t="n">
-        <v>86751</v>
+        <v>86753</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>128512741</v>
       </c>
       <c r="B125" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90886</v>
+        <v>90888</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B128" t="n">
-        <v>90999</v>
+        <v>92401</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B129" t="n">
-        <v>92399</v>
+        <v>91001</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90894</v>
+        <v>90896</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B131" t="n">
-        <v>86751</v>
+        <v>90899</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R131" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B132" t="n">
-        <v>90897</v>
+        <v>86753</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R132" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>128693300</v>
       </c>
       <c r="B134" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128698487</v>
       </c>
       <c r="B135" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14794,10 +14794,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128698483</v>
+        <v>128698489</v>
       </c>
       <c r="B136" t="n">
-        <v>105630</v>
+        <v>92790</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14805,21 +14805,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14829,10 +14829,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R136" t="n">
-        <v>6367646</v>
+        <v>6367618</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14891,10 +14891,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128698489</v>
+        <v>128698483</v>
       </c>
       <c r="B137" t="n">
-        <v>92788</v>
+        <v>105642</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14902,21 +14902,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R137" t="n">
-        <v>6367618</v>
+        <v>6367646</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14991,7 +14991,7 @@
         <v>128698472</v>
       </c>
       <c r="B138" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>128698459</v>
       </c>
       <c r="B139" t="n">
-        <v>86970</v>
+        <v>86972</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>128700405</v>
       </c>
       <c r="B140" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>128693303</v>
       </c>
       <c r="B141" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>128693342</v>
       </c>
       <c r="B142" t="n">
-        <v>86751</v>
+        <v>86753</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>128693299</v>
       </c>
       <c r="B143" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>128698473</v>
       </c>
       <c r="B144" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>128693333</v>
       </c>
       <c r="B145" t="n">
-        <v>90886</v>
+        <v>90888</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15777,10 +15777,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128693297</v>
+        <v>128698494</v>
       </c>
       <c r="B146" t="n">
-        <v>86773</v>
+        <v>86914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15788,34 +15788,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>424</v>
+        <v>3599</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729184</v>
+        <v>729262</v>
       </c>
       <c r="R146" t="n">
-        <v>6367808</v>
+        <v>6367640</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15862,12 +15862,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -15877,7 +15877,7 @@
         <v>128693293</v>
       </c>
       <c r="B147" t="n">
-        <v>86970</v>
+        <v>86972</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15971,10 +15971,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693307</v>
+        <v>128693297</v>
       </c>
       <c r="B148" t="n">
-        <v>90999</v>
+        <v>86775</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15982,21 +15982,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5747</v>
+        <v>424</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729261</v>
+        <v>729184</v>
       </c>
       <c r="R148" t="n">
-        <v>6367585</v>
+        <v>6367808</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16068,10 +16068,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128698494</v>
+        <v>128693307</v>
       </c>
       <c r="B149" t="n">
-        <v>86912</v>
+        <v>91001</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16079,34 +16079,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3599</v>
+        <v>5747</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729262</v>
+        <v>729261</v>
       </c>
       <c r="R149" t="n">
-        <v>6367640</v>
+        <v>6367585</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16153,12 +16153,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -16168,7 +16168,7 @@
         <v>128698471</v>
       </c>
       <c r="B150" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>128693327</v>
       </c>
       <c r="B151" t="n">
-        <v>86947</v>
+        <v>86949</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>128693335</v>
       </c>
       <c r="B152" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>128698475</v>
       </c>
       <c r="B153" t="n">
-        <v>86912</v>
+        <v>86914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>128698476</v>
       </c>
       <c r="B154" t="n">
-        <v>86912</v>
+        <v>86914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>128700660</v>
       </c>
       <c r="B155" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>128698488</v>
       </c>
       <c r="B156" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16859,45 +16859,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128698484</v>
+        <v>128693336</v>
       </c>
       <c r="B157" t="n">
-        <v>86947</v>
+        <v>92790</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729261</v>
+        <v>729237</v>
       </c>
       <c r="R157" t="n">
-        <v>6367615</v>
+        <v>6367593</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16938,28 +16941,29 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128700501</v>
+        <v>128693295</v>
       </c>
       <c r="B158" t="n">
-        <v>92788</v>
+        <v>88662</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16967,34 +16971,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729268</v>
+        <v>729221</v>
       </c>
       <c r="R158" t="n">
-        <v>6367544</v>
+        <v>6367854</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17024,19 +17028,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17051,22 +17045,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128693295</v>
+        <v>128700501</v>
       </c>
       <c r="B159" t="n">
-        <v>88660</v>
+        <v>92790</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17074,34 +17068,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4379</v>
+        <v>5964</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729221</v>
+        <v>729268</v>
       </c>
       <c r="R159" t="n">
-        <v>6367854</v>
+        <v>6367544</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17131,9 +17125,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17148,60 +17152,57 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128693336</v>
+        <v>128698484</v>
       </c>
       <c r="B160" t="n">
-        <v>92788</v>
+        <v>86949</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729237</v>
+        <v>729261</v>
       </c>
       <c r="R160" t="n">
-        <v>6367593</v>
+        <v>6367615</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17242,19 +17243,18 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17264,7 +17264,7 @@
         <v>128700626</v>
       </c>
       <c r="B161" t="n">
-        <v>98607</v>
+        <v>98610</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17368,32 +17368,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128693324</v>
+        <v>128693326</v>
       </c>
       <c r="B162" t="n">
-        <v>91883</v>
+        <v>86949</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5420</v>
+        <v>449</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17403,10 +17403,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729284</v>
+        <v>729164</v>
       </c>
       <c r="R162" t="n">
-        <v>6367580</v>
+        <v>6367575</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17465,32 +17465,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128693326</v>
+        <v>128693324</v>
       </c>
       <c r="B163" t="n">
-        <v>86947</v>
+        <v>91885</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>449</v>
+        <v>5420</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17500,10 +17500,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>729164</v>
+        <v>729284</v>
       </c>
       <c r="R163" t="n">
-        <v>6367575</v>
+        <v>6367580</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17565,7 +17565,7 @@
         <v>128700430</v>
       </c>
       <c r="B164" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>128693328</v>
       </c>
       <c r="B165" t="n">
-        <v>86947</v>
+        <v>86949</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>128693340</v>
       </c>
       <c r="B166" t="n">
-        <v>86751</v>
+        <v>86753</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>128693330</v>
       </c>
       <c r="B167" t="n">
-        <v>86947</v>
+        <v>86949</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>128693294</v>
       </c>
       <c r="B168" t="n">
-        <v>86970</v>
+        <v>86972</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18058,10 +18058,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B169" t="n">
-        <v>92788</v>
+        <v>90900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18069,21 +18069,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R169" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18155,32 +18155,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698465</v>
+        <v>128698485</v>
       </c>
       <c r="B170" t="n">
-        <v>90898</v>
+        <v>86949</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2009</v>
+        <v>449</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18190,10 +18190,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729275</v>
+        <v>729283</v>
       </c>
       <c r="R170" t="n">
-        <v>6367651</v>
+        <v>6367586</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18228,12 +18228,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18252,32 +18258,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B171" t="n">
-        <v>86947</v>
+        <v>92790</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18287,10 +18293,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R171" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18325,18 +18331,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B128" t="n">
-        <v>92401</v>
+        <v>91001</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B129" t="n">
-        <v>91001</v>
+        <v>92401</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14794,10 +14794,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128698489</v>
+        <v>128698483</v>
       </c>
       <c r="B136" t="n">
-        <v>92790</v>
+        <v>105651</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14805,21 +14805,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14829,10 +14829,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R136" t="n">
-        <v>6367618</v>
+        <v>6367646</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14891,10 +14891,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128698483</v>
+        <v>128698489</v>
       </c>
       <c r="B137" t="n">
-        <v>105642</v>
+        <v>92790</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14902,21 +14902,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R137" t="n">
-        <v>6367646</v>
+        <v>6367618</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14988,32 +14988,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128698472</v>
+        <v>128698459</v>
       </c>
       <c r="B138" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15023,10 +15023,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729284</v>
+        <v>729257</v>
       </c>
       <c r="R138" t="n">
-        <v>6367626</v>
+        <v>6367641</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15067,7 +15067,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15086,45 +15085,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698459</v>
+        <v>128700405</v>
       </c>
       <c r="B139" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729257</v>
+        <v>729300</v>
       </c>
       <c r="R139" t="n">
-        <v>6367641</v>
+        <v>6367577</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15154,9 +15153,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15171,19 +15180,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128700405</v>
+        <v>128698472</v>
       </c>
       <c r="B140" t="n">
         <v>86927</v>
@@ -15214,14 +15223,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729300</v>
+        <v>729284</v>
       </c>
       <c r="R140" t="n">
-        <v>6367577</v>
+        <v>6367626</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,39 +15260,30 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15680,45 +15680,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128693333</v>
+        <v>128698494</v>
       </c>
       <c r="B145" t="n">
-        <v>90888</v>
+        <v>86914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4188</v>
+        <v>3599</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729244</v>
+        <v>729262</v>
       </c>
       <c r="R145" t="n">
-        <v>6367576</v>
+        <v>6367640</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15765,44 +15765,44 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128698494</v>
+        <v>128698471</v>
       </c>
       <c r="B146" t="n">
-        <v>86914</v>
+        <v>86927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3599</v>
+        <v>6003295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729262</v>
+        <v>729291</v>
       </c>
       <c r="R146" t="n">
-        <v>6367640</v>
+        <v>6367618</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15856,6 +15856,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15874,10 +15875,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693293</v>
+        <v>128693297</v>
       </c>
       <c r="B147" t="n">
-        <v>86972</v>
+        <v>86775</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15885,21 +15886,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15909,10 +15910,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729196</v>
+        <v>729184</v>
       </c>
       <c r="R147" t="n">
-        <v>6367804</v>
+        <v>6367808</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15971,32 +15972,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693297</v>
+        <v>128693333</v>
       </c>
       <c r="B148" t="n">
-        <v>86775</v>
+        <v>90888</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>424</v>
+        <v>4188</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16006,10 +16007,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729184</v>
+        <v>729244</v>
       </c>
       <c r="R148" t="n">
-        <v>6367808</v>
+        <v>6367576</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16068,10 +16069,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128693307</v>
+        <v>128693293</v>
       </c>
       <c r="B149" t="n">
-        <v>91001</v>
+        <v>86972</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16079,21 +16080,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5747</v>
+        <v>3767</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16103,10 +16104,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729261</v>
+        <v>729196</v>
       </c>
       <c r="R149" t="n">
-        <v>6367585</v>
+        <v>6367804</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16165,45 +16166,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128698471</v>
+        <v>128693307</v>
       </c>
       <c r="B150" t="n">
-        <v>86927</v>
+        <v>91001</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729291</v>
+        <v>729261</v>
       </c>
       <c r="R150" t="n">
-        <v>6367618</v>
+        <v>6367585</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16244,19 +16245,18 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16360,48 +16360,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693335</v>
+        <v>128698475</v>
       </c>
       <c r="B152" t="n">
-        <v>92790</v>
+        <v>86914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729198</v>
+        <v>729259</v>
       </c>
       <c r="R152" t="n">
-        <v>6367846</v>
+        <v>6367635</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16442,64 +16439,66 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128698475</v>
+        <v>128693335</v>
       </c>
       <c r="B153" t="n">
-        <v>86914</v>
+        <v>92790</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R153" t="n">
-        <v>6367635</v>
+        <v>6367846</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16540,18 +16539,19 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -16960,10 +16960,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128693295</v>
+        <v>128700501</v>
       </c>
       <c r="B158" t="n">
-        <v>88662</v>
+        <v>92790</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16971,34 +16971,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4379</v>
+        <v>5964</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729221</v>
+        <v>729268</v>
       </c>
       <c r="R158" t="n">
-        <v>6367854</v>
+        <v>6367544</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17028,9 +17028,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17045,57 +17055,57 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128700501</v>
+        <v>128698484</v>
       </c>
       <c r="B159" t="n">
-        <v>92790</v>
+        <v>86949</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729268</v>
+        <v>729261</v>
       </c>
       <c r="R159" t="n">
-        <v>6367544</v>
+        <v>6367615</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17125,19 +17135,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17152,57 +17152,57 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128698484</v>
+        <v>128693295</v>
       </c>
       <c r="B160" t="n">
-        <v>86949</v>
+        <v>88662</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>449</v>
+        <v>4379</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729261</v>
+        <v>729221</v>
       </c>
       <c r="R160" t="n">
-        <v>6367615</v>
+        <v>6367854</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17249,22 +17249,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128700626</v>
+        <v>128693324</v>
       </c>
       <c r="B161" t="n">
-        <v>98610</v>
+        <v>91885</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17272,34 +17272,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>219862</v>
+        <v>5420</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729278</v>
+        <v>729284</v>
       </c>
       <c r="R161" t="n">
-        <v>6367669</v>
+        <v>6367580</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17329,19 +17329,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17356,12 +17346,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -17465,10 +17455,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B163" t="n">
-        <v>91885</v>
+        <v>98613</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17476,34 +17466,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R163" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17533,9 +17523,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17550,12 +17550,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -18058,32 +18058,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698465</v>
+        <v>128698485</v>
       </c>
       <c r="B169" t="n">
-        <v>90900</v>
+        <v>86949</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2009</v>
+        <v>449</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729275</v>
+        <v>729283</v>
       </c>
       <c r="R169" t="n">
-        <v>6367651</v>
+        <v>6367586</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18131,12 +18131,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18155,32 +18161,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B170" t="n">
-        <v>86949</v>
+        <v>92790</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18190,10 +18196,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R170" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18228,18 +18234,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18258,10 +18258,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B171" t="n">
-        <v>92790</v>
+        <v>90900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18269,21 +18269,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18293,10 +18293,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R171" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14988,32 +14988,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128698459</v>
+        <v>128698472</v>
       </c>
       <c r="B138" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15023,10 +15023,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729257</v>
+        <v>729284</v>
       </c>
       <c r="R138" t="n">
-        <v>6367641</v>
+        <v>6367626</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15067,6 +15067,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15085,45 +15086,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128700405</v>
+        <v>128698459</v>
       </c>
       <c r="B139" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729300</v>
+        <v>729257</v>
       </c>
       <c r="R139" t="n">
-        <v>6367577</v>
+        <v>6367641</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15153,19 +15154,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15180,19 +15171,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128698472</v>
+        <v>128700405</v>
       </c>
       <c r="B140" t="n">
         <v>86927</v>
@@ -15223,14 +15214,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729284</v>
+        <v>729300</v>
       </c>
       <c r="R140" t="n">
-        <v>6367626</v>
+        <v>6367577</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15260,30 +15251,39 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15777,45 +15777,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128698471</v>
+        <v>128693297</v>
       </c>
       <c r="B146" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729291</v>
+        <v>729184</v>
       </c>
       <c r="R146" t="n">
-        <v>6367618</v>
+        <v>6367808</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15856,51 +15856,50 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693297</v>
+        <v>128693333</v>
       </c>
       <c r="B147" t="n">
-        <v>86775</v>
+        <v>90888</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>424</v>
+        <v>4188</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15910,10 +15909,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729184</v>
+        <v>729244</v>
       </c>
       <c r="R147" t="n">
-        <v>6367808</v>
+        <v>6367576</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15972,32 +15971,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693333</v>
+        <v>128693293</v>
       </c>
       <c r="B148" t="n">
-        <v>90888</v>
+        <v>86972</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4188</v>
+        <v>3767</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16007,10 +16006,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729244</v>
+        <v>729196</v>
       </c>
       <c r="R148" t="n">
-        <v>6367576</v>
+        <v>6367804</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16069,10 +16068,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128693293</v>
+        <v>128693307</v>
       </c>
       <c r="B149" t="n">
-        <v>86972</v>
+        <v>91001</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16080,21 +16079,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16104,10 +16103,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729196</v>
+        <v>729261</v>
       </c>
       <c r="R149" t="n">
-        <v>6367804</v>
+        <v>6367585</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16166,45 +16165,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693307</v>
+        <v>128698471</v>
       </c>
       <c r="B150" t="n">
-        <v>91001</v>
+        <v>86927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729261</v>
+        <v>729291</v>
       </c>
       <c r="R150" t="n">
-        <v>6367585</v>
+        <v>6367618</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16245,18 +16244,19 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B165" t="n">
-        <v>86949</v>
+        <v>86753</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R165" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17766,32 +17766,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B166" t="n">
-        <v>86753</v>
+        <v>86949</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17801,10 +17801,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R166" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18161,10 +18161,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B170" t="n">
-        <v>92790</v>
+        <v>90900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18172,21 +18172,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18196,10 +18196,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R170" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18258,10 +18258,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128698465</v>
+        <v>128698490</v>
       </c>
       <c r="B171" t="n">
-        <v>90900</v>
+        <v>92790</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18269,21 +18269,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2009</v>
+        <v>5964</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18293,10 +18293,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>729275</v>
+        <v>729277</v>
       </c>
       <c r="R171" t="n">
-        <v>6367651</v>
+        <v>6367576</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90888</v>
+        <v>90889</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B128" t="n">
-        <v>91001</v>
+        <v>92402</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B129" t="n">
-        <v>92401</v>
+        <v>91002</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90896</v>
+        <v>90897</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>128693331</v>
       </c>
       <c r="B131" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>128693300</v>
       </c>
       <c r="B134" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128698487</v>
       </c>
       <c r="B135" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14794,10 +14794,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128698483</v>
+        <v>128698489</v>
       </c>
       <c r="B136" t="n">
-        <v>105651</v>
+        <v>92791</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14805,21 +14805,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14829,10 +14829,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R136" t="n">
-        <v>6367646</v>
+        <v>6367618</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14891,10 +14891,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128698489</v>
+        <v>128698483</v>
       </c>
       <c r="B137" t="n">
-        <v>92790</v>
+        <v>105654</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14902,21 +14902,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R137" t="n">
-        <v>6367618</v>
+        <v>6367646</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14988,7 +14988,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128698472</v>
+        <v>128700405</v>
       </c>
       <c r="B138" t="n">
         <v>86927</v>
@@ -15019,14 +15019,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729284</v>
+        <v>729300</v>
       </c>
       <c r="R138" t="n">
-        <v>6367626</v>
+        <v>6367577</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,30 +15056,39 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -15183,7 +15192,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128700405</v>
+        <v>128698472</v>
       </c>
       <c r="B140" t="n">
         <v>86927</v>
@@ -15214,14 +15223,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729300</v>
+        <v>729284</v>
       </c>
       <c r="R140" t="n">
-        <v>6367577</v>
+        <v>6367626</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,39 +15260,30 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15488,7 +15488,7 @@
         <v>128693299</v>
       </c>
       <c r="B143" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15680,45 +15680,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698494</v>
+        <v>128693333</v>
       </c>
       <c r="B145" t="n">
-        <v>86914</v>
+        <v>90889</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3599</v>
+        <v>4188</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729262</v>
+        <v>729244</v>
       </c>
       <c r="R145" t="n">
-        <v>6367640</v>
+        <v>6367576</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15765,22 +15765,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128693297</v>
+        <v>128698494</v>
       </c>
       <c r="B146" t="n">
-        <v>86775</v>
+        <v>86914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15788,34 +15788,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>424</v>
+        <v>3599</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729184</v>
+        <v>729262</v>
       </c>
       <c r="R146" t="n">
-        <v>6367808</v>
+        <v>6367640</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15862,44 +15862,44 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693333</v>
+        <v>128693293</v>
       </c>
       <c r="B147" t="n">
-        <v>90888</v>
+        <v>86972</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4188</v>
+        <v>3767</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15909,10 +15909,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729244</v>
+        <v>729196</v>
       </c>
       <c r="R147" t="n">
-        <v>6367576</v>
+        <v>6367804</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15971,45 +15971,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693293</v>
+        <v>128698471</v>
       </c>
       <c r="B148" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729196</v>
+        <v>729291</v>
       </c>
       <c r="R148" t="n">
-        <v>6367804</v>
+        <v>6367618</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16050,18 +16050,19 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16071,7 +16072,7 @@
         <v>128693307</v>
       </c>
       <c r="B149" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16165,45 +16166,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128698471</v>
+        <v>128693327</v>
       </c>
       <c r="B150" t="n">
-        <v>86927</v>
+        <v>86949</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729291</v>
+        <v>729261</v>
       </c>
       <c r="R150" t="n">
-        <v>6367618</v>
+        <v>6367585</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16244,29 +16245,28 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B151" t="n">
-        <v>86949</v>
+        <v>86914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16274,34 +16274,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R151" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16348,57 +16348,60 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128698475</v>
+        <v>128693335</v>
       </c>
       <c r="B152" t="n">
-        <v>86914</v>
+        <v>92791</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R152" t="n">
-        <v>6367635</v>
+        <v>6367846</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16439,66 +16442,64 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128693335</v>
+        <v>128698476</v>
       </c>
       <c r="B153" t="n">
-        <v>92790</v>
+        <v>86914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>729198</v>
+        <v>729270</v>
       </c>
       <c r="R153" t="n">
-        <v>6367846</v>
+        <v>6367626</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16539,64 +16540,63 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128698476</v>
+        <v>128700660</v>
       </c>
       <c r="B154" t="n">
-        <v>86914</v>
+        <v>86927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3599</v>
+        <v>6003295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>729270</v>
+        <v>729278</v>
       </c>
       <c r="R154" t="n">
-        <v>6367626</v>
+        <v>6367669</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16626,9 +16626,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16643,57 +16653,57 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128700660</v>
+        <v>128698488</v>
       </c>
       <c r="B155" t="n">
-        <v>86927</v>
+        <v>92791</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>729278</v>
+        <v>729159</v>
       </c>
       <c r="R155" t="n">
-        <v>6367669</v>
+        <v>6367521</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16723,19 +16733,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16750,44 +16750,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128698488</v>
+        <v>128698484</v>
       </c>
       <c r="B156" t="n">
-        <v>92790</v>
+        <v>86949</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16797,10 +16797,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729159</v>
+        <v>729261</v>
       </c>
       <c r="R156" t="n">
-        <v>6367521</v>
+        <v>6367615</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16859,10 +16859,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128693336</v>
+        <v>128693295</v>
       </c>
       <c r="B157" t="n">
-        <v>92790</v>
+        <v>88662</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16870,37 +16870,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729237</v>
+        <v>729221</v>
       </c>
       <c r="R157" t="n">
-        <v>6367593</v>
+        <v>6367854</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16941,7 +16938,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -16960,10 +16956,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128700501</v>
+        <v>128693336</v>
       </c>
       <c r="B158" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16989,16 +16985,19 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729268</v>
+        <v>729237</v>
       </c>
       <c r="R158" t="n">
-        <v>6367544</v>
+        <v>6367593</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17028,84 +17027,75 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128698484</v>
+        <v>128700501</v>
       </c>
       <c r="B159" t="n">
-        <v>86949</v>
+        <v>92791</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729261</v>
+        <v>729268</v>
       </c>
       <c r="R159" t="n">
-        <v>6367615</v>
+        <v>6367544</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17135,9 +17125,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17152,22 +17152,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128693295</v>
+        <v>128693324</v>
       </c>
       <c r="B160" t="n">
-        <v>88662</v>
+        <v>91886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17175,21 +17175,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4379</v>
+        <v>5420</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17199,10 +17199,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729221</v>
+        <v>729284</v>
       </c>
       <c r="R160" t="n">
-        <v>6367854</v>
+        <v>6367580</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17261,10 +17261,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B161" t="n">
-        <v>91885</v>
+        <v>98614</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17272,34 +17272,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R161" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17329,9 +17329,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17346,12 +17356,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -17455,32 +17465,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128700626</v>
+        <v>128700430</v>
       </c>
       <c r="B163" t="n">
-        <v>98613</v>
+        <v>86927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17490,10 +17500,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>729278</v>
+        <v>729302</v>
       </c>
       <c r="R163" t="n">
-        <v>6367669</v>
+        <v>6367546</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17525,7 +17535,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17535,7 +17545,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17562,45 +17572,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128700430</v>
+        <v>128693328</v>
       </c>
       <c r="B164" t="n">
-        <v>86927</v>
+        <v>86949</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729302</v>
+        <v>729292</v>
       </c>
       <c r="R164" t="n">
-        <v>6367546</v>
+        <v>6367593</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17630,19 +17640,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>12:10</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17657,12 +17657,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -17766,7 +17766,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128693328</v>
+        <v>128693330</v>
       </c>
       <c r="B166" t="n">
         <v>86949</v>
@@ -17801,10 +17801,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>729292</v>
+        <v>729294</v>
       </c>
       <c r="R166" t="n">
-        <v>6367593</v>
+        <v>6367598</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17863,10 +17863,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128693330</v>
+        <v>128693294</v>
       </c>
       <c r="B167" t="n">
-        <v>86949</v>
+        <v>86972</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17874,21 +17874,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17898,10 +17898,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>729294</v>
+        <v>729183</v>
       </c>
       <c r="R167" t="n">
-        <v>6367598</v>
+        <v>6367808</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17942,6 +17942,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17960,45 +17961,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128693294</v>
+        <v>128698465</v>
       </c>
       <c r="B168" t="n">
-        <v>86972</v>
+        <v>90901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3767</v>
+        <v>2009</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729183</v>
+        <v>729275</v>
       </c>
       <c r="R168" t="n">
-        <v>6367808</v>
+        <v>6367651</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18039,51 +18040,50 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B169" t="n">
-        <v>86949</v>
+        <v>92791</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R169" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18131,18 +18131,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18161,32 +18155,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698465</v>
+        <v>128698485</v>
       </c>
       <c r="B170" t="n">
-        <v>90900</v>
+        <v>86949</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2009</v>
+        <v>449</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18196,10 +18190,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729275</v>
+        <v>729283</v>
       </c>
       <c r="R170" t="n">
-        <v>6367651</v>
+        <v>6367586</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18234,12 +18228,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18258,10 +18258,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128698490</v>
+        <v>128717177</v>
       </c>
       <c r="B171" t="n">
-        <v>92790</v>
+        <v>86753</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18269,37 +18269,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>729277</v>
+        <v>729190</v>
       </c>
       <c r="R171" t="n">
-        <v>6367576</v>
+        <v>6367463</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18326,9 +18326,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18343,60 +18353,60 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128717177</v>
+        <v>128693297</v>
       </c>
       <c r="B172" t="n">
-        <v>86753</v>
+        <v>86775</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>729190</v>
+        <v>729184</v>
       </c>
       <c r="R172" t="n">
-        <v>6367463</v>
+        <v>6367808</v>
       </c>
       <c r="S172" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18423,19 +18433,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>13:51</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18450,12 +18450,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13424,7 +13424,7 @@
         <v>128520851</v>
       </c>
       <c r="B122" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>128512741</v>
       </c>
       <c r="B125" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90889</v>
+        <v>90916</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>128512738</v>
       </c>
       <c r="B128" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>128512742</v>
       </c>
       <c r="B129" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90897</v>
+        <v>90924</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B131" t="n">
-        <v>90900</v>
+        <v>86780</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R131" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14395,39 +14395,39 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B132" t="n">
-        <v>86753</v>
+        <v>90927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R132" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14603,7 +14603,7 @@
         <v>128693300</v>
       </c>
       <c r="B134" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14700,7 +14700,7 @@
         <v>128698487</v>
       </c>
       <c r="B135" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>128698489</v>
       </c>
       <c r="B136" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>128698483</v>
       </c>
       <c r="B137" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14988,45 +14988,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128700405</v>
+        <v>128698459</v>
       </c>
       <c r="B138" t="n">
-        <v>86927</v>
+        <v>86999</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729300</v>
+        <v>729257</v>
       </c>
       <c r="R138" t="n">
-        <v>6367577</v>
+        <v>6367641</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,19 +15056,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15083,57 +15073,57 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698459</v>
+        <v>128700405</v>
       </c>
       <c r="B139" t="n">
-        <v>86972</v>
+        <v>86954</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729257</v>
+        <v>729300</v>
       </c>
       <c r="R139" t="n">
-        <v>6367641</v>
+        <v>6367577</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15163,9 +15153,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15180,12 +15180,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -15195,7 +15195,7 @@
         <v>128698472</v>
       </c>
       <c r="B140" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15290,32 +15290,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128693303</v>
+        <v>128693342</v>
       </c>
       <c r="B141" t="n">
-        <v>86927</v>
+        <v>86780</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15325,10 +15325,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>729311</v>
+        <v>729241</v>
       </c>
       <c r="R141" t="n">
-        <v>6367596</v>
+        <v>6367592</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15369,7 +15369,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15381,39 +15380,39 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128693342</v>
+        <v>128693303</v>
       </c>
       <c r="B142" t="n">
-        <v>86753</v>
+        <v>86954</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15423,10 +15422,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>729241</v>
+        <v>729311</v>
       </c>
       <c r="R142" t="n">
-        <v>6367592</v>
+        <v>6367596</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15467,6 +15466,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15488,7 +15488,7 @@
         <v>128693299</v>
       </c>
       <c r="B143" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15585,7 +15585,7 @@
         <v>128698473</v>
       </c>
       <c r="B144" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15680,45 +15680,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128693333</v>
+        <v>128698471</v>
       </c>
       <c r="B145" t="n">
-        <v>90889</v>
+        <v>86954</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4188</v>
+        <v>6003295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729244</v>
+        <v>729291</v>
       </c>
       <c r="R145" t="n">
-        <v>6367576</v>
+        <v>6367618</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15759,28 +15759,29 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128698494</v>
+        <v>128693307</v>
       </c>
       <c r="B146" t="n">
-        <v>86914</v>
+        <v>91029</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15788,34 +15789,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3599</v>
+        <v>5747</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729262</v>
+        <v>729261</v>
       </c>
       <c r="R146" t="n">
-        <v>6367640</v>
+        <v>6367585</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15862,44 +15863,44 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693293</v>
+        <v>128693333</v>
       </c>
       <c r="B147" t="n">
-        <v>86972</v>
+        <v>90916</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3767</v>
+        <v>4188</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15909,10 +15910,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729196</v>
+        <v>729244</v>
       </c>
       <c r="R147" t="n">
-        <v>6367804</v>
+        <v>6367576</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15964,39 +15965,39 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128698471</v>
+        <v>128698494</v>
       </c>
       <c r="B148" t="n">
-        <v>86927</v>
+        <v>86941</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6003295</v>
+        <v>3599</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16006,10 +16007,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729291</v>
+        <v>729262</v>
       </c>
       <c r="R148" t="n">
-        <v>6367618</v>
+        <v>6367640</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16050,7 +16051,6 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -16069,10 +16069,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128693307</v>
+        <v>128693293</v>
       </c>
       <c r="B149" t="n">
-        <v>91002</v>
+        <v>86999</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16080,21 +16080,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5747</v>
+        <v>3767</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16104,10 +16104,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729261</v>
+        <v>729196</v>
       </c>
       <c r="R149" t="n">
-        <v>6367585</v>
+        <v>6367804</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16159,52 +16159,55 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693327</v>
+        <v>128693335</v>
       </c>
       <c r="B150" t="n">
-        <v>86949</v>
+        <v>92818</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729261</v>
+        <v>729198</v>
       </c>
       <c r="R150" t="n">
-        <v>6367585</v>
+        <v>6367846</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16245,6 +16248,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16256,7 +16260,7 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16266,7 +16270,7 @@
         <v>128698475</v>
       </c>
       <c r="B151" t="n">
-        <v>86914</v>
+        <v>86941</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16360,48 +16364,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B152" t="n">
-        <v>92791</v>
+        <v>86976</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R152" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16442,7 +16443,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16464,7 +16464,7 @@
         <v>128698476</v>
       </c>
       <c r="B153" t="n">
-        <v>86914</v>
+        <v>86941</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>128700660</v>
       </c>
       <c r="B154" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>128698488</v>
       </c>
       <c r="B155" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16762,45 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128698484</v>
+        <v>128700501</v>
       </c>
       <c r="B156" t="n">
-        <v>86949</v>
+        <v>92818</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729261</v>
+        <v>729268</v>
       </c>
       <c r="R156" t="n">
-        <v>6367615</v>
+        <v>6367544</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16830,9 +16830,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16847,22 +16857,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128693295</v>
+        <v>128693336</v>
       </c>
       <c r="B157" t="n">
-        <v>88662</v>
+        <v>92818</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16870,34 +16880,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4379</v>
+        <v>5964</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729221</v>
+        <v>729237</v>
       </c>
       <c r="R157" t="n">
-        <v>6367854</v>
+        <v>6367593</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16938,6 +16951,7 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -16949,55 +16963,52 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128693336</v>
+        <v>128698484</v>
       </c>
       <c r="B158" t="n">
-        <v>92791</v>
+        <v>86976</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729237</v>
+        <v>729261</v>
       </c>
       <c r="R158" t="n">
-        <v>6367593</v>
+        <v>6367615</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17038,29 +17049,28 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128700501</v>
+        <v>128693295</v>
       </c>
       <c r="B159" t="n">
-        <v>92791</v>
+        <v>88689</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17068,34 +17078,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729268</v>
+        <v>729221</v>
       </c>
       <c r="R159" t="n">
-        <v>6367544</v>
+        <v>6367854</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17125,19 +17135,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17152,12 +17152,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
         <v>128693324</v>
       </c>
       <c r="B160" t="n">
-        <v>91886</v>
+        <v>91913</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen, Liam Sebestyén, Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17264,7 +17264,7 @@
         <v>128700626</v>
       </c>
       <c r="B161" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>128693326</v>
       </c>
       <c r="B162" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
         <v>128700430</v>
       </c>
       <c r="B163" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B164" t="n">
-        <v>86949</v>
+        <v>86780</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R164" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17662,39 +17662,39 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B165" t="n">
-        <v>86753</v>
+        <v>86976</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R165" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
         <v>128693330</v>
       </c>
       <c r="B166" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -17866,7 +17866,7 @@
         <v>128693294</v>
       </c>
       <c r="B167" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17954,17 +17954,17 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698465</v>
+        <v>128698490</v>
       </c>
       <c r="B168" t="n">
-        <v>90901</v>
+        <v>92818</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17972,21 +17972,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2009</v>
+        <v>5964</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729275</v>
+        <v>729277</v>
       </c>
       <c r="R168" t="n">
-        <v>6367651</v>
+        <v>6367576</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18058,10 +18058,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B169" t="n">
-        <v>92791</v>
+        <v>90928</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18069,21 +18069,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R169" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18158,7 +18158,7 @@
         <v>128698485</v>
       </c>
       <c r="B170" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>128717177</v>
       </c>
       <c r="B171" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>128693297</v>
       </c>
       <c r="B172" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13210,7 +13210,7 @@
         <v>128472799</v>
       </c>
       <c r="B120" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>128473008</v>
       </c>
       <c r="B121" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B128" t="n">
-        <v>92429</v>
+        <v>91029</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B129" t="n">
-        <v>91029</v>
+        <v>92429</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14794,10 +14794,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128698489</v>
+        <v>128698483</v>
       </c>
       <c r="B136" t="n">
-        <v>92818</v>
+        <v>105682</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14805,21 +14805,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14829,10 +14829,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R136" t="n">
-        <v>6367618</v>
+        <v>6367646</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14891,10 +14891,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128698483</v>
+        <v>128698489</v>
       </c>
       <c r="B137" t="n">
-        <v>105682</v>
+        <v>92818</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14902,21 +14902,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R137" t="n">
-        <v>6367646</v>
+        <v>6367618</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14988,45 +14988,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128698459</v>
+        <v>128700405</v>
       </c>
       <c r="B138" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729257</v>
+        <v>729300</v>
       </c>
       <c r="R138" t="n">
-        <v>6367641</v>
+        <v>6367577</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,9 +15056,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15073,57 +15083,57 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128700405</v>
+        <v>128698459</v>
       </c>
       <c r="B139" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729300</v>
+        <v>729257</v>
       </c>
       <c r="R139" t="n">
-        <v>6367577</v>
+        <v>6367641</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15153,19 +15163,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15180,12 +15180,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15680,45 +15680,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698471</v>
+        <v>128693333</v>
       </c>
       <c r="B145" t="n">
-        <v>86954</v>
+        <v>90916</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6003295</v>
+        <v>4188</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729291</v>
+        <v>729244</v>
       </c>
       <c r="R145" t="n">
-        <v>6367618</v>
+        <v>6367576</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15759,19 +15759,18 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15868,52 +15867,52 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693333</v>
+        <v>128698494</v>
       </c>
       <c r="B147" t="n">
-        <v>90916</v>
+        <v>86941</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4188</v>
+        <v>3599</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729244</v>
+        <v>729262</v>
       </c>
       <c r="R147" t="n">
-        <v>6367576</v>
+        <v>6367640</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15960,22 +15959,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128698494</v>
+        <v>128693293</v>
       </c>
       <c r="B148" t="n">
-        <v>86941</v>
+        <v>86999</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15983,34 +15982,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729262</v>
+        <v>729196</v>
       </c>
       <c r="R148" t="n">
-        <v>6367640</v>
+        <v>6367804</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16057,57 +16056,57 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128693293</v>
+        <v>128698471</v>
       </c>
       <c r="B149" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729196</v>
+        <v>729291</v>
       </c>
       <c r="R149" t="n">
-        <v>6367804</v>
+        <v>6367618</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16148,66 +16147,64 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B150" t="n">
-        <v>92818</v>
+        <v>86976</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R150" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16248,7 +16245,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16260,52 +16256,55 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128698475</v>
+        <v>128693335</v>
       </c>
       <c r="B151" t="n">
-        <v>86941</v>
+        <v>92818</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R151" t="n">
-        <v>6367635</v>
+        <v>6367846</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16346,28 +16345,29 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B152" t="n">
-        <v>86976</v>
+        <v>86941</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16375,34 +16375,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R152" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16449,12 +16449,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16869,48 +16869,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128693336</v>
+        <v>128698484</v>
       </c>
       <c r="B157" t="n">
-        <v>92818</v>
+        <v>86976</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729237</v>
+        <v>729261</v>
       </c>
       <c r="R157" t="n">
-        <v>6367593</v>
+        <v>6367615</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16951,64 +16948,63 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128698484</v>
+        <v>128693295</v>
       </c>
       <c r="B158" t="n">
-        <v>86976</v>
+        <v>88689</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>449</v>
+        <v>4379</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729261</v>
+        <v>729221</v>
       </c>
       <c r="R158" t="n">
-        <v>6367615</v>
+        <v>6367854</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17055,22 +17051,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128693295</v>
+        <v>128693336</v>
       </c>
       <c r="B159" t="n">
-        <v>88689</v>
+        <v>92818</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17078,34 +17074,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4379</v>
+        <v>5964</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729221</v>
+        <v>729237</v>
       </c>
       <c r="R159" t="n">
-        <v>6367854</v>
+        <v>6367593</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17146,6 +17145,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -17157,17 +17157,17 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B160" t="n">
-        <v>91913</v>
+        <v>98641</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17175,34 +17175,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R160" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,9 +17232,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17249,57 +17259,57 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128700626</v>
+        <v>128693326</v>
       </c>
       <c r="B161" t="n">
-        <v>98641</v>
+        <v>86976</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729278</v>
+        <v>729164</v>
       </c>
       <c r="R161" t="n">
-        <v>6367669</v>
+        <v>6367575</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17329,19 +17339,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17356,44 +17356,44 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128693326</v>
+        <v>128693324</v>
       </c>
       <c r="B162" t="n">
-        <v>86976</v>
+        <v>91913</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>449</v>
+        <v>5420</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17403,10 +17403,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729164</v>
+        <v>729284</v>
       </c>
       <c r="R162" t="n">
-        <v>6367575</v>
+        <v>6367580</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -17954,39 +17954,39 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén, Martin Axegård</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698490</v>
+        <v>128698485</v>
       </c>
       <c r="B168" t="n">
-        <v>92818</v>
+        <v>86976</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729277</v>
+        <v>729283</v>
       </c>
       <c r="R168" t="n">
-        <v>6367576</v>
+        <v>6367586</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18034,12 +18034,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -18058,10 +18064,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698465</v>
+        <v>128698490</v>
       </c>
       <c r="B169" t="n">
-        <v>90928</v>
+        <v>92818</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18069,21 +18075,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2009</v>
+        <v>5964</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18099,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729275</v>
+        <v>729277</v>
       </c>
       <c r="R169" t="n">
-        <v>6367651</v>
+        <v>6367576</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18155,32 +18161,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698485</v>
+        <v>128698465</v>
       </c>
       <c r="B170" t="n">
-        <v>86976</v>
+        <v>90928</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>449</v>
+        <v>2009</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18190,10 +18196,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729283</v>
+        <v>729275</v>
       </c>
       <c r="R170" t="n">
-        <v>6367586</v>
+        <v>6367651</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18228,18 +18234,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18455,7 +18455,7 @@
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13424,7 +13424,7 @@
         <v>128520851</v>
       </c>
       <c r="B122" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>128512741</v>
       </c>
       <c r="B125" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90916</v>
+        <v>90921</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B128" t="n">
-        <v>91029</v>
+        <v>92434</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B129" t="n">
-        <v>92429</v>
+        <v>91034</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90924</v>
+        <v>90929</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>128693341</v>
       </c>
       <c r="B131" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>128693331</v>
       </c>
       <c r="B132" t="n">
-        <v>90927</v>
+        <v>90932</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B134" t="n">
-        <v>92796</v>
+        <v>92823</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R134" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B135" t="n">
-        <v>92818</v>
+        <v>92801</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R135" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,12 +14782,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14797,7 +14797,7 @@
         <v>128698483</v>
       </c>
       <c r="B136" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>128698489</v>
       </c>
       <c r="B137" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14988,10 +14988,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128700405</v>
+        <v>128698472</v>
       </c>
       <c r="B138" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15019,14 +15019,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729300</v>
+        <v>729284</v>
       </c>
       <c r="R138" t="n">
-        <v>6367577</v>
+        <v>6367626</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,84 +15056,75 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698459</v>
+        <v>128700405</v>
       </c>
       <c r="B139" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729257</v>
+        <v>729300</v>
       </c>
       <c r="R139" t="n">
-        <v>6367641</v>
+        <v>6367577</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15163,9 +15154,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15180,44 +15181,44 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128698472</v>
+        <v>128698459</v>
       </c>
       <c r="B140" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15227,10 +15228,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729284</v>
+        <v>729257</v>
       </c>
       <c r="R140" t="n">
-        <v>6367626</v>
+        <v>6367641</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15271,7 +15272,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15293,7 +15293,7 @@
         <v>128693342</v>
       </c>
       <c r="B141" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>128693303</v>
       </c>
       <c r="B142" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>128693299</v>
       </c>
       <c r="B143" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>128698473</v>
       </c>
       <c r="B144" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15680,32 +15680,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128693333</v>
+        <v>128693307</v>
       </c>
       <c r="B145" t="n">
-        <v>90916</v>
+        <v>91034</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4188</v>
+        <v>5747</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15715,10 +15715,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729244</v>
+        <v>729261</v>
       </c>
       <c r="R145" t="n">
-        <v>6367576</v>
+        <v>6367585</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15777,32 +15777,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128693307</v>
+        <v>128693333</v>
       </c>
       <c r="B146" t="n">
-        <v>91029</v>
+        <v>90921</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5747</v>
+        <v>4188</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729261</v>
+        <v>729244</v>
       </c>
       <c r="R146" t="n">
-        <v>6367585</v>
+        <v>6367576</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15877,7 +15877,7 @@
         <v>128698494</v>
       </c>
       <c r="B147" t="n">
-        <v>86941</v>
+        <v>86945</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>128693293</v>
       </c>
       <c r="B148" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16071,7 +16071,7 @@
         <v>128698471</v>
       </c>
       <c r="B149" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16166,45 +16166,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693327</v>
+        <v>128693335</v>
       </c>
       <c r="B150" t="n">
-        <v>86976</v>
+        <v>92823</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729261</v>
+        <v>729198</v>
       </c>
       <c r="R150" t="n">
-        <v>6367585</v>
+        <v>6367846</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16245,6 +16248,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16263,48 +16267,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128693335</v>
+        <v>128698475</v>
       </c>
       <c r="B151" t="n">
-        <v>92818</v>
+        <v>86945</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729198</v>
+        <v>729259</v>
       </c>
       <c r="R151" t="n">
-        <v>6367846</v>
+        <v>6367635</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16345,29 +16346,28 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128698475</v>
+        <v>128693327</v>
       </c>
       <c r="B152" t="n">
-        <v>86941</v>
+        <v>86980</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16375,34 +16375,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3599</v>
+        <v>449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729259</v>
+        <v>729261</v>
       </c>
       <c r="R152" t="n">
-        <v>6367635</v>
+        <v>6367585</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16449,12 +16449,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16464,7 +16464,7 @@
         <v>128698476</v>
       </c>
       <c r="B153" t="n">
-        <v>86941</v>
+        <v>86945</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>128700660</v>
       </c>
       <c r="B154" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>128698488</v>
       </c>
       <c r="B155" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16762,10 +16762,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128700501</v>
+        <v>128693295</v>
       </c>
       <c r="B156" t="n">
-        <v>92818</v>
+        <v>88693</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16773,34 +16773,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729268</v>
+        <v>729221</v>
       </c>
       <c r="R156" t="n">
-        <v>6367544</v>
+        <v>6367854</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16830,19 +16830,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16857,57 +16847,60 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128698484</v>
+        <v>128693336</v>
       </c>
       <c r="B157" t="n">
-        <v>86976</v>
+        <v>92823</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729261</v>
+        <v>729237</v>
       </c>
       <c r="R157" t="n">
-        <v>6367615</v>
+        <v>6367593</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16948,63 +16941,64 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128693295</v>
+        <v>128698484</v>
       </c>
       <c r="B158" t="n">
-        <v>88689</v>
+        <v>86980</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4379</v>
+        <v>449</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729221</v>
+        <v>729261</v>
       </c>
       <c r="R158" t="n">
-        <v>6367854</v>
+        <v>6367615</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17051,22 +17045,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128693336</v>
+        <v>128700501</v>
       </c>
       <c r="B159" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17092,19 +17086,16 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729237</v>
+        <v>729268</v>
       </c>
       <c r="R159" t="n">
-        <v>6367593</v>
+        <v>6367544</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17134,40 +17125,49 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128700626</v>
+        <v>128693324</v>
       </c>
       <c r="B160" t="n">
-        <v>98641</v>
+        <v>91918</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17175,34 +17175,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219862</v>
+        <v>5420</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729278</v>
+        <v>729284</v>
       </c>
       <c r="R160" t="n">
-        <v>6367669</v>
+        <v>6367580</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,19 +17232,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17259,12 +17249,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17274,7 +17264,7 @@
         <v>128693326</v>
       </c>
       <c r="B161" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17368,10 +17358,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B162" t="n">
-        <v>91913</v>
+        <v>98647</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17379,34 +17369,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R162" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17436,9 +17426,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
         <v>128700430</v>
       </c>
       <c r="B163" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>128693340</v>
       </c>
       <c r="B164" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>128693328</v>
       </c>
       <c r="B165" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>128693330</v>
       </c>
       <c r="B166" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>128693294</v>
       </c>
       <c r="B167" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17954,39 +17954,39 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén, Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B168" t="n">
-        <v>86976</v>
+        <v>92823</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R168" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18034,18 +18034,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -18064,10 +18058,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B169" t="n">
-        <v>92818</v>
+        <v>90933</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18075,21 +18069,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18099,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R169" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18161,32 +18155,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698465</v>
+        <v>128698485</v>
       </c>
       <c r="B170" t="n">
-        <v>90928</v>
+        <v>86980</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2009</v>
+        <v>449</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18196,10 +18190,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729275</v>
+        <v>729283</v>
       </c>
       <c r="R170" t="n">
-        <v>6367651</v>
+        <v>6367586</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18234,12 +18228,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18261,7 +18261,7 @@
         <v>128717177</v>
       </c>
       <c r="B171" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>128693297</v>
       </c>
       <c r="B172" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13210,7 +13210,7 @@
         <v>128472799</v>
       </c>
       <c r="B120" t="n">
-        <v>86976</v>
+        <v>86981</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>128473008</v>
       </c>
       <c r="B121" t="n">
-        <v>86917</v>
+        <v>86922</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>128512741</v>
       </c>
       <c r="B125" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90921</v>
+        <v>90926</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B128" t="n">
-        <v>92434</v>
+        <v>91039</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B129" t="n">
-        <v>91034</v>
+        <v>92439</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90929</v>
+        <v>90934</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B131" t="n">
-        <v>86784</v>
+        <v>90937</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R131" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B132" t="n">
-        <v>90932</v>
+        <v>86784</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R132" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>128698487</v>
       </c>
       <c r="B134" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128693300</v>
       </c>
       <c r="B135" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14794,10 +14794,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128698483</v>
+        <v>128698489</v>
       </c>
       <c r="B136" t="n">
-        <v>105688</v>
+        <v>92830</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14805,21 +14805,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14829,10 +14829,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R136" t="n">
-        <v>6367646</v>
+        <v>6367618</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14891,10 +14891,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128698489</v>
+        <v>128698483</v>
       </c>
       <c r="B137" t="n">
-        <v>92823</v>
+        <v>105695</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14902,21 +14902,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R137" t="n">
-        <v>6367618</v>
+        <v>6367646</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14991,7 +14991,7 @@
         <v>128698472</v>
       </c>
       <c r="B138" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15086,45 +15086,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128700405</v>
+        <v>128698459</v>
       </c>
       <c r="B139" t="n">
-        <v>86958</v>
+        <v>87004</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729300</v>
+        <v>729257</v>
       </c>
       <c r="R139" t="n">
-        <v>6367577</v>
+        <v>6367641</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15154,19 +15154,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15181,57 +15171,57 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128698459</v>
+        <v>128700405</v>
       </c>
       <c r="B140" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729257</v>
+        <v>729300</v>
       </c>
       <c r="R140" t="n">
-        <v>6367641</v>
+        <v>6367577</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15261,9 +15251,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15278,12 +15278,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15390,7 +15390,7 @@
         <v>128693303</v>
       </c>
       <c r="B142" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>128693299</v>
       </c>
       <c r="B143" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>128698473</v>
       </c>
       <c r="B144" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15680,45 +15680,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128693307</v>
+        <v>128698471</v>
       </c>
       <c r="B145" t="n">
-        <v>91034</v>
+        <v>86959</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729261</v>
+        <v>729291</v>
       </c>
       <c r="R145" t="n">
-        <v>6367585</v>
+        <v>6367618</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15759,50 +15759,51 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128693333</v>
+        <v>128693307</v>
       </c>
       <c r="B146" t="n">
-        <v>90921</v>
+        <v>91039</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4188</v>
+        <v>5747</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15812,10 +15813,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729244</v>
+        <v>729261</v>
       </c>
       <c r="R146" t="n">
-        <v>6367576</v>
+        <v>6367585</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15874,45 +15875,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128698494</v>
+        <v>128693333</v>
       </c>
       <c r="B147" t="n">
-        <v>86945</v>
+        <v>90926</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3599</v>
+        <v>4188</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729262</v>
+        <v>729244</v>
       </c>
       <c r="R147" t="n">
-        <v>6367640</v>
+        <v>6367576</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15959,12 +15960,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -15974,7 +15975,7 @@
         <v>128693293</v>
       </c>
       <c r="B148" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16068,32 +16069,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128698471</v>
+        <v>128698494</v>
       </c>
       <c r="B149" t="n">
-        <v>86958</v>
+        <v>86946</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6003295</v>
+        <v>3599</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16103,10 +16104,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729291</v>
+        <v>729262</v>
       </c>
       <c r="R149" t="n">
-        <v>6367618</v>
+        <v>6367640</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16147,7 +16148,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16166,48 +16166,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B150" t="n">
-        <v>92823</v>
+        <v>86981</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R150" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16248,7 +16245,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16267,45 +16263,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128698475</v>
+        <v>128693335</v>
       </c>
       <c r="B151" t="n">
-        <v>86945</v>
+        <v>92830</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R151" t="n">
-        <v>6367635</v>
+        <v>6367846</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16346,28 +16345,29 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B152" t="n">
-        <v>86980</v>
+        <v>86946</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16375,34 +16375,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R152" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16449,12 +16449,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16464,7 +16464,7 @@
         <v>128698476</v>
       </c>
       <c r="B153" t="n">
-        <v>86945</v>
+        <v>86946</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>128700660</v>
       </c>
       <c r="B154" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>128698488</v>
       </c>
       <c r="B155" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16762,45 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128693295</v>
+        <v>128698484</v>
       </c>
       <c r="B156" t="n">
-        <v>88693</v>
+        <v>86981</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4379</v>
+        <v>449</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729221</v>
+        <v>729261</v>
       </c>
       <c r="R156" t="n">
-        <v>6367854</v>
+        <v>6367615</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16847,12 +16847,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -16862,7 +16862,7 @@
         <v>128693336</v>
       </c>
       <c r="B157" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16960,45 +16960,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128698484</v>
+        <v>128693295</v>
       </c>
       <c r="B158" t="n">
-        <v>86980</v>
+        <v>88694</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>449</v>
+        <v>4379</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729261</v>
+        <v>729221</v>
       </c>
       <c r="R158" t="n">
-        <v>6367615</v>
+        <v>6367854</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17045,12 +17045,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17060,7 +17060,7 @@
         <v>128700501</v>
       </c>
       <c r="B159" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17164,10 +17164,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B160" t="n">
-        <v>91918</v>
+        <v>98654</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17175,34 +17175,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R160" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,9 +17232,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17249,12 +17259,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17264,7 +17274,7 @@
         <v>128693326</v>
       </c>
       <c r="B161" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17358,10 +17368,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128700626</v>
+        <v>128693324</v>
       </c>
       <c r="B162" t="n">
-        <v>98647</v>
+        <v>91923</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17369,34 +17379,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219862</v>
+        <v>5420</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729278</v>
+        <v>729284</v>
       </c>
       <c r="R162" t="n">
-        <v>6367669</v>
+        <v>6367580</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17426,19 +17436,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
         <v>128700430</v>
       </c>
       <c r="B163" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B164" t="n">
-        <v>86784</v>
+        <v>86981</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R164" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B165" t="n">
-        <v>86980</v>
+        <v>86784</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R165" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>128693330</v>
       </c>
       <c r="B166" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>128693294</v>
       </c>
       <c r="B167" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B168" t="n">
-        <v>92823</v>
+        <v>90938</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17972,21 +17972,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R168" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18058,32 +18058,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698465</v>
+        <v>128698485</v>
       </c>
       <c r="B169" t="n">
-        <v>90933</v>
+        <v>86981</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2009</v>
+        <v>449</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729275</v>
+        <v>729283</v>
       </c>
       <c r="R169" t="n">
-        <v>6367651</v>
+        <v>6367586</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18131,12 +18131,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18155,32 +18161,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B170" t="n">
-        <v>86980</v>
+        <v>92830</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18190,10 +18196,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R170" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18228,18 +18234,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B128" t="n">
-        <v>91039</v>
+        <v>92439</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B129" t="n">
-        <v>92439</v>
+        <v>91039</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B131" t="n">
-        <v>90937</v>
+        <v>86784</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R131" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B132" t="n">
-        <v>86784</v>
+        <v>90937</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R132" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B134" t="n">
-        <v>92830</v>
+        <v>92806</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R134" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B135" t="n">
-        <v>92806</v>
+        <v>92830</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R135" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,12 +14782,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14988,7 +14988,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128698472</v>
+        <v>128700405</v>
       </c>
       <c r="B138" t="n">
         <v>86959</v>
@@ -15019,14 +15019,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729284</v>
+        <v>729300</v>
       </c>
       <c r="R138" t="n">
-        <v>6367626</v>
+        <v>6367577</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,30 +15056,39 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -15183,7 +15192,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128700405</v>
+        <v>128698472</v>
       </c>
       <c r="B140" t="n">
         <v>86959</v>
@@ -15214,14 +15223,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729300</v>
+        <v>729284</v>
       </c>
       <c r="R140" t="n">
-        <v>6367577</v>
+        <v>6367626</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,39 +15260,30 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15680,32 +15680,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698471</v>
+        <v>128698494</v>
       </c>
       <c r="B145" t="n">
-        <v>86959</v>
+        <v>86946</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6003295</v>
+        <v>3599</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15715,10 +15715,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729291</v>
+        <v>729262</v>
       </c>
       <c r="R145" t="n">
-        <v>6367618</v>
+        <v>6367640</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15759,7 +15759,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15778,45 +15777,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128693307</v>
+        <v>128698471</v>
       </c>
       <c r="B146" t="n">
-        <v>91039</v>
+        <v>86959</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729261</v>
+        <v>729291</v>
       </c>
       <c r="R146" t="n">
-        <v>6367585</v>
+        <v>6367618</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15857,18 +15856,19 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -15972,10 +15972,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693293</v>
+        <v>128693307</v>
       </c>
       <c r="B148" t="n">
-        <v>87004</v>
+        <v>91039</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15983,21 +15983,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16007,10 +16007,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729196</v>
+        <v>729261</v>
       </c>
       <c r="R148" t="n">
-        <v>6367804</v>
+        <v>6367585</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16069,10 +16069,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128698494</v>
+        <v>128693293</v>
       </c>
       <c r="B149" t="n">
-        <v>86946</v>
+        <v>87004</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16080,34 +16080,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729262</v>
+        <v>729196</v>
       </c>
       <c r="R149" t="n">
-        <v>6367640</v>
+        <v>6367804</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16154,57 +16154,60 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693327</v>
+        <v>128693335</v>
       </c>
       <c r="B150" t="n">
-        <v>86981</v>
+        <v>92830</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729261</v>
+        <v>729198</v>
       </c>
       <c r="R150" t="n">
-        <v>6367585</v>
+        <v>6367846</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16245,6 +16248,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16263,48 +16267,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B151" t="n">
-        <v>92830</v>
+        <v>86981</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R151" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16345,7 +16346,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16762,45 +16762,48 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128698484</v>
+        <v>128693336</v>
       </c>
       <c r="B156" t="n">
-        <v>86981</v>
+        <v>92830</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729261</v>
+        <v>729237</v>
       </c>
       <c r="R156" t="n">
-        <v>6367615</v>
+        <v>6367593</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16841,28 +16844,29 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128693336</v>
+        <v>128693295</v>
       </c>
       <c r="B157" t="n">
-        <v>92830</v>
+        <v>88694</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16870,37 +16874,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729237</v>
+        <v>729221</v>
       </c>
       <c r="R157" t="n">
-        <v>6367593</v>
+        <v>6367854</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16941,7 +16942,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -16960,45 +16960,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128693295</v>
+        <v>128698484</v>
       </c>
       <c r="B158" t="n">
-        <v>88694</v>
+        <v>86981</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4379</v>
+        <v>449</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729221</v>
+        <v>729261</v>
       </c>
       <c r="R158" t="n">
-        <v>6367854</v>
+        <v>6367615</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17045,12 +17045,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17164,45 +17164,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128700626</v>
+        <v>128693326</v>
       </c>
       <c r="B160" t="n">
-        <v>98654</v>
+        <v>86981</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729278</v>
+        <v>729164</v>
       </c>
       <c r="R160" t="n">
-        <v>6367669</v>
+        <v>6367575</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,19 +17232,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17259,44 +17249,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693326</v>
+        <v>128693324</v>
       </c>
       <c r="B161" t="n">
-        <v>86981</v>
+        <v>91923</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>449</v>
+        <v>5420</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17306,10 +17296,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729164</v>
+        <v>729284</v>
       </c>
       <c r="R161" t="n">
-        <v>6367575</v>
+        <v>6367580</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17368,10 +17358,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B162" t="n">
-        <v>91923</v>
+        <v>98654</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17379,34 +17369,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R162" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17436,9 +17426,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B164" t="n">
-        <v>86981</v>
+        <v>86784</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R164" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B165" t="n">
-        <v>86784</v>
+        <v>86981</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R165" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698465</v>
+        <v>128698490</v>
       </c>
       <c r="B168" t="n">
-        <v>90938</v>
+        <v>92830</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17972,21 +17972,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2009</v>
+        <v>5964</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729275</v>
+        <v>729277</v>
       </c>
       <c r="R168" t="n">
-        <v>6367651</v>
+        <v>6367576</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18161,10 +18161,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B170" t="n">
-        <v>92830</v>
+        <v>90938</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18172,21 +18172,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18196,10 +18196,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R170" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B131" t="n">
-        <v>86784</v>
+        <v>90937</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R131" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B132" t="n">
-        <v>90937</v>
+        <v>86784</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R132" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B134" t="n">
-        <v>92806</v>
+        <v>92830</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R134" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B135" t="n">
-        <v>92830</v>
+        <v>92806</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R135" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,12 +14782,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -15680,32 +15680,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698494</v>
+        <v>128698471</v>
       </c>
       <c r="B145" t="n">
-        <v>86946</v>
+        <v>86959</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3599</v>
+        <v>6003295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15715,10 +15715,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729262</v>
+        <v>729291</v>
       </c>
       <c r="R145" t="n">
-        <v>6367640</v>
+        <v>6367618</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15759,6 +15759,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15777,32 +15778,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128698471</v>
+        <v>128698494</v>
       </c>
       <c r="B146" t="n">
-        <v>86959</v>
+        <v>86946</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6003295</v>
+        <v>3599</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15812,10 +15813,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729291</v>
+        <v>729262</v>
       </c>
       <c r="R146" t="n">
-        <v>6367618</v>
+        <v>6367640</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15856,7 +15857,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15875,32 +15875,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693333</v>
+        <v>128693307</v>
       </c>
       <c r="B147" t="n">
-        <v>90926</v>
+        <v>91039</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4188</v>
+        <v>5747</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15910,10 +15910,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729244</v>
+        <v>729261</v>
       </c>
       <c r="R147" t="n">
-        <v>6367576</v>
+        <v>6367585</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15972,32 +15972,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693307</v>
+        <v>128693333</v>
       </c>
       <c r="B148" t="n">
-        <v>91039</v>
+        <v>90926</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5747</v>
+        <v>4188</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16007,10 +16007,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729261</v>
+        <v>729244</v>
       </c>
       <c r="R148" t="n">
-        <v>6367585</v>
+        <v>6367576</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16166,48 +16166,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693335</v>
+        <v>128698475</v>
       </c>
       <c r="B150" t="n">
-        <v>92830</v>
+        <v>86946</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729198</v>
+        <v>729259</v>
       </c>
       <c r="R150" t="n">
-        <v>6367846</v>
+        <v>6367635</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16248,64 +16245,66 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128693327</v>
+        <v>128693335</v>
       </c>
       <c r="B151" t="n">
-        <v>86981</v>
+        <v>92830</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729261</v>
+        <v>729198</v>
       </c>
       <c r="R151" t="n">
-        <v>6367585</v>
+        <v>6367846</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16346,6 +16345,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16364,10 +16364,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128698475</v>
+        <v>128693327</v>
       </c>
       <c r="B152" t="n">
-        <v>86946</v>
+        <v>86981</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16375,34 +16375,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3599</v>
+        <v>449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729259</v>
+        <v>729261</v>
       </c>
       <c r="R152" t="n">
-        <v>6367635</v>
+        <v>6367585</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16449,12 +16449,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16762,7 +16762,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128693336</v>
+        <v>128700501</v>
       </c>
       <c r="B156" t="n">
         <v>92830</v>
@@ -16791,19 +16791,16 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729237</v>
+        <v>729268</v>
       </c>
       <c r="R156" t="n">
-        <v>6367593</v>
+        <v>6367544</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16833,30 +16830,39 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -17057,7 +17063,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128700501</v>
+        <v>128693336</v>
       </c>
       <c r="B159" t="n">
         <v>92830</v>
@@ -17086,16 +17092,19 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729268</v>
+        <v>729237</v>
       </c>
       <c r="R159" t="n">
-        <v>6367544</v>
+        <v>6367593</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17125,84 +17134,75 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128693326</v>
+        <v>128700626</v>
       </c>
       <c r="B160" t="n">
-        <v>86981</v>
+        <v>98654</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729164</v>
+        <v>729278</v>
       </c>
       <c r="R160" t="n">
-        <v>6367575</v>
+        <v>6367669</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,9 +17232,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17249,44 +17259,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693324</v>
+        <v>128693326</v>
       </c>
       <c r="B161" t="n">
-        <v>91923</v>
+        <v>86981</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5420</v>
+        <v>449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17296,10 +17306,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729284</v>
+        <v>729164</v>
       </c>
       <c r="R161" t="n">
-        <v>6367580</v>
+        <v>6367575</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17358,10 +17368,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128700626</v>
+        <v>128693324</v>
       </c>
       <c r="B162" t="n">
-        <v>98654</v>
+        <v>91923</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17369,34 +17379,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219862</v>
+        <v>5420</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729278</v>
+        <v>729284</v>
       </c>
       <c r="R162" t="n">
-        <v>6367669</v>
+        <v>6367580</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17426,19 +17436,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B164" t="n">
-        <v>86784</v>
+        <v>86981</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R164" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B165" t="n">
-        <v>86981</v>
+        <v>86784</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R165" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B168" t="n">
-        <v>92830</v>
+        <v>90938</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17972,21 +17972,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R168" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18058,32 +18058,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B169" t="n">
-        <v>86981</v>
+        <v>92830</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R169" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18131,18 +18131,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18161,32 +18155,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698465</v>
+        <v>128698485</v>
       </c>
       <c r="B170" t="n">
-        <v>90938</v>
+        <v>86981</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2009</v>
+        <v>449</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18196,10 +18190,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729275</v>
+        <v>729283</v>
       </c>
       <c r="R170" t="n">
-        <v>6367651</v>
+        <v>6367586</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18234,12 +18228,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13424,7 +13424,7 @@
         <v>128520851</v>
       </c>
       <c r="B122" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>128512741</v>
       </c>
       <c r="B125" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90926</v>
+        <v>90930</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>128512738</v>
       </c>
       <c r="B128" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>128512742</v>
       </c>
       <c r="B129" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90934</v>
+        <v>90938</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B131" t="n">
-        <v>90937</v>
+        <v>86788</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R131" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B132" t="n">
-        <v>86784</v>
+        <v>90941</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R132" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>128698487</v>
       </c>
       <c r="B134" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128693300</v>
       </c>
       <c r="B135" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>128698489</v>
       </c>
       <c r="B136" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>128698483</v>
       </c>
       <c r="B137" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>128700405</v>
       </c>
       <c r="B138" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>128698459</v>
       </c>
       <c r="B139" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>128698472</v>
       </c>
       <c r="B140" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15290,32 +15290,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128693342</v>
+        <v>128693303</v>
       </c>
       <c r="B141" t="n">
-        <v>86784</v>
+        <v>86963</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15325,10 +15325,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>729241</v>
+        <v>729311</v>
       </c>
       <c r="R141" t="n">
-        <v>6367592</v>
+        <v>6367596</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15369,6 +15369,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15387,32 +15388,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128693303</v>
+        <v>128693342</v>
       </c>
       <c r="B142" t="n">
-        <v>86959</v>
+        <v>86788</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15422,10 +15423,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>729311</v>
+        <v>729241</v>
       </c>
       <c r="R142" t="n">
-        <v>6367596</v>
+        <v>6367592</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15466,7 +15467,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15488,7 +15488,7 @@
         <v>128693299</v>
       </c>
       <c r="B143" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>128698473</v>
       </c>
       <c r="B144" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15680,32 +15680,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698471</v>
+        <v>128698494</v>
       </c>
       <c r="B145" t="n">
-        <v>86959</v>
+        <v>86950</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6003295</v>
+        <v>3599</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15715,10 +15715,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729291</v>
+        <v>729262</v>
       </c>
       <c r="R145" t="n">
-        <v>6367618</v>
+        <v>6367640</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15759,7 +15759,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15778,10 +15777,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128698494</v>
+        <v>128693307</v>
       </c>
       <c r="B146" t="n">
-        <v>86946</v>
+        <v>91043</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15789,34 +15788,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3599</v>
+        <v>5747</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729262</v>
+        <v>729261</v>
       </c>
       <c r="R146" t="n">
-        <v>6367640</v>
+        <v>6367585</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15863,44 +15862,44 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693307</v>
+        <v>128693333</v>
       </c>
       <c r="B147" t="n">
-        <v>91039</v>
+        <v>90930</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5747</v>
+        <v>4188</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15910,10 +15909,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729261</v>
+        <v>729244</v>
       </c>
       <c r="R147" t="n">
-        <v>6367585</v>
+        <v>6367576</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15972,32 +15971,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693333</v>
+        <v>128693293</v>
       </c>
       <c r="B148" t="n">
-        <v>90926</v>
+        <v>87008</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4188</v>
+        <v>3767</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16007,10 +16006,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729244</v>
+        <v>729196</v>
       </c>
       <c r="R148" t="n">
-        <v>6367576</v>
+        <v>6367804</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16069,45 +16068,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128693293</v>
+        <v>128698471</v>
       </c>
       <c r="B149" t="n">
-        <v>87004</v>
+        <v>86963</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729196</v>
+        <v>729291</v>
       </c>
       <c r="R149" t="n">
-        <v>6367804</v>
+        <v>6367618</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16148,18 +16147,19 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -16169,7 +16169,7 @@
         <v>128698475</v>
       </c>
       <c r="B150" t="n">
-        <v>86946</v>
+        <v>86950</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>128693335</v>
       </c>
       <c r="B151" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>128693327</v>
       </c>
       <c r="B152" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>128698476</v>
       </c>
       <c r="B153" t="n">
-        <v>86946</v>
+        <v>86950</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>128700660</v>
       </c>
       <c r="B154" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>128698488</v>
       </c>
       <c r="B155" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16762,10 +16762,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128700501</v>
+        <v>128693336</v>
       </c>
       <c r="B156" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16791,16 +16791,19 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729268</v>
+        <v>729237</v>
       </c>
       <c r="R156" t="n">
-        <v>6367544</v>
+        <v>6367593</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16830,39 +16833,30 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -16872,7 +16866,7 @@
         <v>128693295</v>
       </c>
       <c r="B157" t="n">
-        <v>88694</v>
+        <v>88698</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16969,7 +16963,7 @@
         <v>128698484</v>
       </c>
       <c r="B158" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17063,10 +17057,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128693336</v>
+        <v>128700501</v>
       </c>
       <c r="B159" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17092,19 +17086,16 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729237</v>
+        <v>729268</v>
       </c>
       <c r="R159" t="n">
-        <v>6367593</v>
+        <v>6367544</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17134,75 +17125,84 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128700626</v>
+        <v>128693326</v>
       </c>
       <c r="B160" t="n">
-        <v>98654</v>
+        <v>86985</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729278</v>
+        <v>729164</v>
       </c>
       <c r="R160" t="n">
-        <v>6367669</v>
+        <v>6367575</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,19 +17232,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17259,44 +17249,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693326</v>
+        <v>128693324</v>
       </c>
       <c r="B161" t="n">
-        <v>86981</v>
+        <v>91927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>449</v>
+        <v>5420</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17306,10 +17296,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729164</v>
+        <v>729284</v>
       </c>
       <c r="R161" t="n">
-        <v>6367575</v>
+        <v>6367580</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17368,10 +17358,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B162" t="n">
-        <v>91923</v>
+        <v>98658</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17379,34 +17369,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R162" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17436,9 +17426,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
         <v>128700430</v>
       </c>
       <c r="B163" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B164" t="n">
-        <v>86981</v>
+        <v>86788</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R164" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B165" t="n">
-        <v>86784</v>
+        <v>86985</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R165" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>128693330</v>
       </c>
       <c r="B166" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>128693294</v>
       </c>
       <c r="B167" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>128698465</v>
       </c>
       <c r="B168" t="n">
-        <v>90938</v>
+        <v>90942</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>128698490</v>
       </c>
       <c r="B169" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>128698485</v>
       </c>
       <c r="B170" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>128717177</v>
       </c>
       <c r="B171" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>128693297</v>
       </c>
       <c r="B172" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13210,7 +13210,7 @@
         <v>128472799</v>
       </c>
       <c r="B120" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>128473008</v>
       </c>
       <c r="B121" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B131" t="n">
-        <v>86788</v>
+        <v>90941</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R131" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B132" t="n">
-        <v>90941</v>
+        <v>86788</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R132" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B134" t="n">
-        <v>92834</v>
+        <v>92810</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R134" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B135" t="n">
-        <v>92810</v>
+        <v>92834</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R135" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,12 +14782,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -15485,45 +15485,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128693299</v>
+        <v>128698473</v>
       </c>
       <c r="B143" t="n">
-        <v>92810</v>
+        <v>86963</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>729191</v>
+        <v>729278</v>
       </c>
       <c r="R143" t="n">
-        <v>6367801</v>
+        <v>6367631</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15564,63 +15564,64 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128698473</v>
+        <v>128693299</v>
       </c>
       <c r="B144" t="n">
-        <v>86963</v>
+        <v>92810</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>729278</v>
+        <v>729191</v>
       </c>
       <c r="R144" t="n">
-        <v>6367631</v>
+        <v>6367801</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15661,29 +15662,28 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698494</v>
+        <v>128693307</v>
       </c>
       <c r="B145" t="n">
-        <v>86950</v>
+        <v>91043</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15691,34 +15691,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3599</v>
+        <v>5747</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729262</v>
+        <v>729261</v>
       </c>
       <c r="R145" t="n">
-        <v>6367640</v>
+        <v>6367585</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15765,44 +15765,44 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128693307</v>
+        <v>128693333</v>
       </c>
       <c r="B146" t="n">
-        <v>91043</v>
+        <v>90930</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5747</v>
+        <v>4188</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729261</v>
+        <v>729244</v>
       </c>
       <c r="R146" t="n">
-        <v>6367585</v>
+        <v>6367576</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15874,45 +15874,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693333</v>
+        <v>128698494</v>
       </c>
       <c r="B147" t="n">
-        <v>90930</v>
+        <v>86950</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4188</v>
+        <v>3599</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729244</v>
+        <v>729262</v>
       </c>
       <c r="R147" t="n">
-        <v>6367576</v>
+        <v>6367640</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15959,12 +15959,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -16166,45 +16166,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128698475</v>
+        <v>128693335</v>
       </c>
       <c r="B150" t="n">
-        <v>86950</v>
+        <v>92834</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R150" t="n">
-        <v>6367635</v>
+        <v>6367846</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16245,66 +16248,64 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B151" t="n">
-        <v>92834</v>
+        <v>86985</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R151" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16345,7 +16346,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16364,10 +16364,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B152" t="n">
-        <v>86985</v>
+        <v>86950</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16375,34 +16375,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R152" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16449,12 +16449,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16762,48 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128693336</v>
+        <v>128698484</v>
       </c>
       <c r="B156" t="n">
-        <v>92834</v>
+        <v>86985</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729237</v>
+        <v>729261</v>
       </c>
       <c r="R156" t="n">
-        <v>6367593</v>
+        <v>6367615</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16844,29 +16841,28 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128693295</v>
+        <v>128700501</v>
       </c>
       <c r="B157" t="n">
-        <v>88698</v>
+        <v>92834</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16874,34 +16870,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4379</v>
+        <v>5964</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729221</v>
+        <v>729268</v>
       </c>
       <c r="R157" t="n">
-        <v>6367854</v>
+        <v>6367544</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16931,9 +16927,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16948,57 +16954,57 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128698484</v>
+        <v>128693295</v>
       </c>
       <c r="B158" t="n">
-        <v>86985</v>
+        <v>88698</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>449</v>
+        <v>4379</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729261</v>
+        <v>729221</v>
       </c>
       <c r="R158" t="n">
-        <v>6367615</v>
+        <v>6367854</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17045,19 +17051,19 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128700501</v>
+        <v>128693336</v>
       </c>
       <c r="B159" t="n">
         <v>92834</v>
@@ -17086,16 +17092,19 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729268</v>
+        <v>729237</v>
       </c>
       <c r="R159" t="n">
-        <v>6367544</v>
+        <v>6367593</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17125,84 +17134,75 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128693326</v>
+        <v>128700626</v>
       </c>
       <c r="B160" t="n">
-        <v>86985</v>
+        <v>98658</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729164</v>
+        <v>729278</v>
       </c>
       <c r="R160" t="n">
-        <v>6367575</v>
+        <v>6367669</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,9 +17232,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17249,44 +17259,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693324</v>
+        <v>128693326</v>
       </c>
       <c r="B161" t="n">
-        <v>91927</v>
+        <v>86985</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5420</v>
+        <v>449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17296,10 +17306,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729284</v>
+        <v>729164</v>
       </c>
       <c r="R161" t="n">
-        <v>6367580</v>
+        <v>6367575</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17358,10 +17368,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128700626</v>
+        <v>128693324</v>
       </c>
       <c r="B162" t="n">
-        <v>98658</v>
+        <v>91927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17369,34 +17379,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219862</v>
+        <v>5420</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729278</v>
+        <v>729284</v>
       </c>
       <c r="R162" t="n">
-        <v>6367669</v>
+        <v>6367580</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17426,19 +17436,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B164" t="n">
-        <v>86788</v>
+        <v>86985</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R164" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B165" t="n">
-        <v>86985</v>
+        <v>86788</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R165" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698465</v>
+        <v>128698490</v>
       </c>
       <c r="B168" t="n">
-        <v>90942</v>
+        <v>92834</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17972,21 +17972,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2009</v>
+        <v>5964</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729275</v>
+        <v>729277</v>
       </c>
       <c r="R168" t="n">
-        <v>6367651</v>
+        <v>6367576</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18058,10 +18058,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B169" t="n">
-        <v>92834</v>
+        <v>90942</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18069,21 +18069,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R169" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B131" t="n">
-        <v>90941</v>
+        <v>86788</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R131" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B132" t="n">
-        <v>86788</v>
+        <v>90941</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R132" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14988,45 +14988,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128700405</v>
+        <v>128698459</v>
       </c>
       <c r="B138" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729300</v>
+        <v>729257</v>
       </c>
       <c r="R138" t="n">
-        <v>6367577</v>
+        <v>6367641</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,19 +15056,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15083,44 +15073,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698459</v>
+        <v>128698472</v>
       </c>
       <c r="B139" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15130,10 +15120,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729257</v>
+        <v>729284</v>
       </c>
       <c r="R139" t="n">
-        <v>6367641</v>
+        <v>6367626</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15174,6 +15164,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15192,7 +15183,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128698472</v>
+        <v>128700405</v>
       </c>
       <c r="B140" t="n">
         <v>86963</v>
@@ -15223,14 +15214,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729284</v>
+        <v>729300</v>
       </c>
       <c r="R140" t="n">
-        <v>6367626</v>
+        <v>6367577</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15260,62 +15251,71 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128693303</v>
+        <v>128693342</v>
       </c>
       <c r="B141" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15325,10 +15325,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>729311</v>
+        <v>729241</v>
       </c>
       <c r="R141" t="n">
-        <v>6367596</v>
+        <v>6367592</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15369,7 +15369,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15388,32 +15387,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128693342</v>
+        <v>128693303</v>
       </c>
       <c r="B142" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15423,10 +15422,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>729241</v>
+        <v>729311</v>
       </c>
       <c r="R142" t="n">
-        <v>6367592</v>
+        <v>6367596</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15467,6 +15466,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15874,10 +15874,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128698494</v>
+        <v>128693293</v>
       </c>
       <c r="B147" t="n">
-        <v>86950</v>
+        <v>87008</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15885,34 +15885,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729262</v>
+        <v>729196</v>
       </c>
       <c r="R147" t="n">
-        <v>6367640</v>
+        <v>6367804</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15959,22 +15959,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693293</v>
+        <v>128698494</v>
       </c>
       <c r="B148" t="n">
-        <v>87008</v>
+        <v>86950</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15982,34 +15982,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729196</v>
+        <v>729262</v>
       </c>
       <c r="R148" t="n">
-        <v>6367804</v>
+        <v>6367640</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16056,12 +16056,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16267,10 +16267,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B151" t="n">
-        <v>86985</v>
+        <v>86950</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16278,34 +16278,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R151" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16352,22 +16352,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128698475</v>
+        <v>128693327</v>
       </c>
       <c r="B152" t="n">
-        <v>86950</v>
+        <v>86985</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16375,34 +16375,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3599</v>
+        <v>449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729259</v>
+        <v>729261</v>
       </c>
       <c r="R152" t="n">
-        <v>6367635</v>
+        <v>6367585</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16449,12 +16449,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16762,45 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128698484</v>
+        <v>128693295</v>
       </c>
       <c r="B156" t="n">
-        <v>86985</v>
+        <v>88698</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>449</v>
+        <v>4379</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729261</v>
+        <v>729221</v>
       </c>
       <c r="R156" t="n">
-        <v>6367615</v>
+        <v>6367854</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16847,57 +16847,57 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128700501</v>
+        <v>128698484</v>
       </c>
       <c r="B157" t="n">
-        <v>92834</v>
+        <v>86985</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729268</v>
+        <v>729261</v>
       </c>
       <c r="R157" t="n">
-        <v>6367544</v>
+        <v>6367615</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16927,19 +16927,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16954,22 +16944,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128693295</v>
+        <v>128693336</v>
       </c>
       <c r="B158" t="n">
-        <v>88698</v>
+        <v>92834</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16977,34 +16967,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4379</v>
+        <v>5964</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729221</v>
+        <v>729237</v>
       </c>
       <c r="R158" t="n">
-        <v>6367854</v>
+        <v>6367593</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17045,6 +17038,7 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -17063,7 +17057,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128693336</v>
+        <v>128700501</v>
       </c>
       <c r="B159" t="n">
         <v>92834</v>
@@ -17092,19 +17086,16 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729237</v>
+        <v>729268</v>
       </c>
       <c r="R159" t="n">
-        <v>6367593</v>
+        <v>6367544</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17134,40 +17125,49 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128700626</v>
+        <v>128693324</v>
       </c>
       <c r="B160" t="n">
-        <v>98658</v>
+        <v>91927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17175,34 +17175,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219862</v>
+        <v>5420</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729278</v>
+        <v>729284</v>
       </c>
       <c r="R160" t="n">
-        <v>6367669</v>
+        <v>6367580</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,19 +17232,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17259,12 +17249,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17368,10 +17358,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B162" t="n">
-        <v>91927</v>
+        <v>98658</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17379,34 +17369,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R162" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17436,9 +17426,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B164" t="n">
-        <v>86985</v>
+        <v>86788</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R164" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B165" t="n">
-        <v>86788</v>
+        <v>86985</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R165" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13210,7 +13210,7 @@
         <v>128472799</v>
       </c>
       <c r="B120" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>128473008</v>
       </c>
       <c r="B121" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>128520851</v>
       </c>
       <c r="B122" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>128512741</v>
       </c>
       <c r="B125" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90930</v>
+        <v>90935</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>128512738</v>
       </c>
       <c r="B128" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>128512742</v>
       </c>
       <c r="B129" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90938</v>
+        <v>90943</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>128693341</v>
       </c>
       <c r="B131" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>128693331</v>
       </c>
       <c r="B132" t="n">
-        <v>90941</v>
+        <v>90946</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B134" t="n">
-        <v>92810</v>
+        <v>92839</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R134" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B135" t="n">
-        <v>92834</v>
+        <v>92815</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R135" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,12 +14782,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14797,7 +14797,7 @@
         <v>128698489</v>
       </c>
       <c r="B136" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>128698483</v>
       </c>
       <c r="B137" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14988,32 +14988,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128698459</v>
+        <v>128698472</v>
       </c>
       <c r="B138" t="n">
-        <v>87008</v>
+        <v>86968</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15023,10 +15023,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729257</v>
+        <v>729284</v>
       </c>
       <c r="R138" t="n">
-        <v>6367641</v>
+        <v>6367626</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15067,6 +15067,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15085,10 +15086,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698472</v>
+        <v>128700405</v>
       </c>
       <c r="B139" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15116,14 +15117,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729284</v>
+        <v>729300</v>
       </c>
       <c r="R139" t="n">
-        <v>6367626</v>
+        <v>6367577</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15153,75 +15154,84 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128700405</v>
+        <v>128698459</v>
       </c>
       <c r="B140" t="n">
-        <v>86963</v>
+        <v>87013</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729300</v>
+        <v>729257</v>
       </c>
       <c r="R140" t="n">
-        <v>6367577</v>
+        <v>6367641</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,19 +15261,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15278,12 +15278,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15293,7 +15293,7 @@
         <v>128693342</v>
       </c>
       <c r="B141" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>128693303</v>
       </c>
       <c r="B142" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15485,45 +15485,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128698473</v>
+        <v>128693299</v>
       </c>
       <c r="B143" t="n">
-        <v>86963</v>
+        <v>92815</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>729278</v>
+        <v>729191</v>
       </c>
       <c r="R143" t="n">
-        <v>6367631</v>
+        <v>6367801</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15564,64 +15564,63 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128693299</v>
+        <v>128698473</v>
       </c>
       <c r="B144" t="n">
-        <v>92810</v>
+        <v>86968</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>729191</v>
+        <v>729278</v>
       </c>
       <c r="R144" t="n">
-        <v>6367801</v>
+        <v>6367631</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15662,18 +15661,19 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
         <v>128693307</v>
       </c>
       <c r="B145" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>128693333</v>
       </c>
       <c r="B146" t="n">
-        <v>90930</v>
+        <v>90935</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15874,10 +15874,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693293</v>
+        <v>128698494</v>
       </c>
       <c r="B147" t="n">
-        <v>87008</v>
+        <v>86955</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15885,34 +15885,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729196</v>
+        <v>729262</v>
       </c>
       <c r="R147" t="n">
-        <v>6367804</v>
+        <v>6367640</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15959,22 +15959,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128698494</v>
+        <v>128693293</v>
       </c>
       <c r="B148" t="n">
-        <v>86950</v>
+        <v>87013</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15982,34 +15982,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729262</v>
+        <v>729196</v>
       </c>
       <c r="R148" t="n">
-        <v>6367640</v>
+        <v>6367804</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16056,12 +16056,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16071,7 +16071,7 @@
         <v>128698471</v>
       </c>
       <c r="B149" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16166,48 +16166,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B150" t="n">
-        <v>92834</v>
+        <v>86990</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R150" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16248,7 +16245,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16267,45 +16263,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128698475</v>
+        <v>128693335</v>
       </c>
       <c r="B151" t="n">
-        <v>86950</v>
+        <v>92839</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R151" t="n">
-        <v>6367635</v>
+        <v>6367846</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16346,28 +16345,29 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B152" t="n">
-        <v>86985</v>
+        <v>86955</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16375,34 +16375,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R152" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16449,12 +16449,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16464,7 +16464,7 @@
         <v>128698476</v>
       </c>
       <c r="B153" t="n">
-        <v>86950</v>
+        <v>86955</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>128700660</v>
       </c>
       <c r="B154" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>128698488</v>
       </c>
       <c r="B155" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16762,45 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128693295</v>
+        <v>128698484</v>
       </c>
       <c r="B156" t="n">
-        <v>88698</v>
+        <v>86990</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4379</v>
+        <v>449</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729221</v>
+        <v>729261</v>
       </c>
       <c r="R156" t="n">
-        <v>6367854</v>
+        <v>6367615</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16847,57 +16847,57 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128698484</v>
+        <v>128693295</v>
       </c>
       <c r="B157" t="n">
-        <v>86985</v>
+        <v>88703</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>449</v>
+        <v>4379</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729261</v>
+        <v>729221</v>
       </c>
       <c r="R157" t="n">
-        <v>6367615</v>
+        <v>6367854</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16944,12 +16944,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -16959,7 +16959,7 @@
         <v>128693336</v>
       </c>
       <c r="B158" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>128700501</v>
       </c>
       <c r="B159" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17164,32 +17164,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128693324</v>
+        <v>128693326</v>
       </c>
       <c r="B160" t="n">
-        <v>91927</v>
+        <v>86990</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5420</v>
+        <v>449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17199,10 +17199,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729284</v>
+        <v>729164</v>
       </c>
       <c r="R160" t="n">
-        <v>6367580</v>
+        <v>6367575</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17261,32 +17261,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693326</v>
+        <v>128693324</v>
       </c>
       <c r="B161" t="n">
-        <v>86985</v>
+        <v>91932</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>449</v>
+        <v>5420</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17296,10 +17296,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729164</v>
+        <v>729284</v>
       </c>
       <c r="R161" t="n">
-        <v>6367575</v>
+        <v>6367580</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17361,7 +17361,7 @@
         <v>128700626</v>
       </c>
       <c r="B162" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>128700430</v>
       </c>
       <c r="B163" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B164" t="n">
-        <v>86788</v>
+        <v>86990</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R164" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B165" t="n">
-        <v>86985</v>
+        <v>86793</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R165" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>128693330</v>
       </c>
       <c r="B166" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>128693294</v>
       </c>
       <c r="B167" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>128698490</v>
       </c>
       <c r="B168" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18058,32 +18058,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698465</v>
+        <v>128698485</v>
       </c>
       <c r="B169" t="n">
-        <v>90942</v>
+        <v>86990</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2009</v>
+        <v>449</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729275</v>
+        <v>729283</v>
       </c>
       <c r="R169" t="n">
-        <v>6367651</v>
+        <v>6367586</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18131,12 +18131,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18155,32 +18161,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698485</v>
+        <v>128698465</v>
       </c>
       <c r="B170" t="n">
-        <v>86985</v>
+        <v>90947</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>449</v>
+        <v>2009</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18190,10 +18196,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729283</v>
+        <v>729275</v>
       </c>
       <c r="R170" t="n">
-        <v>6367586</v>
+        <v>6367651</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18228,18 +18234,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18261,7 +18261,7 @@
         <v>128717177</v>
       </c>
       <c r="B171" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>128693297</v>
       </c>
       <c r="B172" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -13424,7 +13424,7 @@
         <v>128520851</v>
       </c>
       <c r="B122" t="n">
-        <v>86795</v>
+        <v>86800</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>128512739</v>
       </c>
       <c r="B123" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>128512744</v>
       </c>
       <c r="B124" t="n">
-        <v>91050</v>
+        <v>91055</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>128512741</v>
       </c>
       <c r="B125" t="n">
-        <v>86970</v>
+        <v>86975</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>128512749</v>
       </c>
       <c r="B126" t="n">
-        <v>90937</v>
+        <v>90942</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>128512743</v>
       </c>
       <c r="B127" t="n">
-        <v>91050</v>
+        <v>91055</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B128" t="n">
-        <v>91050</v>
+        <v>92456</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B129" t="n">
-        <v>92451</v>
+        <v>91055</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14211,7 +14211,7 @@
         <v>128512747</v>
       </c>
       <c r="B130" t="n">
-        <v>90945</v>
+        <v>90950</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B134" t="n">
-        <v>92847</v>
+        <v>92823</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R134" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B135" t="n">
-        <v>92823</v>
+        <v>92847</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R135" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,12 +14782,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -15485,45 +15485,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128693299</v>
+        <v>128698473</v>
       </c>
       <c r="B143" t="n">
-        <v>92823</v>
+        <v>86975</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>729191</v>
+        <v>729278</v>
       </c>
       <c r="R143" t="n">
-        <v>6367801</v>
+        <v>6367631</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15564,63 +15564,64 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128698473</v>
+        <v>128693299</v>
       </c>
       <c r="B144" t="n">
-        <v>86975</v>
+        <v>92823</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>729278</v>
+        <v>729191</v>
       </c>
       <c r="R144" t="n">
-        <v>6367631</v>
+        <v>6367801</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15661,51 +15662,50 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698494</v>
+        <v>128698471</v>
       </c>
       <c r="B145" t="n">
-        <v>86962</v>
+        <v>86975</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3599</v>
+        <v>6003295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15715,10 +15715,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729262</v>
+        <v>729291</v>
       </c>
       <c r="R145" t="n">
-        <v>6367640</v>
+        <v>6367618</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15759,6 +15759,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15777,10 +15778,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128693307</v>
+        <v>128698494</v>
       </c>
       <c r="B146" t="n">
-        <v>91055</v>
+        <v>86962</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15788,34 +15789,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5747</v>
+        <v>3599</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729261</v>
+        <v>729262</v>
       </c>
       <c r="R146" t="n">
-        <v>6367585</v>
+        <v>6367640</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15862,12 +15863,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -15971,10 +15972,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693293</v>
+        <v>128693307</v>
       </c>
       <c r="B148" t="n">
-        <v>87020</v>
+        <v>91055</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15982,21 +15983,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16006,10 +16007,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729196</v>
+        <v>729261</v>
       </c>
       <c r="R148" t="n">
-        <v>6367804</v>
+        <v>6367585</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16068,45 +16069,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128698471</v>
+        <v>128693293</v>
       </c>
       <c r="B149" t="n">
-        <v>86975</v>
+        <v>87020</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729291</v>
+        <v>729196</v>
       </c>
       <c r="R149" t="n">
-        <v>6367618</v>
+        <v>6367804</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16147,29 +16148,28 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128698475</v>
+        <v>128693327</v>
       </c>
       <c r="B150" t="n">
-        <v>86962</v>
+        <v>86997</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16177,34 +16177,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3599</v>
+        <v>449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729259</v>
+        <v>729261</v>
       </c>
       <c r="R150" t="n">
-        <v>6367635</v>
+        <v>6367585</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16251,22 +16251,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B151" t="n">
-        <v>86997</v>
+        <v>86962</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16274,34 +16274,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R151" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16348,12 +16348,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16762,45 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128698484</v>
+        <v>128700501</v>
       </c>
       <c r="B156" t="n">
-        <v>86997</v>
+        <v>92847</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729261</v>
+        <v>729268</v>
       </c>
       <c r="R156" t="n">
-        <v>6367615</v>
+        <v>6367544</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16830,9 +16830,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16847,57 +16857,57 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128693295</v>
+        <v>128698484</v>
       </c>
       <c r="B157" t="n">
-        <v>88710</v>
+        <v>86997</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4379</v>
+        <v>449</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729221</v>
+        <v>729261</v>
       </c>
       <c r="R157" t="n">
-        <v>6367854</v>
+        <v>6367615</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16944,19 +16954,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128700501</v>
+        <v>128693336</v>
       </c>
       <c r="B158" t="n">
         <v>92847</v>
@@ -16985,16 +16995,19 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729268</v>
+        <v>729237</v>
       </c>
       <c r="R158" t="n">
-        <v>6367544</v>
+        <v>6367593</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17024,49 +17037,40 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128693336</v>
+        <v>128693295</v>
       </c>
       <c r="B159" t="n">
-        <v>92847</v>
+        <v>88710</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17074,37 +17078,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729237</v>
+        <v>729221</v>
       </c>
       <c r="R159" t="n">
-        <v>6367593</v>
+        <v>6367854</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17145,7 +17146,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -17164,45 +17164,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128700626</v>
+        <v>128693326</v>
       </c>
       <c r="B160" t="n">
-        <v>98673</v>
+        <v>86997</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729278</v>
+        <v>729164</v>
       </c>
       <c r="R160" t="n">
-        <v>6367669</v>
+        <v>6367575</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,19 +17232,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17259,22 +17249,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B161" t="n">
-        <v>91940</v>
+        <v>98673</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17282,34 +17272,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R161" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17339,9 +17329,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17356,44 +17356,44 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128693326</v>
+        <v>128693324</v>
       </c>
       <c r="B162" t="n">
-        <v>86997</v>
+        <v>91940</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>449</v>
+        <v>5420</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17403,10 +17403,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729164</v>
+        <v>729284</v>
       </c>
       <c r="R162" t="n">
-        <v>6367575</v>
+        <v>6367580</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14014,32 +14014,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128512738</v>
+        <v>128512742</v>
       </c>
       <c r="B128" t="n">
-        <v>92456</v>
+        <v>91055</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>729258</v>
       </c>
       <c r="R128" t="n">
-        <v>6367577</v>
+        <v>6367590</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14111,32 +14111,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128512742</v>
+        <v>128512738</v>
       </c>
       <c r="B129" t="n">
-        <v>91055</v>
+        <v>92456</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>729258</v>
       </c>
       <c r="R129" t="n">
-        <v>6367590</v>
+        <v>6367577</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B131" t="n">
-        <v>86800</v>
+        <v>90956</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R131" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B132" t="n">
-        <v>90953</v>
+        <v>86803</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R132" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B134" t="n">
-        <v>92823</v>
+        <v>92852</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R134" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B135" t="n">
-        <v>92847</v>
+        <v>92828</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R135" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,22 +14782,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128698489</v>
+        <v>128698483</v>
       </c>
       <c r="B136" t="n">
-        <v>92847</v>
+        <v>105719</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14805,21 +14805,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14829,10 +14829,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R136" t="n">
-        <v>6367618</v>
+        <v>6367646</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14891,10 +14891,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128698483</v>
+        <v>128698489</v>
       </c>
       <c r="B137" t="n">
-        <v>105714</v>
+        <v>92852</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14902,21 +14902,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R137" t="n">
-        <v>6367646</v>
+        <v>6367618</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14988,45 +14988,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128700405</v>
+        <v>128698459</v>
       </c>
       <c r="B138" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729300</v>
+        <v>729257</v>
       </c>
       <c r="R138" t="n">
-        <v>6367577</v>
+        <v>6367641</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,19 +15056,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15083,44 +15073,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698459</v>
+        <v>128698472</v>
       </c>
       <c r="B139" t="n">
-        <v>87020</v>
+        <v>86978</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15130,10 +15120,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729257</v>
+        <v>729284</v>
       </c>
       <c r="R139" t="n">
-        <v>6367641</v>
+        <v>6367626</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15174,6 +15164,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15192,10 +15183,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128698472</v>
+        <v>128700405</v>
       </c>
       <c r="B140" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15223,14 +15214,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729284</v>
+        <v>729300</v>
       </c>
       <c r="R140" t="n">
-        <v>6367626</v>
+        <v>6367577</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15260,30 +15251,39 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15293,7 +15293,7 @@
         <v>128693342</v>
       </c>
       <c r="B141" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>128693303</v>
       </c>
       <c r="B142" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15485,45 +15485,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128698473</v>
+        <v>128693299</v>
       </c>
       <c r="B143" t="n">
-        <v>86975</v>
+        <v>92828</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>729278</v>
+        <v>729191</v>
       </c>
       <c r="R143" t="n">
-        <v>6367631</v>
+        <v>6367801</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15564,64 +15564,63 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128693299</v>
+        <v>128698473</v>
       </c>
       <c r="B144" t="n">
-        <v>92823</v>
+        <v>86978</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>729191</v>
+        <v>729278</v>
       </c>
       <c r="R144" t="n">
-        <v>6367801</v>
+        <v>6367631</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15662,50 +15661,51 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698471</v>
+        <v>128698494</v>
       </c>
       <c r="B145" t="n">
-        <v>86975</v>
+        <v>86965</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6003295</v>
+        <v>3599</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15715,10 +15715,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729291</v>
+        <v>729262</v>
       </c>
       <c r="R145" t="n">
-        <v>6367618</v>
+        <v>6367640</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15759,7 +15759,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15778,10 +15777,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128698494</v>
+        <v>128693293</v>
       </c>
       <c r="B146" t="n">
-        <v>86962</v>
+        <v>87023</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15789,34 +15788,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3599</v>
+        <v>3767</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729262</v>
+        <v>729196</v>
       </c>
       <c r="R146" t="n">
-        <v>6367640</v>
+        <v>6367804</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15863,44 +15862,44 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693333</v>
+        <v>128693307</v>
       </c>
       <c r="B147" t="n">
-        <v>90942</v>
+        <v>91058</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4188</v>
+        <v>5747</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15910,10 +15909,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729244</v>
+        <v>729261</v>
       </c>
       <c r="R147" t="n">
-        <v>6367576</v>
+        <v>6367585</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15972,32 +15971,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693307</v>
+        <v>128693333</v>
       </c>
       <c r="B148" t="n">
-        <v>91055</v>
+        <v>90945</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5747</v>
+        <v>4188</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16007,10 +16006,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729261</v>
+        <v>729244</v>
       </c>
       <c r="R148" t="n">
-        <v>6367585</v>
+        <v>6367576</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16069,45 +16068,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128693293</v>
+        <v>128698471</v>
       </c>
       <c r="B149" t="n">
-        <v>87020</v>
+        <v>86978</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729196</v>
+        <v>729291</v>
       </c>
       <c r="R149" t="n">
-        <v>6367804</v>
+        <v>6367618</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16148,63 +16147,67 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693327</v>
+        <v>128693335</v>
       </c>
       <c r="B150" t="n">
-        <v>86997</v>
+        <v>92852</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729261</v>
+        <v>729198</v>
       </c>
       <c r="R150" t="n">
-        <v>6367585</v>
+        <v>6367846</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16245,6 +16248,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16266,7 +16270,7 @@
         <v>128698475</v>
       </c>
       <c r="B151" t="n">
-        <v>86962</v>
+        <v>86965</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16360,48 +16364,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B152" t="n">
-        <v>92847</v>
+        <v>87000</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R152" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16442,7 +16443,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16464,7 +16464,7 @@
         <v>128698476</v>
       </c>
       <c r="B153" t="n">
-        <v>86962</v>
+        <v>86965</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>128700660</v>
       </c>
       <c r="B154" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>128698488</v>
       </c>
       <c r="B155" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16762,45 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128700501</v>
+        <v>128698484</v>
       </c>
       <c r="B156" t="n">
-        <v>92847</v>
+        <v>87000</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729268</v>
+        <v>729261</v>
       </c>
       <c r="R156" t="n">
-        <v>6367544</v>
+        <v>6367615</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16830,19 +16830,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16857,57 +16847,60 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128698484</v>
+        <v>128693336</v>
       </c>
       <c r="B157" t="n">
-        <v>86997</v>
+        <v>92852</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729261</v>
+        <v>729237</v>
       </c>
       <c r="R157" t="n">
-        <v>6367615</v>
+        <v>6367593</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16948,28 +16941,29 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128693336</v>
+        <v>128693295</v>
       </c>
       <c r="B158" t="n">
-        <v>92847</v>
+        <v>88713</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16977,37 +16971,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729237</v>
+        <v>729221</v>
       </c>
       <c r="R158" t="n">
-        <v>6367593</v>
+        <v>6367854</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17048,7 +17039,6 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -17067,10 +17057,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128693295</v>
+        <v>128700501</v>
       </c>
       <c r="B159" t="n">
-        <v>88710</v>
+        <v>92852</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17078,34 +17068,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4379</v>
+        <v>5964</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729221</v>
+        <v>729268</v>
       </c>
       <c r="R159" t="n">
-        <v>6367854</v>
+        <v>6367544</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17135,9 +17125,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17152,12 +17152,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
         <v>128693326</v>
       </c>
       <c r="B160" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17261,10 +17261,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128700626</v>
+        <v>128693324</v>
       </c>
       <c r="B161" t="n">
-        <v>98673</v>
+        <v>91943</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17272,34 +17272,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>219862</v>
+        <v>5420</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729278</v>
+        <v>729284</v>
       </c>
       <c r="R161" t="n">
-        <v>6367669</v>
+        <v>6367580</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17329,19 +17329,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17356,22 +17346,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B162" t="n">
-        <v>91940</v>
+        <v>98678</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17379,34 +17369,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R162" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17436,9 +17426,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
         <v>128700430</v>
       </c>
       <c r="B163" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B164" t="n">
-        <v>86997</v>
+        <v>86803</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R164" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B165" t="n">
-        <v>86800</v>
+        <v>87000</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R165" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>128693330</v>
       </c>
       <c r="B166" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>128693294</v>
       </c>
       <c r="B167" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>128698465</v>
       </c>
       <c r="B168" t="n">
-        <v>90954</v>
+        <v>90957</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18058,32 +18058,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B169" t="n">
-        <v>86997</v>
+        <v>92852</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R169" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18131,18 +18131,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18161,32 +18155,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698490</v>
+        <v>128698485</v>
       </c>
       <c r="B170" t="n">
-        <v>92847</v>
+        <v>87000</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18196,10 +18190,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729277</v>
+        <v>729283</v>
       </c>
       <c r="R170" t="n">
-        <v>6367576</v>
+        <v>6367586</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18234,12 +18228,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18261,7 +18261,7 @@
         <v>128717177</v>
       </c>
       <c r="B171" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>128693297</v>
       </c>
       <c r="B172" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14305,32 +14305,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128693331</v>
+        <v>128693341</v>
       </c>
       <c r="B131" t="n">
-        <v>90956</v>
+        <v>86806</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2008</v>
+        <v>3712</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>729278</v>
+        <v>729192</v>
       </c>
       <c r="R131" t="n">
-        <v>6367590</v>
+        <v>6367827</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128693341</v>
+        <v>128693331</v>
       </c>
       <c r="B132" t="n">
-        <v>86803</v>
+        <v>90959</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3712</v>
+        <v>2008</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>729192</v>
+        <v>729278</v>
       </c>
       <c r="R132" t="n">
-        <v>6367827</v>
+        <v>6367590</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>128698487</v>
       </c>
       <c r="B134" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128693300</v>
       </c>
       <c r="B135" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>128698483</v>
       </c>
       <c r="B136" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>128698489</v>
       </c>
       <c r="B137" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14988,45 +14988,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128698459</v>
+        <v>128700405</v>
       </c>
       <c r="B138" t="n">
-        <v>87023</v>
+        <v>86981</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729257</v>
+        <v>729300</v>
       </c>
       <c r="R138" t="n">
-        <v>6367641</v>
+        <v>6367577</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,9 +15056,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15073,44 +15083,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698472</v>
+        <v>128698459</v>
       </c>
       <c r="B139" t="n">
-        <v>86978</v>
+        <v>87026</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15120,10 +15130,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729284</v>
+        <v>729257</v>
       </c>
       <c r="R139" t="n">
-        <v>6367626</v>
+        <v>6367641</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15164,7 +15174,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15183,10 +15192,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128700405</v>
+        <v>128698472</v>
       </c>
       <c r="B140" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15214,14 +15223,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729300</v>
+        <v>729284</v>
       </c>
       <c r="R140" t="n">
-        <v>6367577</v>
+        <v>6367626</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,71 +15260,62 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128693342</v>
+        <v>128693303</v>
       </c>
       <c r="B141" t="n">
-        <v>86803</v>
+        <v>86981</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15325,10 +15325,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>729241</v>
+        <v>729311</v>
       </c>
       <c r="R141" t="n">
-        <v>6367592</v>
+        <v>6367596</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15369,6 +15369,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15387,32 +15388,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128693303</v>
+        <v>128693342</v>
       </c>
       <c r="B142" t="n">
-        <v>86978</v>
+        <v>86806</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15422,10 +15423,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>729311</v>
+        <v>729241</v>
       </c>
       <c r="R142" t="n">
-        <v>6367596</v>
+        <v>6367592</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15466,7 +15467,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15488,7 +15488,7 @@
         <v>128693299</v>
       </c>
       <c r="B143" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>128698473</v>
       </c>
       <c r="B144" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>128698494</v>
       </c>
       <c r="B145" t="n">
-        <v>86965</v>
+        <v>86968</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15777,32 +15777,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128693293</v>
+        <v>128693333</v>
       </c>
       <c r="B146" t="n">
-        <v>87023</v>
+        <v>90948</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3767</v>
+        <v>4188</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729196</v>
+        <v>729244</v>
       </c>
       <c r="R146" t="n">
-        <v>6367804</v>
+        <v>6367576</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15874,10 +15874,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693307</v>
+        <v>128693293</v>
       </c>
       <c r="B147" t="n">
-        <v>91058</v>
+        <v>87026</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15885,21 +15885,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5747</v>
+        <v>3767</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15909,10 +15909,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729261</v>
+        <v>729196</v>
       </c>
       <c r="R147" t="n">
-        <v>6367585</v>
+        <v>6367804</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15971,32 +15971,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693333</v>
+        <v>128693307</v>
       </c>
       <c r="B148" t="n">
-        <v>90945</v>
+        <v>91061</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4188</v>
+        <v>5747</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729244</v>
+        <v>729261</v>
       </c>
       <c r="R148" t="n">
-        <v>6367576</v>
+        <v>6367585</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16071,7 +16071,7 @@
         <v>128698471</v>
       </c>
       <c r="B149" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16166,48 +16166,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B150" t="n">
-        <v>92852</v>
+        <v>87003</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R150" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16248,7 +16245,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16270,7 +16266,7 @@
         <v>128698475</v>
       </c>
       <c r="B151" t="n">
-        <v>86965</v>
+        <v>86968</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16364,45 +16360,48 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693327</v>
+        <v>128693335</v>
       </c>
       <c r="B152" t="n">
-        <v>87000</v>
+        <v>92855</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729261</v>
+        <v>729198</v>
       </c>
       <c r="R152" t="n">
-        <v>6367585</v>
+        <v>6367846</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16443,6 +16442,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16464,7 +16464,7 @@
         <v>128698476</v>
       </c>
       <c r="B153" t="n">
-        <v>86965</v>
+        <v>86968</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>128700660</v>
       </c>
       <c r="B154" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>128698488</v>
       </c>
       <c r="B155" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16762,45 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128698484</v>
+        <v>128700501</v>
       </c>
       <c r="B156" t="n">
-        <v>87000</v>
+        <v>92855</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729261</v>
+        <v>729268</v>
       </c>
       <c r="R156" t="n">
-        <v>6367615</v>
+        <v>6367544</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16830,9 +16830,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16847,12 +16857,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -16862,7 +16872,7 @@
         <v>128693336</v>
       </c>
       <c r="B157" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16960,45 +16970,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128693295</v>
+        <v>128698484</v>
       </c>
       <c r="B158" t="n">
-        <v>88713</v>
+        <v>87003</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4379</v>
+        <v>449</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729221</v>
+        <v>729261</v>
       </c>
       <c r="R158" t="n">
-        <v>6367854</v>
+        <v>6367615</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17045,22 +17055,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128700501</v>
+        <v>128693295</v>
       </c>
       <c r="B159" t="n">
-        <v>92852</v>
+        <v>88716</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17068,34 +17078,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729268</v>
+        <v>729221</v>
       </c>
       <c r="R159" t="n">
-        <v>6367544</v>
+        <v>6367854</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17125,19 +17135,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17152,57 +17152,57 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128693326</v>
+        <v>128700626</v>
       </c>
       <c r="B160" t="n">
-        <v>87000</v>
+        <v>98681</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729164</v>
+        <v>729278</v>
       </c>
       <c r="R160" t="n">
-        <v>6367575</v>
+        <v>6367669</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,9 +17232,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17249,44 +17259,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693324</v>
+        <v>128693326</v>
       </c>
       <c r="B161" t="n">
-        <v>91943</v>
+        <v>87003</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5420</v>
+        <v>449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17296,10 +17306,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729284</v>
+        <v>729164</v>
       </c>
       <c r="R161" t="n">
-        <v>6367580</v>
+        <v>6367575</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17358,10 +17368,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128700626</v>
+        <v>128693324</v>
       </c>
       <c r="B162" t="n">
-        <v>98678</v>
+        <v>91946</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17369,34 +17379,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219862</v>
+        <v>5420</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729278</v>
+        <v>729284</v>
       </c>
       <c r="R162" t="n">
-        <v>6367669</v>
+        <v>6367580</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17426,19 +17436,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
         <v>128700430</v>
       </c>
       <c r="B163" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B164" t="n">
-        <v>86803</v>
+        <v>87003</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R164" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B165" t="n">
-        <v>87000</v>
+        <v>86806</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R165" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>128693330</v>
       </c>
       <c r="B166" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>128693294</v>
       </c>
       <c r="B167" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17961,32 +17961,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698465</v>
+        <v>128698485</v>
       </c>
       <c r="B168" t="n">
-        <v>90957</v>
+        <v>87003</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2009</v>
+        <v>449</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729275</v>
+        <v>729283</v>
       </c>
       <c r="R168" t="n">
-        <v>6367651</v>
+        <v>6367586</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18034,12 +18034,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -18058,10 +18064,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B169" t="n">
-        <v>92852</v>
+        <v>90960</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18069,21 +18075,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18099,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R169" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18155,32 +18161,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B170" t="n">
-        <v>87000</v>
+        <v>92855</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18190,10 +18196,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R170" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18228,18 +18234,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18261,7 +18261,7 @@
         <v>128717177</v>
       </c>
       <c r="B171" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>128693297</v>
       </c>
       <c r="B172" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14794,10 +14794,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128698483</v>
+        <v>128698489</v>
       </c>
       <c r="B136" t="n">
-        <v>105722</v>
+        <v>92855</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14805,21 +14805,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14829,10 +14829,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>729260</v>
+        <v>729268</v>
       </c>
       <c r="R136" t="n">
-        <v>6367646</v>
+        <v>6367618</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14891,10 +14891,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128698489</v>
+        <v>128698483</v>
       </c>
       <c r="B137" t="n">
-        <v>92855</v>
+        <v>105722</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14902,21 +14902,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>729268</v>
+        <v>729260</v>
       </c>
       <c r="R137" t="n">
-        <v>6367618</v>
+        <v>6367646</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14988,45 +14988,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128700405</v>
+        <v>128698459</v>
       </c>
       <c r="B138" t="n">
-        <v>86981</v>
+        <v>87026</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729300</v>
+        <v>729257</v>
       </c>
       <c r="R138" t="n">
-        <v>6367577</v>
+        <v>6367641</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,19 +15056,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15083,44 +15073,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698459</v>
+        <v>128698472</v>
       </c>
       <c r="B139" t="n">
-        <v>87026</v>
+        <v>86981</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15130,10 +15120,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729257</v>
+        <v>729284</v>
       </c>
       <c r="R139" t="n">
-        <v>6367641</v>
+        <v>6367626</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15174,6 +15164,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15192,7 +15183,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128698472</v>
+        <v>128700405</v>
       </c>
       <c r="B140" t="n">
         <v>86981</v>
@@ -15223,14 +15214,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729284</v>
+        <v>729300</v>
       </c>
       <c r="R140" t="n">
-        <v>6367626</v>
+        <v>6367577</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15260,30 +15251,39 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16166,10 +16166,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B150" t="n">
-        <v>87003</v>
+        <v>86968</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16177,34 +16177,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R150" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16251,22 +16251,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128698475</v>
+        <v>128693327</v>
       </c>
       <c r="B151" t="n">
-        <v>86968</v>
+        <v>87003</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16274,34 +16274,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3599</v>
+        <v>449</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729259</v>
+        <v>729261</v>
       </c>
       <c r="R151" t="n">
-        <v>6367635</v>
+        <v>6367585</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16348,12 +16348,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16762,45 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128700501</v>
+        <v>128698484</v>
       </c>
       <c r="B156" t="n">
-        <v>92855</v>
+        <v>87003</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729268</v>
+        <v>729261</v>
       </c>
       <c r="R156" t="n">
-        <v>6367544</v>
+        <v>6367615</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16830,19 +16830,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16857,22 +16847,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128693336</v>
+        <v>128693295</v>
       </c>
       <c r="B157" t="n">
-        <v>92855</v>
+        <v>88716</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16880,37 +16870,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729237</v>
+        <v>729221</v>
       </c>
       <c r="R157" t="n">
-        <v>6367593</v>
+        <v>6367854</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16951,7 +16938,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -16970,45 +16956,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128698484</v>
+        <v>128693336</v>
       </c>
       <c r="B158" t="n">
-        <v>87003</v>
+        <v>92855</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729261</v>
+        <v>729237</v>
       </c>
       <c r="R158" t="n">
-        <v>6367615</v>
+        <v>6367593</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17049,28 +17038,29 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128693295</v>
+        <v>128700501</v>
       </c>
       <c r="B159" t="n">
-        <v>88716</v>
+        <v>92855</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17078,34 +17068,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4379</v>
+        <v>5964</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729221</v>
+        <v>729268</v>
       </c>
       <c r="R159" t="n">
-        <v>6367854</v>
+        <v>6367544</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17135,9 +17125,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17152,57 +17152,57 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128700626</v>
+        <v>128693326</v>
       </c>
       <c r="B160" t="n">
-        <v>98681</v>
+        <v>87003</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729278</v>
+        <v>729164</v>
       </c>
       <c r="R160" t="n">
-        <v>6367669</v>
+        <v>6367575</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17232,19 +17232,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17259,44 +17249,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693326</v>
+        <v>128693324</v>
       </c>
       <c r="B161" t="n">
-        <v>87003</v>
+        <v>91946</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>449</v>
+        <v>5420</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17306,10 +17296,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729164</v>
+        <v>729284</v>
       </c>
       <c r="R161" t="n">
-        <v>6367575</v>
+        <v>6367580</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17368,10 +17358,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128693324</v>
+        <v>128700626</v>
       </c>
       <c r="B162" t="n">
-        <v>91946</v>
+        <v>98681</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17379,34 +17369,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5420</v>
+        <v>219862</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>729284</v>
+        <v>729278</v>
       </c>
       <c r="R162" t="n">
-        <v>6367580</v>
+        <v>6367669</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17436,9 +17426,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17453,12 +17453,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B134" t="n">
-        <v>92855</v>
+        <v>92831</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R134" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B135" t="n">
-        <v>92831</v>
+        <v>92855</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R135" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,12 +14782,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14988,45 +14988,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128698459</v>
+        <v>128700405</v>
       </c>
       <c r="B138" t="n">
-        <v>87026</v>
+        <v>86981</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729257</v>
+        <v>729300</v>
       </c>
       <c r="R138" t="n">
-        <v>6367641</v>
+        <v>6367577</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,9 +15056,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15073,44 +15083,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698472</v>
+        <v>128698459</v>
       </c>
       <c r="B139" t="n">
-        <v>86981</v>
+        <v>87026</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15120,10 +15130,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729284</v>
+        <v>729257</v>
       </c>
       <c r="R139" t="n">
-        <v>6367626</v>
+        <v>6367641</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15164,7 +15174,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15183,7 +15192,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128700405</v>
+        <v>128698472</v>
       </c>
       <c r="B140" t="n">
         <v>86981</v>
@@ -15214,14 +15223,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729300</v>
+        <v>729284</v>
       </c>
       <c r="R140" t="n">
-        <v>6367577</v>
+        <v>6367626</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,71 +15260,62 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128693303</v>
+        <v>128693342</v>
       </c>
       <c r="B141" t="n">
-        <v>86981</v>
+        <v>86806</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15325,10 +15325,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>729311</v>
+        <v>729241</v>
       </c>
       <c r="R141" t="n">
-        <v>6367596</v>
+        <v>6367592</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15369,7 +15369,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15388,32 +15387,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128693342</v>
+        <v>128693303</v>
       </c>
       <c r="B142" t="n">
-        <v>86806</v>
+        <v>86981</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15423,10 +15422,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>729241</v>
+        <v>729311</v>
       </c>
       <c r="R142" t="n">
-        <v>6367592</v>
+        <v>6367596</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15467,6 +15466,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15680,10 +15680,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128698494</v>
+        <v>128693307</v>
       </c>
       <c r="B145" t="n">
-        <v>86968</v>
+        <v>91061</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15691,34 +15691,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3599</v>
+        <v>5747</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729262</v>
+        <v>729261</v>
       </c>
       <c r="R145" t="n">
-        <v>6367640</v>
+        <v>6367585</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15765,12 +15765,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15874,10 +15874,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128693293</v>
+        <v>128698494</v>
       </c>
       <c r="B147" t="n">
-        <v>87026</v>
+        <v>86968</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15885,34 +15885,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3767</v>
+        <v>3599</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729196</v>
+        <v>729262</v>
       </c>
       <c r="R147" t="n">
-        <v>6367804</v>
+        <v>6367640</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15959,22 +15959,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128693307</v>
+        <v>128693293</v>
       </c>
       <c r="B148" t="n">
-        <v>91061</v>
+        <v>87026</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15982,21 +15982,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5747</v>
+        <v>3767</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>729261</v>
+        <v>729196</v>
       </c>
       <c r="R148" t="n">
-        <v>6367585</v>
+        <v>6367804</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16166,45 +16166,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128698475</v>
+        <v>128693335</v>
       </c>
       <c r="B150" t="n">
-        <v>86968</v>
+        <v>92855</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R150" t="n">
-        <v>6367635</v>
+        <v>6367846</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16245,28 +16248,29 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B151" t="n">
-        <v>87003</v>
+        <v>86968</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16274,34 +16278,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R151" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16348,60 +16352,57 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B152" t="n">
-        <v>92855</v>
+        <v>87003</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R152" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16442,7 +16443,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16762,45 +16762,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128698484</v>
+        <v>128693295</v>
       </c>
       <c r="B156" t="n">
-        <v>87003</v>
+        <v>88716</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>449</v>
+        <v>4379</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>729261</v>
+        <v>729221</v>
       </c>
       <c r="R156" t="n">
-        <v>6367615</v>
+        <v>6367854</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16847,57 +16847,57 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128693295</v>
+        <v>128698484</v>
       </c>
       <c r="B157" t="n">
-        <v>88716</v>
+        <v>87003</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4379</v>
+        <v>449</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729221</v>
+        <v>729261</v>
       </c>
       <c r="R157" t="n">
-        <v>6367854</v>
+        <v>6367615</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16944,19 +16944,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128693336</v>
+        <v>128700501</v>
       </c>
       <c r="B158" t="n">
         <v>92855</v>
@@ -16985,19 +16985,16 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729237</v>
+        <v>729268</v>
       </c>
       <c r="R158" t="n">
-        <v>6367593</v>
+        <v>6367544</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17027,37 +17024,46 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128700501</v>
+        <v>128693336</v>
       </c>
       <c r="B159" t="n">
         <v>92855</v>
@@ -17086,16 +17092,19 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729268</v>
+        <v>729237</v>
       </c>
       <c r="R159" t="n">
-        <v>6367544</v>
+        <v>6367593</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17125,71 +17134,62 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128693326</v>
+        <v>128693324</v>
       </c>
       <c r="B160" t="n">
-        <v>87003</v>
+        <v>91946</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>449</v>
+        <v>5420</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17199,10 +17199,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>729164</v>
+        <v>729284</v>
       </c>
       <c r="R160" t="n">
-        <v>6367575</v>
+        <v>6367580</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17261,32 +17261,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128693324</v>
+        <v>128693326</v>
       </c>
       <c r="B161" t="n">
-        <v>91946</v>
+        <v>87003</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5420</v>
+        <v>449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17296,10 +17296,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>729284</v>
+        <v>729164</v>
       </c>
       <c r="R161" t="n">
-        <v>6367580</v>
+        <v>6367575</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B164" t="n">
-        <v>87003</v>
+        <v>86806</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R164" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B165" t="n">
-        <v>86806</v>
+        <v>87003</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R165" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17961,32 +17961,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B168" t="n">
-        <v>87003</v>
+        <v>92855</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R168" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18034,18 +18034,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -18161,32 +18155,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698490</v>
+        <v>128698485</v>
       </c>
       <c r="B170" t="n">
-        <v>92855</v>
+        <v>87003</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18196,10 +18190,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729277</v>
+        <v>729283</v>
       </c>
       <c r="R170" t="n">
-        <v>6367576</v>
+        <v>6367586</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18234,12 +18228,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14988,45 +14988,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128700405</v>
+        <v>128698459</v>
       </c>
       <c r="B138" t="n">
-        <v>86981</v>
+        <v>87026</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>729300</v>
+        <v>729257</v>
       </c>
       <c r="R138" t="n">
-        <v>6367577</v>
+        <v>6367641</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15056,19 +15056,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15083,44 +15073,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128698459</v>
+        <v>128698472</v>
       </c>
       <c r="B139" t="n">
-        <v>87026</v>
+        <v>86981</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15130,10 +15120,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>729257</v>
+        <v>729284</v>
       </c>
       <c r="R139" t="n">
-        <v>6367641</v>
+        <v>6367626</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15174,6 +15164,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15192,7 +15183,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128698472</v>
+        <v>128700405</v>
       </c>
       <c r="B140" t="n">
         <v>86981</v>
@@ -15223,14 +15214,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>729284</v>
+        <v>729300</v>
       </c>
       <c r="R140" t="n">
-        <v>6367626</v>
+        <v>6367577</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15260,30 +15251,39 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15680,45 +15680,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128693307</v>
+        <v>128698471</v>
       </c>
       <c r="B145" t="n">
-        <v>91061</v>
+        <v>86981</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>729261</v>
+        <v>729291</v>
       </c>
       <c r="R145" t="n">
-        <v>6367585</v>
+        <v>6367618</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15759,63 +15759,64 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128693333</v>
+        <v>128698494</v>
       </c>
       <c r="B146" t="n">
-        <v>90948</v>
+        <v>86968</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4188</v>
+        <v>3599</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>729244</v>
+        <v>729262</v>
       </c>
       <c r="R146" t="n">
-        <v>6367576</v>
+        <v>6367640</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15862,57 +15863,57 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128698494</v>
+        <v>128693333</v>
       </c>
       <c r="B147" t="n">
-        <v>86968</v>
+        <v>90948</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3599</v>
+        <v>4188</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>729262</v>
+        <v>729244</v>
       </c>
       <c r="R147" t="n">
-        <v>6367640</v>
+        <v>6367576</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15959,12 +15960,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -16068,45 +16069,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128698471</v>
+        <v>128693307</v>
       </c>
       <c r="B149" t="n">
-        <v>86981</v>
+        <v>91061</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>729291</v>
+        <v>729261</v>
       </c>
       <c r="R149" t="n">
-        <v>6367618</v>
+        <v>6367585</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16147,67 +16148,63 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128693335</v>
+        <v>128693327</v>
       </c>
       <c r="B150" t="n">
-        <v>92855</v>
+        <v>87003</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>729198</v>
+        <v>729261</v>
       </c>
       <c r="R150" t="n">
-        <v>6367846</v>
+        <v>6367585</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16248,7 +16245,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16267,45 +16263,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128698475</v>
+        <v>128693335</v>
       </c>
       <c r="B151" t="n">
-        <v>86968</v>
+        <v>92855</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>729259</v>
+        <v>729198</v>
       </c>
       <c r="R151" t="n">
-        <v>6367635</v>
+        <v>6367846</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16346,28 +16345,29 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128693327</v>
+        <v>128698475</v>
       </c>
       <c r="B152" t="n">
-        <v>87003</v>
+        <v>86968</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16375,34 +16375,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>449</v>
+        <v>3599</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>729261</v>
+        <v>729259</v>
       </c>
       <c r="R152" t="n">
-        <v>6367585</v>
+        <v>6367635</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16449,12 +16449,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16859,45 +16859,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128698484</v>
+        <v>128693336</v>
       </c>
       <c r="B157" t="n">
-        <v>87003</v>
+        <v>92855</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>729261</v>
+        <v>729237</v>
       </c>
       <c r="R157" t="n">
-        <v>6367615</v>
+        <v>6367593</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16938,63 +16941,64 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128700501</v>
+        <v>128698484</v>
       </c>
       <c r="B158" t="n">
-        <v>92855</v>
+        <v>87003</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5964</v>
+        <v>449</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hallgardshage, Hallgardshage, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>729268</v>
+        <v>729261</v>
       </c>
       <c r="R158" t="n">
-        <v>6367544</v>
+        <v>6367615</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17024,19 +17028,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17051,19 +17045,19 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128693336</v>
+        <v>128700501</v>
       </c>
       <c r="B159" t="n">
         <v>92855</v>
@@ -17092,19 +17086,16 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>Hallgardshage, Hallgardshage, Gtl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>729237</v>
+        <v>729268</v>
       </c>
       <c r="R159" t="n">
-        <v>6367593</v>
+        <v>6367544</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17134,30 +17125,39 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -17572,32 +17572,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128693340</v>
+        <v>128693328</v>
       </c>
       <c r="B164" t="n">
-        <v>86806</v>
+        <v>87003</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>729188</v>
+        <v>729292</v>
       </c>
       <c r="R164" t="n">
-        <v>6367797</v>
+        <v>6367593</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17669,32 +17669,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128693328</v>
+        <v>128693340</v>
       </c>
       <c r="B165" t="n">
-        <v>87003</v>
+        <v>86806</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>729292</v>
+        <v>729188</v>
       </c>
       <c r="R165" t="n">
-        <v>6367593</v>
+        <v>6367797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128698490</v>
+        <v>128698465</v>
       </c>
       <c r="B168" t="n">
-        <v>92855</v>
+        <v>90960</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17972,21 +17972,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>729277</v>
+        <v>729275</v>
       </c>
       <c r="R168" t="n">
-        <v>6367576</v>
+        <v>6367651</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18058,32 +18058,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128698465</v>
+        <v>128698485</v>
       </c>
       <c r="B169" t="n">
-        <v>90960</v>
+        <v>87003</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2009</v>
+        <v>449</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>729275</v>
+        <v>729283</v>
       </c>
       <c r="R169" t="n">
-        <v>6367651</v>
+        <v>6367586</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18131,12 +18131,18 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Kollekt samlat för DNA-sekvensering.</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18155,32 +18161,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128698485</v>
+        <v>128698490</v>
       </c>
       <c r="B170" t="n">
-        <v>87003</v>
+        <v>92855</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18190,10 +18196,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>729283</v>
+        <v>729277</v>
       </c>
       <c r="R170" t="n">
-        <v>6367586</v>
+        <v>6367576</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18228,18 +18234,12 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Kollekt samlat för DNA-sekvensering.</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4572-2025 artfynd.xlsx
+++ b/artfynd/A 4572-2025 artfynd.xlsx
@@ -14308,7 +14308,7 @@
         <v>128693341</v>
       </c>
       <c r="B131" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>128693331</v>
       </c>
       <c r="B132" t="n">
-        <v>90959</v>
+        <v>90963</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>128693337</v>
       </c>
       <c r="B133" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128693300</v>
+        <v>128698487</v>
       </c>
       <c r="B134" t="n">
-        <v>92831</v>
+        <v>92862</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14611,34 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kalktallskog V Skogby, Gtl</t>
+          <t>V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>729311</v>
+        <v>729255</v>
       </c>
       <c r="R134" t="n">
-        <v>6367609</v>
+        <v>6367567</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,22 +14685,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128698487</v>
+        <v>128693300</v>
       </c>
       <c r="B135" t="n">
-        <v>92855</v>
+        <v>92838</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14708,34 +14708,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>V Skogby, Gtl</t>
+          <t>Kalktallskog V Skogby, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>729255</v>
+        <v>729311</v>
       </c>
       <c r="R135" t="n">
-        <v>6367567</v>
+        <v>6367609</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,12 +14782,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14797,7 +14797,7 @@
         <v>128698489</v>
       </c>
       <c r="B136" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>128698483</v>
       </c>
       <c r="B137" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14988,45 +14988,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128698459</v>
+        <v>128700405</v>
       </c>
       <c r="B138" t="n">
-        <v>87026</v>
+        <v>86985</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-     